--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Publication" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="186">
   <si>
     <t xml:space="preserve">Item name</t>
   </si>
@@ -541,6 +541,9 @@
   </si>
   <si>
     <t xml:space="preserve">Microhomolgy of GA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEST</t>
   </si>
   <si>
     <t xml:space="preserve">n/a</t>
@@ -681,67 +684,67 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2845,7 +2848,9 @@
       <c r="D12" s="15" t="n">
         <v>126965660</v>
       </c>
-      <c r="E12" s="15"/>
+      <c r="E12" s="15" t="s">
+        <v>173</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="5"/>
     </row>
@@ -2934,10 +2939,10 @@
         <v>672515</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2974,10 +2979,10 @@
         <v>609000</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3014,10 +3019,10 @@
         <v>474998</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3054,10 +3059,10 @@
         <v>250000</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="true" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3080,7 +3085,7 @@
         <v>160</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3120,7 +3125,7 @@
         <v>160</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3143,7 +3148,7 @@
         <v>160</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3166,7 +3171,7 @@
         <v>160</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3189,7 +3194,7 @@
         <v>160</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3212,7 +3217,7 @@
         <v>160</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Publication" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="185">
   <si>
     <t xml:space="preserve">Item name</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t xml:space="preserve">Pedigree II, Pedigree III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADLD_dup_30</t>
   </si>
   <si>
     <t xml:space="preserve">Origin</t>
@@ -1509,7 +1512,9 @@
       <c r="E41" s="3"/>
     </row>
     <row r="42" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5"/>
+      <c r="A42" s="5" t="s">
+        <v>115</v>
+      </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
@@ -1819,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" s="4" customFormat="true" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1836,14 +1841,14 @@
         <v>5</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C2" s="10" t="n">
         <v>16</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" s="4" customFormat="true" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1851,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" s="10" t="n">
         <v>31</v>
@@ -1860,7 +1865,7 @@
         <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" s="4" customFormat="true" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1868,7 +1873,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C4" s="10" t="n">
         <v>3</v>
@@ -1877,7 +1882,7 @@
         <v>43</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" s="4" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1885,14 +1890,14 @@
         <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" s="4" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1900,7 +1905,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -1911,16 +1916,16 @@
         <v>27</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" s="4" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1928,7 +1933,7 @@
         <v>32</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
@@ -1939,16 +1944,16 @@
         <v>34</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" s="4" customFormat="true" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1956,16 +1961,16 @@
         <v>37</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" s="4" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1973,7 +1978,7 @@
         <v>39</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -2020,7 +2025,7 @@
         <v>45</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -2033,10 +2038,10 @@
       <c r="B17" s="5"/>
       <c r="C17" s="11"/>
       <c r="D17" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" s="4" customFormat="true" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2049,7 +2054,7 @@
         <v>52</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2066,7 +2071,7 @@
         <v>70</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -2077,7 +2082,7 @@
         <v>65</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -2094,7 +2099,7 @@
     </row>
     <row r="23" s="4" customFormat="true" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="11"/>
@@ -2102,7 +2107,7 @@
         <v>34</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2113,7 +2118,7 @@
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" s="4" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2130,7 +2135,7 @@
         <v>84</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C26" s="10" t="n">
         <v>2</v>
@@ -2139,7 +2144,7 @@
         <v>48</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" s="4" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2147,7 +2152,7 @@
         <v>86</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
@@ -2158,7 +2163,7 @@
         <v>91</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C28" s="10" t="n">
         <v>12</v>
@@ -2167,7 +2172,7 @@
         <v>45</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" s="4" customFormat="true" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2175,16 +2180,16 @@
         <v>96</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C29" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2222,7 +2227,7 @@
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2253,7 +2258,9 @@
       <c r="E36" s="5"/>
     </row>
     <row r="37" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5"/>
+      <c r="A37" s="5" t="s">
+        <v>115</v>
+      </c>
       <c r="B37" s="5"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
@@ -2579,22 +2586,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2602,7 +2609,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C2" s="15" t="n">
         <v>126687731</v>
@@ -2614,10 +2621,10 @@
         <v>277929</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2625,7 +2632,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C3" s="15" t="n">
         <v>126736375</v>
@@ -2637,10 +2644,10 @@
         <v>203432</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2648,7 +2655,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C4" s="14" t="n">
         <v>126742343</v>
@@ -2660,10 +2667,10 @@
         <v>189731</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" s="4" customFormat="true" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2671,7 +2678,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>126763901</v>
@@ -2683,10 +2690,10 @@
         <v>150283</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2694,7 +2701,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>126683194</v>
@@ -2706,10 +2713,10 @@
         <v>238941</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" s="4" customFormat="true" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2717,7 +2724,7 @@
         <v>27</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" s="15" t="n">
         <v>126761184</v>
@@ -2726,13 +2733,13 @@
         <v>126930640</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2740,7 +2747,7 @@
         <v>32</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C8" s="14" t="n">
         <v>126667591</v>
@@ -2752,10 +2759,10 @@
         <v>340785</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2763,7 +2770,7 @@
         <v>34</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>126705616</v>
@@ -2775,10 +2782,10 @@
         <v>203842</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2786,7 +2793,7 @@
         <v>37</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C10" s="14" t="n">
         <v>126686881</v>
@@ -2798,10 +2805,10 @@
         <v>228672</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2809,7 +2816,7 @@
         <v>39</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C11" s="14" t="n">
         <v>126766751</v>
@@ -2821,10 +2828,10 @@
         <v>229243</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2832,7 +2839,7 @@
         <v>41</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C12" s="15" t="n">
         <v>126687731</v>
@@ -2849,7 +2856,7 @@
         <v>42</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>126775269</v>
@@ -2866,7 +2873,7 @@
         <v>43</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>126716573</v>
@@ -2883,7 +2890,7 @@
         <v>44</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C15" s="15" t="n">
         <v>126743135</v>
@@ -2900,7 +2907,7 @@
         <v>45</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C16" s="15" t="n">
         <v>125918128</v>
@@ -2917,7 +2924,7 @@
         <v>46</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C17" s="14" t="n">
         <v>126016772</v>
@@ -2929,10 +2936,10 @@
         <v>672515</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2940,7 +2947,7 @@
         <v>56</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="14" t="n">
         <v>126050112</v>
@@ -2957,7 +2964,7 @@
         <v>61</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C19" s="14" t="n">
         <v>126156719</v>
@@ -2969,10 +2976,10 @@
         <v>609000</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2980,7 +2987,7 @@
         <v>70</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C20" s="14" t="n">
         <v>126156745</v>
@@ -2997,7 +3004,7 @@
         <v>65</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>126363827</v>
@@ -3009,10 +3016,10 @@
         <v>474998</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" s="4" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3020,7 +3027,7 @@
         <v>67</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C22" s="15" t="n">
         <v>126512007</v>
@@ -3034,10 +3041,10 @@
     </row>
     <row r="23" s="4" customFormat="true" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C23" s="14" t="n">
         <v>126522203</v>
@@ -3049,10 +3056,10 @@
         <v>250000</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" s="4" customFormat="true" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3060,7 +3067,7 @@
         <v>79</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>126695490</v>
@@ -3072,10 +3079,10 @@
         <v>340785</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3083,7 +3090,7 @@
         <v>80</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" s="14" t="n">
         <v>126698430</v>
@@ -3100,7 +3107,7 @@
         <v>84</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C26" s="14" t="n">
         <v>126705102</v>
@@ -3112,10 +3119,10 @@
         <v>324675</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3123,7 +3130,7 @@
         <v>86</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="14" t="n">
         <v>126713540</v>
@@ -3135,10 +3142,10 @@
         <v>234020</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3146,7 +3153,7 @@
         <v>91</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C28" s="14" t="n">
         <v>126718880</v>
@@ -3158,10 +3165,10 @@
         <v>148085</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3169,7 +3176,7 @@
         <v>96</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C29" s="14" t="n">
         <v>126732318</v>
@@ -3181,10 +3188,10 @@
         <v>153769</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="30" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3192,7 +3199,7 @@
         <v>98</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C30" s="14" t="n">
         <v>126736453</v>
@@ -3204,10 +3211,10 @@
         <v>127608</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3215,7 +3222,7 @@
         <v>100</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C31" s="14" t="n">
         <v>126739243</v>
@@ -3232,7 +3239,7 @@
         <v>101</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C32" s="14" t="n">
         <v>126753827</v>
@@ -3249,7 +3256,7 @@
         <v>102</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C33" s="14" t="n">
         <v>126763765</v>
@@ -3268,7 +3275,7 @@
         <v>105</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C34" s="14" t="n">
         <v>126766199</v>
@@ -3285,7 +3292,7 @@
         <v>109</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C35" s="14" t="n">
         <v>126762001</v>
@@ -3302,7 +3309,7 @@
         <v>113</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C36" s="14" t="n">
         <v>126805047</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Publication" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="185">
   <si>
     <t xml:space="preserve">Item name</t>
   </si>
@@ -3322,10 +3322,18 @@
       <c r="G36" s="5"/>
     </row>
     <row r="37" s="4" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
+      <c r="A37" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>126676469</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>126897351</v>
+      </c>
       <c r="E37" s="15"/>
       <c r="F37" s="11"/>
       <c r="G37" s="5"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2053C6-7829-4CC1-8FDE-AB235058FBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9672A1B2-89B3-4306-8B8A-1008DA86F5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Molecular" sheetId="4" r:id="rId1"/>
@@ -97,9 +97,6 @@
     <t>Canada</t>
   </si>
   <si>
-    <t>Bladder/bowel disturbances, lower limb weakness, orthostatic hypotension, impotence, decreased sweating, temperature dysregulation, ataxia, MRI showing leukodystrophy, lower limb hyperreflexia with occasional upper limb involvement</t>
-  </si>
-  <si>
     <t>10.1002/humu.22348, 10.1007/s10048-010-0269-y</t>
   </si>
   <si>
@@ -616,9 +613,6 @@
     <t>Negative family history, + autonomic disturbance, + pyramidal signs, + Ataxia, Cognitive impairment +MMSE23, MRI findings with MCP lesion</t>
   </si>
   <si>
-    <t>Three family members - symptoms listed in the Master Excel. Too lengthy place here at the current status of the website</t>
-  </si>
-  <si>
     <t>Pedigree I - Patient I</t>
   </si>
   <si>
@@ -689,6 +683,18 @@
   </si>
   <si>
     <t>Pedigree III - Patient 4</t>
+  </si>
+  <si>
+    <t>Symptoms in this family usually presented early in their 5th decade of life and consisted of bladder and/or bowel disturbances, lower limb weakness, orthostatic hypotension, and/or impotence. Disease progresses slowly and sometimes seems to remit. 
+II-2 and II-4 were said to be “crawling on the floor” in their 50s. III:10 because bedridden (tetraplegic and anarthric) at 72 and survived until 78 years. Lower limbs show marked hyperreflexia in most individuals with occasional involvement of the upper limbs. 
+Patients display a spastic gait and have frequent falls. Babinski sign is usually present of indifferent. Less overt cerebellar signs with slightly affected rapid alternating movements and finger-to-nose tests. Sensory system is intact. No hearing or visual loss. No dementia reported in the family. Nerve conduction studies normal. Electroencephalogram did not show any epileptic discharges, but did show a diffuse slowing of electrical activity. Impotence, bladder incontinence, constipation or fecal incontinence, decreased sweating, and orthostatic hypotension. 
+IV:13 had severe episodic temperature dysregulation leading to drops in temperature to as low as 32 degC. Average age of death: 62 years. 
+Brain MRI of IV:4 is representative of those seen in other family members – fluid-attenuated inversion recovery images show severe and confluent abnormalities of the white matter, even more pronounced in the posterior areas, and no significant cortical atrophy or ventriculomegaly. Spinal cord has consistently shown severe atrophy throughout. 
+Bladder/bowel disturbances, lower limb weakness, orthostatic hypotension, impotence, decreased sweating, temperature dysregulation, ataxia, MRI showing leukodystrophy, lower limb hyperreflexia with occasional upper limb involvement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedigree II - Patient 2: Sex: Male; + family history; 55 yo age of onset, 57 age at examination; + autonomic disturbance, + pyramidal signs, + ataxia; Cognitive impairment +MoCA 21 
+Pedigree II - Patient 3: Sex: Male; + family history; 52 yo age of onset; + autonomic disturbance; + pyramidal signs; + ataxia; Cognitive impairment +MMSE15 </t>
   </si>
 </sst>
 </file>
@@ -752,7 +758,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -768,6 +774,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1110,7 +1119,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2">
         <v>5</v>
@@ -1128,12 +1137,12 @@
         <v>16</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2">
         <v>5</v>
@@ -1151,12 +1160,12 @@
         <v>16</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2">
         <v>5</v>
@@ -1174,12 +1183,12 @@
         <v>16</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -1197,12 +1206,12 @@
         <v>16</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2">
         <v>5</v>
@@ -1217,15 +1226,15 @@
         <v>169456</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
@@ -1240,15 +1249,15 @@
         <v>340785</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
@@ -1266,12 +1275,12 @@
         <v>16</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2">
         <v>5</v>
@@ -1289,12 +1298,12 @@
         <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2">
         <v>5</v>
@@ -1312,12 +1321,12 @@
         <v>16</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="2">
         <v>5</v>
@@ -1334,7 +1343,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B13" s="2">
         <v>5</v>
@@ -1352,12 +1361,12 @@
         <v>16</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" s="2">
         <v>5</v>
@@ -1375,12 +1384,12 @@
         <v>16</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B15" s="2">
         <v>5</v>
@@ -1397,7 +1406,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
@@ -1415,12 +1424,12 @@
         <v>16</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B17" s="2">
         <v>5</v>
@@ -1435,15 +1444,15 @@
         <v>672515</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -1458,12 +1467,12 @@
         <v>4365976</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1478,12 +1487,12 @@
         <v>4366000</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B20" s="2">
         <v>5</v>
@@ -1500,7 +1509,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B21" s="2">
         <v>5</v>
@@ -1517,7 +1526,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" s="2">
         <v>5</v>
@@ -1532,15 +1541,15 @@
         <v>608833</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B23" s="2">
         <v>5</v>
@@ -1555,15 +1564,15 @@
         <v>474998</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" s="2">
         <v>5</v>
@@ -1580,7 +1589,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B25" s="2">
         <v>5</v>
@@ -1595,15 +1604,15 @@
         <v>250000</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B26" s="2">
         <v>5</v>
@@ -1618,12 +1627,12 @@
         <v>275347</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B27" s="2">
         <v>5</v>
@@ -1641,12 +1650,12 @@
         <v>16</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B28" s="2">
         <v>5</v>
@@ -1664,12 +1673,12 @@
         <v>16</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="2">
         <v>5</v>
@@ -1687,12 +1696,12 @@
         <v>16</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="2">
         <v>5</v>
@@ -1710,12 +1719,12 @@
         <v>16</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B31" s="2">
         <v>5</v>
@@ -1733,12 +1742,12 @@
         <v>16</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B32" s="2">
         <v>5</v>
@@ -1756,12 +1765,12 @@
         <v>16</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B33" s="2">
         <v>5</v>
@@ -1779,12 +1788,12 @@
         <v>16</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B34" s="2">
         <v>5</v>
@@ -1801,7 +1810,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B35" s="2">
         <v>5</v>
@@ -1818,7 +1827,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B36" s="2">
         <v>5</v>
@@ -1833,12 +1842,12 @@
         <v>156734</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B37" s="2">
         <v>5</v>
@@ -1855,7 +1864,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="2">
         <v>5</v>
@@ -1870,12 +1879,12 @@
         <v>59651</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B39" s="2">
         <v>5</v>
@@ -1893,12 +1902,12 @@
         <v>16</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B40" s="2">
         <v>5</v>
@@ -1910,12 +1919,12 @@
         <v>126903760</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B41" s="2">
         <v>5</v>
@@ -1927,12 +1936,12 @@
         <v>126896451</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B42" s="2">
         <v>5</v>
@@ -1981,7 +1990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -1991,16 +2000,16 @@
       <c r="C2" s="2">
         <v>16</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>19</v>
+      <c r="E2" s="6" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="2">
         <v>31</v>
@@ -2009,15 +2018,15 @@
         <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -2026,197 +2035,197 @@
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" s="2">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C19" s="2">
         <v>5</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C21" s="2">
         <v>32</v>
@@ -2224,10 +2233,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2236,37 +2245,37 @@
         <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2275,64 +2284,64 @@
         <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="E29" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C31" s="2">
         <v>12</v>
@@ -2341,69 +2350,69 @@
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C32" s="2">
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C38" s="2">
         <v>2</v>
@@ -2412,23 +2421,23 @@
         <v>58</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C40" s="2">
         <v>6</v>
@@ -2437,41 +2446,41 @@
         <v>44</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="C41" s="2">
         <v>6</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>192</v>
+        <v>189</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C42" s="2">
         <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2513,528 +2522,528 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="E27" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9672A1B2-89B3-4306-8B8A-1008DA86F5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5A6A61-A42E-4F79-9F67-4C137756E9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Molecular" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="220">
   <si>
     <t>Item name</t>
   </si>
@@ -118,9 +118,6 @@
     <t>Sweden</t>
   </si>
   <si>
-    <t>Bladder symptoms, constipation, postural hypotention, erectile dysfunction , pyramidal signs, Ataxia, NCS: Normal, SEP:Normal: , MRI showing leukodystrophy, normal cognition</t>
-  </si>
-  <si>
     <t>10.1002/humu.22348, 10.1007/s10048-010-0269-y, PMC8133955, 10.3174/ajnr.A1354, 10.1002/ajmg.b.30342, 10.1002/ana.24452</t>
   </si>
   <si>
@@ -172,12 +169,6 @@
     <t>40.5 ± 4.9</t>
   </si>
   <si>
-    <t>Bladder symptoms, constipation, postural hypotention, dry skin, pyramidal signs, Ataxia, VEP: Normal, NCS: Normal, SEP: Pathological , MRI showing leukodystrophy, increased symptoms with infection</t>
-  </si>
-  <si>
-    <t>Bowel/bladder dysfunction, impotence, orthostatic hypotention, decreased sweating, pyramidal signs, ataxia, MRI showing leukodystrophy, spastic paralysis, posterior column dysfunction, Babinski signs</t>
-  </si>
-  <si>
     <t>10.1002/humu.22348, 10.1007/s10048-010-0269-y, PMC8133955, 10.3174/ajnr.A1354, 10.1002/ana.24452</t>
   </si>
   <si>
@@ -259,12 +250,6 @@
     <t>Microhomology of "GG"</t>
   </si>
   <si>
-    <t>Bladder symptoms, constipation, erectile dysfunction, pyramidal signs, Ataxia, MMT: 23, distal sensory loss clinically, NCS: Normal, MRI showing leukodystrophy, postural tremor, perkinsonism, Levodopa responsive</t>
-  </si>
-  <si>
-    <t>Bladder symptoms, postural hypotension, heat intolerance, fecal incontinnence, pyramidal signs, ataxia, MMT: 24, 26, NCS: Normal, MRI showing leukodystrophy</t>
-  </si>
-  <si>
     <t>ADLD_dup_11</t>
   </si>
   <si>
@@ -595,33 +580,21 @@
     <t>34, 33, 37, 32</t>
   </si>
   <si>
-    <t>Late urinary urgency, dysarthria, speech apraxia and dysphafia, MRI showing leukodystrophy, asymmetrical spastic weakness of upper and lower extremities, decreased dexterity upper limb spasticity, dyspnea likely from neuromuscular weakness, neurological defects reported to be worsened by environmental heat, Additional details from three patients also listed out in Master Excel but too lengthy in the current organization of the website to paste here</t>
-  </si>
-  <si>
     <t>Canada; Northern European</t>
   </si>
   <si>
     <t>Urinary urgency and incontinence, ataxia, MRI showing leukodystrophy, slowly progressive spasticity of lower, Sex: Male, Age at symptom onset: 52, Ethnicity: Northern European, Affect: Chronic anxiety, Oral motor control and atriculation: Speech was normal, Eye and extraocular movement examination: Fine end-point nystagmus on lateral gaze, interrupted saccades, in vertical and horizontal planes, Motor examination: Tremor of lower extremities, spasticity, and cerebellar deficits, DTRs/plantar responses: Spastic in all limbs with lower limb clonus; positive Hoffman response, Sensory examination: Normal, Autonomic nervous system: late urinary urgency adn incontinence, EMG/NCV: Normal, Family history and inheritance patterns: Positive/autosomal dominant, Comorbidities: Hypertension, GERD, and degenerative joint diseaselimbs, fine motor difficulty, fine end point nystagmus on left and right lateral gaze, leg cramps, snout reflex</t>
   </si>
   <si>
-    <t>Early orthostatix intolerance, urinary urgency, ataxia, soft "breathy" and halting voice and dysphagia, MRI showing leukodystrophy, hand tremor, voice difficulties, neurological deficits worsened with respiratory infection, Affect: Normal, Oral motor control and atriculation: Soft "breathy" and halting voice and dysphagia, Eye and extraocular movement examination: normal, Motor examination: Head and hand tremor (asymmetrical), incoordination and spastic and ataxic gait, and weakness of lower extremeties, DTRs/plantar responses: Brisk with clonus/extensor, Sensory examination: Normal, Autonomic nervous system: Early orthostatic intolerance and urinary urgency, EMG/NCV: NA, Family history and inheritance patterns: Negative, Comorbidities: Migraines, gout, and dyslipidemia</t>
-  </si>
-  <si>
     <t>55, 52, 50</t>
   </si>
   <si>
-    <t>Negative family history, + autonomic disturbance, + pyramidal signs, + Ataxia, Cognitive impairment +MMSE23, MRI findings with MCP lesion</t>
-  </si>
-  <si>
     <t>Pedigree I - Patient I</t>
   </si>
   <si>
     <t>Pedigree II - Patient 2, Pedigree II - Patient 3, Pedigree III - Patient 4</t>
   </si>
   <si>
-    <t>Symptoms listed in Master excel from the different individuals while we finalize formating of the database</t>
-  </si>
-  <si>
     <t>F2-1, F2-2, F2-3</t>
   </si>
   <si>
@@ -643,9 +616,6 @@
     <t>48, 50, 48, 42</t>
   </si>
   <si>
-    <t>Urinary urgency, ejaculatory failure, orthostatic intolerance, selective noradreneric failure, isolated cardiovascular sympathetic impairment, pyramidal signs, ataxia, MRI showing leukodystrophy, many additional information for the IV family that is too lengthy for the current version of the website</t>
-  </si>
-  <si>
     <t>Giorgio 2013, Guaraldi 2011, Terlizzi et al. 2016</t>
   </si>
   <si>
@@ -662,9 +632,6 @@
   </si>
   <si>
     <t>China</t>
-  </si>
-  <si>
-    <t>Dificulty using her hands with involuntary movement, gait imbalance, urinary incontinence, constipation, speech slowly and mild inarticulate speech, neurological - postural tremor of all extremities, increasing frequency and intensity of involuntary movement when keeping arms flat or when in a standing posture, slightly increased muscle tone adn mild spasticity in the lower limbs, MMSE normal, MRI showed diffuse and symmetrical T2-hyperintense lesions in WM with less affected perventricular rims, mild withering of the cerebellum, brain stem, cerebrum, and difuse spinal cord atrophy family history - father and elder sister had similar gait impairment at least 10 years before heath and brother had several years' history of autonomic symptoms and gait disturbance and nephew has diffiulty walking</t>
   </si>
   <si>
     <t>Predicted junction</t>
@@ -695,6 +662,48 @@
   <si>
     <t xml:space="preserve">Pedigree II - Patient 2: Sex: Male; + family history; 55 yo age of onset, 57 age at examination; + autonomic disturbance, + pyramidal signs, + ataxia; Cognitive impairment +MoCA 21 
 Pedigree II - Patient 3: Sex: Male; + family history; 52 yo age of onset; + autonomic disturbance; + pyramidal signs; + ataxia; Cognitive impairment +MMSE15 </t>
+  </si>
+  <si>
+    <t>Sex: Male; Onset: 45 year; Autonomic symptoms: Bladder symptoms, constipation, postural hypotension, erectile dysfunction; Pyramidal signs: +; Ataxia: +; Cognition: Normal; Neurophysiological studies: NCS: normal, SEP: normal; MRI showing leukodystrophy: +; Includes 31 affected family members; Bladder symptoms, constipation, postural hypotention, erectile dysfunction , pyramidal signs, Ataxia, NCS: Normal, SEP:Normal: , MRI showing leukodystrophy, normal cognition</t>
+  </si>
+  <si>
+    <t>Sex: Male; Onset: 43 year; Autonomic symptoms: Bladder symptoms, constipation, postural hypotension, dry skin; Pyramidal signs: +; Ataxia: +; Cognition: Normal; Neurophysiological studies: VEP: normal, NCS: normal; SEP: pathological; MRI showing leukodystrophy: +; Other symptoms/signs: Increased symptoms with infection; Includes 3 affected family members // Bladder symptoms, constipation, postural hypotention, dry skin, pyramidal signs, Ataxia, VEP: Normal, NCS: Normal, SEP: Pathological , MRI showing leukodystrophy, increased symptoms with infection</t>
+  </si>
+  <si>
+    <t>20 individuals in this family were misdiagnosed as having chronic progressive MS.  \Early autonomic dysfunction. CT/MRI scans illustrate a widespread symmetrical demyelination of the white matter, normal immunoglobulin levels in cerebrospinal fluid, no pathological indication of brain inflammation has been found. Five generations of the ADLD pedigree involved. Disease onset mean age: 40.5 +- 4.9 years, n = 16. The earliest symptoms usually involve abnormalities of the autonomic nervous system, such as bowel/bladder dysfunction, impotence, orthostatic hypotension and decreased sweating. These symptoms precede others by several years and are followed by loss of fine motor skills. Nerve conduction velocities performed on three affected individuals were normal. Spastic paralysis and posterior column dysfunction occur in 88% of these patients, and 81% exhibit Babinski signs. Exhibit cerebellar signs. For instance, nystagmus is present in 69% of the individuals, and all patients experience ataxia. // Bowel/bladder dysfunction, impotence, orthostatic hypotention, decreased sweating, pyramidal signs, ataxia, MRI showing leukodystrophy, spastic paralysis, posterior column dysfunction, Babinski signs | Ireland: 47-year-old man with 6-year history of autonomic dysfunction; Progressive fatigue, gait ataxia, falls, dysarthria, urinary frequency, and urinary urgency; Examination showed gait ataxia and bilateral past-pointing; Neurological signs progressed over time; MRI demonstrated widespread diffuse white-matter disease with interval radiologic progression on repeat imaging; Slowly progressive multisystem neurological dysfunction consistent with ADLD caused by LMNB1 duplication; First genetically confirmed Irish case reported. | 1/58/F: Constipation for many years before neurologic symptoms. Fine motor difficulty starting in her 40s. Progressive gait difficulty, hand numbness, urinary frequency, and incontinence. Ataxia, spastic paraparesis, dysarthria, dysmetria, head titubation, hyperreflexia, sensory loss, orthostatic hypotension, confusion, lethargy, and mild dementia. Eventually wheelchair-bound and bedridden. CT/MRI showed severe diffuse symmetric white-matter disease, greatest in frontoparietal regions, with cerebellar involvement and ventricular enlargement. | 2/50/F: 15-year progressive neurologic illness. Ataxia, weakness, sensory symptoms, urinary dysfunction, constipation, decreased sweating, orthostatic light-headedness, visual complaints, and hearing impairment. MRI showed severe diffuse cerebral white-matter abnormalities with ventricular enlargement. CT showed diffuse frontoparietal white-matter lucencies. | 3/60/F: 7-year history of progressive ataxia and weakness. Urinary dysfunction, constipation, decreased sweating, visual complaints, and hearing impairment. MRI showed moderate diffuse cerebral white-matter disease with mild ventricular enlargement. CT showed mild frontoparietal-predominant white-matter changes. | 4/53/M: 20-year progressive illness. Ataxia, weakness, sensory symptoms, urinary dysfunction, constipation, decreased sweating, orthostatic symptoms, hearing impairment, and impotence. MRI showed moderate cerebral white-matter abnormalities with cerebellar and brainstem involvement. CT showed mild frontoparietal white-matter disease. | 5/56/M: 18-year progressive illness. Ataxia, weakness, sensory symptoms, urinary dysfunction, constipation, decreased sweating, orthostatic symptoms, visual complaints, and impotence. MRI showed severe diffuse cerebral white-matter abnormalities with cerebellar involvement and ventricular enlargement. CT showed diffuse centrum semiovale white-matter lucencies.</t>
+  </si>
+  <si>
+    <t>Bladder symptoms, constipation, erectile dysfunction, pyramidal signs, Ataxia, MMT: 23, distal sensory loss clinically, NCS: Normal, MRI showing leukodystrophy, postural tremor, perkinsonism, Levodopa responsive // Patient 1: Sex: M; Onset: 54 year; Autonomic symptoms: Bladder symptoms, constipation, erectile dysfunction; Pyramidal signs: +, Ataxia: +; Cognition: Normal; Neurophysiological studies: Distal sensory loss clinically; MRI showing leukodystrophy: +; Other symptoms/signs: Postural tremor; 4 patients were affected in the IL family over three generations. Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD. Patient 2: Sex: M; Onset: 50 year; Autonomic symptoms: Bladder symptoms, constipation, erectile dusfunction; Pyramidal signs: +; Ataxia: +; Cognition: MMT: 23; Neurophysiological studies: NCS: normal; MRI showing leukodystrophy: +; Other symptoms/signs: Parkinsonism, levodopa responsive, no tremor; 4 patients were affected in the IL family over three generations. Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD.</t>
+  </si>
+  <si>
+    <t>Bladder symptoms, postural hypotension, heat intolerance, fecal incontinnence, pyramidal signs, ataxia, MMT: 24, 26, NCS: Normal, MRI showing leukodystrophy // Sex: Female; Onset: 53 year; Autonomic symptoms: Bladder symptoms, postural hypotension, heat intolerance; Pyramidal signs: +; Ataxia: +; Cognition: MMT: 24; Neurophysiological studies: NCS: normal; MRI showing leukodystrophy: +; 4 patients were affected in the DE family over two generations. Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD. | Patient 2: Sex: Female; Onset: 58 year; Autonomic symptoms: Bladder symptoms, fecal incontinence; Pyramidal signs: +; Ataxia: unknown; Cognition: MMT: 26; Neurophysiological studies: NCS: normal; MRI showing leukodystrophy: +; 4 patients were affected in the DE family over two generations. Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD.</t>
+  </si>
+  <si>
+    <t>F2-1: Sex: Male; Negative family history suggestive of LD; Comorbidities: osteoarthritis; No dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination showed difficulty walking attributed to osteoarthritis; No neurodegeneration suggestive of LD; No MRI evidence of LD; Father of F2-2, grandfather of F2-3. | F2-2: Sex: Female; Negative family history suggestive of LD; Comorbidities: depression, anxiety; Presence of dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination showed nystagmus, hyperreflexia and spasticity; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daugther of F2-1, mother of F2-3 | F2-3: Sex: Female; Negative family history suggestive of LD; Comorbidities: speech delay, learning difficulties, behavioral difficulties; Dysautonomic symptoms present; No documented orthostatic hypotension; Neurological examination showed lower limbs hyperreflexia with left plantar unresponsiveness; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daughter of F2-2, granddaughter of F2-1</t>
+  </si>
+  <si>
+    <t>Late urinary urgency, dysarthria, speech apraxia and dysphafia, MRI showing leukodystrophy, asymmetrical spastic weakness of upper and lower extremities, decreased dexterity upper limb spasticity, dyspnea likely from neuromuscular weakness, neurological defects reported to be worsened by environmental heat. | DEL3-1: Sex: Female; Age at symptom onset: 37; Ethnicity: Northern European/Native American; Affect: Depressed mood; Oral motor control and atriculation: Muffled voice, unilateral facial weakness, and drooling; Eye and extraocular movement examination: Normal dilated examination, Saccadic intrusion; Motor examination: Asymmetrical spastic weakness of upper and lower extremities; DTRs/plantar responses: Lower extremity clonus/extensor; Sensory examination: Normal; Autonomic nervous system: Normal by history and laboratory testing; EMG/NCV: Normal; Family history and inheritance patterns: Positive/autosomal dominant; Comorbidities: Neurologic deficity reported to be worsened by environmental heat | DEL3-2: Sex: Female; Age at symptom onset: 34; Ethnicity: Northern European/Native American; Affect: Normal; Oral motor control and atriculation: Speech apraxia and dysphagia; Eye and extraocular movement examination: Optic disk pallor, limited up-gaze and sacadic intrusion; Motor examination: Asymmetrical (left &gt; right) spastic weakness of upper and lower extremities; DTRs/plantar responses: Brisk; Sensory examination: Normal; Autonomic nervous system: Normal by history; EMG/NCV: L peroneal entrapment neuropathy; Family history and inhertance patterns: Positive/autosomal dominant; Comorbidities: Dyspnea likely from neuromusclar weakness; L leg pain likely from peroneal neuropathy | DEL3-3: Sex: Male; Age at symptom onset: 32; Ethnicity: Northern European/Native American; Affect: Pseudobulbar affect; Oral motor control and atriculation: Dysarthria; Eye and extraocular movement examination: Normal; Motor examination: Decreased dexterity upper limb spasticity and asymmetrical weakness of upper and lower limbs (right &gt; left); DTRs/plantar responses: Brisk/extensor; Sensory examination: Normal; Autonomic nervous system: Late urinary urgency; EMG/NCV: NA; Family history and inheritance patterns: Positive/autosomal dominant; Comorbidities: Neurological deficits resported to be worsened by environmental heat</t>
+  </si>
+  <si>
+    <t>F1-1: Sex: Male; Negative family history suggestive of LD; Comorbidities: gout, diabetes, Parkinson, axonal sensorimotor polyneuropathy; Dysautonomic symptoms present; Orthostatic hypotension present; Neurological examination consistent with Parkinson and polyneuropathy; No neurodegeneration suggestive of LD; No MRI evidence of LD; Sibling of F1-2, father of F1-3, grandfather of F1-5 | F1-2: Sex: Male; Negative family history suggestive of LD; Comorbidities: hypothyroidism, sensorineural hearing loss, Meniere, posterior vitreous detachment, hypertension, essential tremor, mild cognitive impairment, irritable bowel syndrome; Negative for dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination showed slightly unsteady gait and the inability to perform the tandem gait; No neurodegeneration suggestive of LD; No MRI evidence of LD; Sibling to F1-1, father of F1-4 | F1-3: Sex: Female; Negative for family history suggestive of LD; Comorbidities: asthma, irritable bowel syndrome, migraines, goiter, erythema nodosum, chronic pain, carpal tunnel syndrome; Dysautonomic symptoms present; No documented orthostatic hypotension; Neurological examination showed slightly slow tongue movements, mild weakness in shoulder abduction, slightly slow fine finger movements and an absent right ankle jerk; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daughter of F1-1, Mother of F1-5 | F1-4: Sex: Male; Negative family history suggestive of LD; Comorbidities: hypothyroidism, depression, back pain; Dysautonomic symptoms present; No documented orthostatic hypotension; Neurological examination showed brisk reflexes, 3-5 beats of clonus, down going plantar, decreased sensation on the left L5-S1 distribution, slow and hesitant gait; No neurodegeneration suggestive of LD; No MRI evidence of LD; Son of F1-2 | F1-5: Sex: Male; Negative family history suggestive of LD; Comorbidities: failure to thrive, microcephaly, global developmental delay, autistic spectrum disorder, learning difficulties, mild dysmorphic facial features; No dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination normal; No neurodegeneration suggestive of LD; No MRI evidence of LD; Son of F1-3, grandson of F1-1</t>
+  </si>
+  <si>
+    <t>Sex: Male; Positive family history suggestive of LD (mother and maternal grandmother with neurological regression around 30 years and death a few years later); Comorbidities: neurological sequelae from MVA at age 31; Dysautonomic symptoms present; Documented orthostatic hypotension present; Neurological examination showed spastic gait, dysdiadokokinesia on the left side, brisk deep tendon reflexes, clonus, Babinski, dysautonomia at age 33; Neurodegeneration suggestive of LD present: bed ridden, no sphincter control, gastronomy at age 39; Presence of MRI evidence of LD</t>
+  </si>
+  <si>
+    <t>F3-1: Sex: Female; Negative family history suggestive of LD; No comorbidities; No dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination unremarkable; No neurodegeneration suggestive of LD; No MRI evidence of LD; Mother of F3-2 | F3-2: Sex: Female; Negative family history suggestive of LD; Comorbidities: chronic dysuria and UTIs, refractory depression, hypothyroidism, hyperlipidemia, panhypopituitarism, vitamin B12 deficiency, ankylosing spondylitis, fibromyalgia; Dysautonomic symptoms present; Documented orthostatic hypotension present; Neurological examination showed gait disturbance; Mild hyperreflexia; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daughter of F3-1</t>
+  </si>
+  <si>
+    <t>DEL1-1: Sex: Male; Age at symptom onset: 34; Ethnicity: East Asian; Affect: Normal; Oral motor control and atriculation: Soft "breathy" and halting voice and dysphagia; Eye and extraocular movement examination: normal; Motor examination: Head and hand tremor (asymmetrical), incoordination and spastic and ataxic gait, and weakness of lower extremeties; DTRs/plantar responses: Brisk with clonus/extensor; Sensory examination: Normal; Autonomic nervous system: Early orthostatic intolerance and urinary urgency; EMG/NCV: NA; Family history and inheritance patterns: Negative; Comorbidities: Migraines, gout, and dyslipidemia | Pedigree IV-Patient 5: Sex: Female; Postive family history; 43 yo age of onset; Negative autonomic disturbance; Postive for pyramidal signs; Positive for ataxia; Cognitive impairment +MMSE 9 | Pedigree IV-Patient 6: Sex: Male; Positive family history; 34 yo age of onset; Negative autonomic disturbance; Postive for pyramidal signs; Positive for ataxia; Cognitive impairment +MoCA 10</t>
+  </si>
+  <si>
+    <t>Urinary urgency, ejaculatory failure, orthostatic intolerance, selective noradreneric failure, isolated cardiovascular sympathetic impairment, pyramidal signs, ataxia, MRI showing leukodystrophy | Cardiovascular reflexes and pharmacological assessment indicated a selective sympathetic failure, sparing cardiovagal function. Microneurography revealed absent sympathetic activity. The evaluation of autonomic innervation of skin annexes showed severely depleted and morphologically abnormal noradrenergic dopamine-β-hydroxylase (DβH) immunoreactive fibres with preserved cholinergic vasoactive intestinal polypeptide (VIP) immunoreactive fibres. | IV11: Sex: Female; Sibling to IV11 and IV12; Age of onset 50; Clinical signs at first evaluation at age 53 - autonomic symptoms: bowel/bladder dysfunction, OH, cerebellar signs: ataxia; pyramidal signs: brisk tendon reflexes; psuedobulbar signs absent; detailed clinical progression listed in paper | IV10: Sex: Male; Sibling to IV10 and IV12; Age of onset 48; clinical signs at first evaluation at age 50 - autonomic symptoms: bowel/bladder dysfunction, impotence, OH; cerebellar signs: nystagmus, dysmetria, ataxia; pyramidal signs: brisk tendon reflexes, pseudobulbar signs absent; detailed clinical progression listed in paper | IV12: Sex: Male; Sibling to IV10 and IV11; age at onset: 42; clinical signs at first evaluation at 44 years old - autonomic symptoms: bladder dysfunction, impotence, OH; cerebellar signs: action tremor, ataxia; pyramidal signs: brisk tendon reflexes, pseudobulbar signs absent; detailed clinical progression listed in paper</t>
+  </si>
+  <si>
+    <t>Proband II-4: Sex: Female; Difficulty using her hands with involuntary movement, gait imbalance, urinary incontinence, constipation, speech slowly and mild inarticulate speech; Neurological - postural tremor of all extremities, increasing frequency and intensity of involuntary movement when keeping arms flat or when in a standing posture, slightly increased muscle tone and mild spasticity in the lower limbs, MMSE normal, MRI showed diffuse and symmetrical T2-hyperintense lesions in WM with less affected perventricular rims, mild withering of the cerebellum, brain stem, cerebrum, and difuse spinal cord atrophy; Family history - father and elder sister had similar gait impairment at least 10 years before heath and brother had several years' history of autonomic symptoms and gait disturbance and nephew has diffiulty walking</t>
+  </si>
+  <si>
+    <t>Pedigree I - Patient 1: Sex: Female; Negative family history; 44 yo age of onset; + autonomic disturbance; + pyramidal signs; + Ataxia; Cognitive impairment +MMSE23; MRI findings with MCP lesion</t>
   </si>
 </sst>
 </file>
@@ -1142,7 +1151,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2">
         <v>5</v>
@@ -1160,12 +1169,12 @@
         <v>16</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2">
         <v>5</v>
@@ -1183,12 +1192,12 @@
         <v>16</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -1206,12 +1215,12 @@
         <v>16</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2">
         <v>5</v>
@@ -1226,15 +1235,15 @@
         <v>169456</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
@@ -1249,15 +1258,15 @@
         <v>340785</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
@@ -1275,12 +1284,12 @@
         <v>16</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2">
         <v>5</v>
@@ -1298,12 +1307,12 @@
         <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2">
         <v>5</v>
@@ -1321,12 +1330,12 @@
         <v>16</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B12" s="2">
         <v>5</v>
@@ -1343,7 +1352,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B13" s="2">
         <v>5</v>
@@ -1361,12 +1370,12 @@
         <v>16</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2">
         <v>5</v>
@@ -1384,12 +1393,12 @@
         <v>16</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B15" s="2">
         <v>5</v>
@@ -1406,7 +1415,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
@@ -1424,12 +1433,12 @@
         <v>16</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B17" s="2">
         <v>5</v>
@@ -1444,15 +1453,15 @@
         <v>672515</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -1467,12 +1476,12 @@
         <v>4365976</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1487,12 +1496,12 @@
         <v>4366000</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B20" s="2">
         <v>5</v>
@@ -1509,7 +1518,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2">
         <v>5</v>
@@ -1526,7 +1535,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B22" s="2">
         <v>5</v>
@@ -1541,15 +1550,15 @@
         <v>608833</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B23" s="2">
         <v>5</v>
@@ -1564,15 +1573,15 @@
         <v>474998</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B24" s="2">
         <v>5</v>
@@ -1589,7 +1598,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B25" s="2">
         <v>5</v>
@@ -1604,15 +1613,15 @@
         <v>250000</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B26" s="2">
         <v>5</v>
@@ -1627,12 +1636,12 @@
         <v>275347</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B27" s="2">
         <v>5</v>
@@ -1650,12 +1659,12 @@
         <v>16</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B28" s="2">
         <v>5</v>
@@ -1673,12 +1682,12 @@
         <v>16</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B29" s="2">
         <v>5</v>
@@ -1696,12 +1705,12 @@
         <v>16</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B30" s="2">
         <v>5</v>
@@ -1719,12 +1728,12 @@
         <v>16</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B31" s="2">
         <v>5</v>
@@ -1742,12 +1751,12 @@
         <v>16</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B32" s="2">
         <v>5</v>
@@ -1765,12 +1774,12 @@
         <v>16</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B33" s="2">
         <v>5</v>
@@ -1788,12 +1797,12 @@
         <v>16</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B34" s="2">
         <v>5</v>
@@ -1810,7 +1819,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B35" s="2">
         <v>5</v>
@@ -1827,7 +1836,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B36" s="2">
         <v>5</v>
@@ -1842,12 +1851,12 @@
         <v>156734</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B37" s="2">
         <v>5</v>
@@ -1864,7 +1873,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B38" s="2">
         <v>5</v>
@@ -1879,12 +1888,12 @@
         <v>59651</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B39" s="2">
         <v>5</v>
@@ -1902,12 +1911,12 @@
         <v>16</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B40" s="2">
         <v>5</v>
@@ -1919,12 +1928,12 @@
         <v>126903760</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B41" s="2">
         <v>5</v>
@@ -1936,12 +1945,12 @@
         <v>126896451</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B42" s="2">
         <v>5</v>
@@ -2001,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2018,12 +2027,12 @@
         <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>26</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>25</v>
@@ -2035,197 +2044,197 @@
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>44</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>45</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>73</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>74</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C19" s="2">
         <v>5</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C21" s="2">
         <v>32</v>
@@ -2233,10 +2242,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2245,37 +2254,37 @@
         <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>40</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2284,64 +2293,64 @@
         <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2">
         <v>12</v>
@@ -2350,69 +2359,69 @@
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C32" s="2">
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C38" s="2">
         <v>2</v>
@@ -2421,23 +2430,23 @@
         <v>58</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C40" s="2">
         <v>6</v>
@@ -2446,41 +2455,41 @@
         <v>44</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="195" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C41" s="2">
         <v>6</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C42" s="2">
         <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2539,511 +2548,511 @@
         <v>23</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5A6A61-A42E-4F79-9F67-4C137756E9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16B7447-1DC4-4810-A71F-79D9D70DB06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Molecular" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="219">
   <si>
     <t>Item name</t>
   </si>
@@ -583,9 +583,6 @@
     <t>Canada; Northern European</t>
   </si>
   <si>
-    <t>Urinary urgency and incontinence, ataxia, MRI showing leukodystrophy, slowly progressive spasticity of lower, Sex: Male, Age at symptom onset: 52, Ethnicity: Northern European, Affect: Chronic anxiety, Oral motor control and atriculation: Speech was normal, Eye and extraocular movement examination: Fine end-point nystagmus on lateral gaze, interrupted saccades, in vertical and horizontal planes, Motor examination: Tremor of lower extremities, spasticity, and cerebellar deficits, DTRs/plantar responses: Spastic in all limbs with lower limb clonus; positive Hoffman response, Sensory examination: Normal, Autonomic nervous system: late urinary urgency adn incontinence, EMG/NCV: Normal, Family history and inheritance patterns: Positive/autosomal dominant, Comorbidities: Hypertension, GERD, and degenerative joint diseaselimbs, fine motor difficulty, fine end point nystagmus on left and right lateral gaze, leg cramps, snout reflex</t>
-  </si>
-  <si>
     <t>55, 52, 50</t>
   </si>
   <si>
@@ -646,64 +643,58 @@
     <t>ADLD_dup_30</t>
   </si>
   <si>
-    <t xml:space="preserve">Pedigree II - Patient 2: Sex: Male; + family history; 55 yo age of onset, 57 age at examination; + autonomic disturbance, + pyramidal signs, + ataxia; Cognitive impairment +MoCA 21 | Pedigree II - Patient 3: Sex: Male; + family history; 52 yo age of onset; + autonomic disturbance; + pyramidal signs; + ataxia; Cognitive impairment +MMSE15 </t>
-  </si>
-  <si>
     <t>Pedigree III - Patient 4</t>
   </si>
   <si>
-    <t>Symptoms in this family usually presented early in their 5th decade of life and consisted of bladder and/or bowel disturbances, lower limb weakness, orthostatic hypotension, and/or impotence. Disease progresses slowly and sometimes seems to remit. 
-II-2 and II-4 were said to be “crawling on the floor” in their 50s. III:10 because bedridden (tetraplegic and anarthric) at 72 and survived until 78 years. Lower limbs show marked hyperreflexia in most individuals with occasional involvement of the upper limbs. 
-Patients display a spastic gait and have frequent falls. Babinski sign is usually present of indifferent. Less overt cerebellar signs with slightly affected rapid alternating movements and finger-to-nose tests. Sensory system is intact. No hearing or visual loss. No dementia reported in the family. Nerve conduction studies normal. Electroencephalogram did not show any epileptic discharges, but did show a diffuse slowing of electrical activity. Impotence, bladder incontinence, constipation or fecal incontinence, decreased sweating, and orthostatic hypotension. 
-IV:13 had severe episodic temperature dysregulation leading to drops in temperature to as low as 32 degC. Average age of death: 62 years. 
-Brain MRI of IV:4 is representative of those seen in other family members – fluid-attenuated inversion recovery images show severe and confluent abnormalities of the white matter, even more pronounced in the posterior areas, and no significant cortical atrophy or ventriculomegaly. Spinal cord has consistently shown severe atrophy throughout. 
-Bladder/bowel disturbances, lower limb weakness, orthostatic hypotension, impotence, decreased sweating, temperature dysregulation, ataxia, MRI showing leukodystrophy, lower limb hyperreflexia with occasional upper limb involvement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedigree II - Patient 2: Sex: Male; + family history; 55 yo age of onset, 57 age at examination; + autonomic disturbance, + pyramidal signs, + ataxia; Cognitive impairment +MoCA 21 
-Pedigree II - Patient 3: Sex: Male; + family history; 52 yo age of onset; + autonomic disturbance; + pyramidal signs; + ataxia; Cognitive impairment +MMSE15 </t>
-  </si>
-  <si>
     <t>Sex: Male; Onset: 45 year; Autonomic symptoms: Bladder symptoms, constipation, postural hypotension, erectile dysfunction; Pyramidal signs: +; Ataxia: +; Cognition: Normal; Neurophysiological studies: NCS: normal, SEP: normal; MRI showing leukodystrophy: +; Includes 31 affected family members; Bladder symptoms, constipation, postural hypotention, erectile dysfunction , pyramidal signs, Ataxia, NCS: Normal, SEP:Normal: , MRI showing leukodystrophy, normal cognition</t>
   </si>
   <si>
-    <t>Sex: Male; Onset: 43 year; Autonomic symptoms: Bladder symptoms, constipation, postural hypotension, dry skin; Pyramidal signs: +; Ataxia: +; Cognition: Normal; Neurophysiological studies: VEP: normal, NCS: normal; SEP: pathological; MRI showing leukodystrophy: +; Other symptoms/signs: Increased symptoms with infection; Includes 3 affected family members // Bladder symptoms, constipation, postural hypotention, dry skin, pyramidal signs, Ataxia, VEP: Normal, NCS: Normal, SEP: Pathological , MRI showing leukodystrophy, increased symptoms with infection</t>
-  </si>
-  <si>
-    <t>20 individuals in this family were misdiagnosed as having chronic progressive MS.  \Early autonomic dysfunction. CT/MRI scans illustrate a widespread symmetrical demyelination of the white matter, normal immunoglobulin levels in cerebrospinal fluid, no pathological indication of brain inflammation has been found. Five generations of the ADLD pedigree involved. Disease onset mean age: 40.5 +- 4.9 years, n = 16. The earliest symptoms usually involve abnormalities of the autonomic nervous system, such as bowel/bladder dysfunction, impotence, orthostatic hypotension and decreased sweating. These symptoms precede others by several years and are followed by loss of fine motor skills. Nerve conduction velocities performed on three affected individuals were normal. Spastic paralysis and posterior column dysfunction occur in 88% of these patients, and 81% exhibit Babinski signs. Exhibit cerebellar signs. For instance, nystagmus is present in 69% of the individuals, and all patients experience ataxia. // Bowel/bladder dysfunction, impotence, orthostatic hypotention, decreased sweating, pyramidal signs, ataxia, MRI showing leukodystrophy, spastic paralysis, posterior column dysfunction, Babinski signs | Ireland: 47-year-old man with 6-year history of autonomic dysfunction; Progressive fatigue, gait ataxia, falls, dysarthria, urinary frequency, and urinary urgency; Examination showed gait ataxia and bilateral past-pointing; Neurological signs progressed over time; MRI demonstrated widespread diffuse white-matter disease with interval radiologic progression on repeat imaging; Slowly progressive multisystem neurological dysfunction consistent with ADLD caused by LMNB1 duplication; First genetically confirmed Irish case reported. | 1/58/F: Constipation for many years before neurologic symptoms. Fine motor difficulty starting in her 40s. Progressive gait difficulty, hand numbness, urinary frequency, and incontinence. Ataxia, spastic paraparesis, dysarthria, dysmetria, head titubation, hyperreflexia, sensory loss, orthostatic hypotension, confusion, lethargy, and mild dementia. Eventually wheelchair-bound and bedridden. CT/MRI showed severe diffuse symmetric white-matter disease, greatest in frontoparietal regions, with cerebellar involvement and ventricular enlargement. | 2/50/F: 15-year progressive neurologic illness. Ataxia, weakness, sensory symptoms, urinary dysfunction, constipation, decreased sweating, orthostatic light-headedness, visual complaints, and hearing impairment. MRI showed severe diffuse cerebral white-matter abnormalities with ventricular enlargement. CT showed diffuse frontoparietal white-matter lucencies. | 3/60/F: 7-year history of progressive ataxia and weakness. Urinary dysfunction, constipation, decreased sweating, visual complaints, and hearing impairment. MRI showed moderate diffuse cerebral white-matter disease with mild ventricular enlargement. CT showed mild frontoparietal-predominant white-matter changes. | 4/53/M: 20-year progressive illness. Ataxia, weakness, sensory symptoms, urinary dysfunction, constipation, decreased sweating, orthostatic symptoms, hearing impairment, and impotence. MRI showed moderate cerebral white-matter abnormalities with cerebellar and brainstem involvement. CT showed mild frontoparietal white-matter disease. | 5/56/M: 18-year progressive illness. Ataxia, weakness, sensory symptoms, urinary dysfunction, constipation, decreased sweating, orthostatic symptoms, visual complaints, and impotence. MRI showed severe diffuse cerebral white-matter abnormalities with cerebellar involvement and ventricular enlargement. CT showed diffuse centrum semiovale white-matter lucencies.</t>
-  </si>
-  <si>
-    <t>Bladder symptoms, constipation, erectile dysfunction, pyramidal signs, Ataxia, MMT: 23, distal sensory loss clinically, NCS: Normal, MRI showing leukodystrophy, postural tremor, perkinsonism, Levodopa responsive // Patient 1: Sex: M; Onset: 54 year; Autonomic symptoms: Bladder symptoms, constipation, erectile dysfunction; Pyramidal signs: +, Ataxia: +; Cognition: Normal; Neurophysiological studies: Distal sensory loss clinically; MRI showing leukodystrophy: +; Other symptoms/signs: Postural tremor; 4 patients were affected in the IL family over three generations. Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD. Patient 2: Sex: M; Onset: 50 year; Autonomic symptoms: Bladder symptoms, constipation, erectile dusfunction; Pyramidal signs: +; Ataxia: +; Cognition: MMT: 23; Neurophysiological studies: NCS: normal; MRI showing leukodystrophy: +; Other symptoms/signs: Parkinsonism, levodopa responsive, no tremor; 4 patients were affected in the IL family over three generations. Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD.</t>
-  </si>
-  <si>
-    <t>Bladder symptoms, postural hypotension, heat intolerance, fecal incontinnence, pyramidal signs, ataxia, MMT: 24, 26, NCS: Normal, MRI showing leukodystrophy // Sex: Female; Onset: 53 year; Autonomic symptoms: Bladder symptoms, postural hypotension, heat intolerance; Pyramidal signs: +; Ataxia: +; Cognition: MMT: 24; Neurophysiological studies: NCS: normal; MRI showing leukodystrophy: +; 4 patients were affected in the DE family over two generations. Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD. | Patient 2: Sex: Female; Onset: 58 year; Autonomic symptoms: Bladder symptoms, fecal incontinence; Pyramidal signs: +; Ataxia: unknown; Cognition: MMT: 26; Neurophysiological studies: NCS: normal; MRI showing leukodystrophy: +; 4 patients were affected in the DE family over two generations. Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD.</t>
-  </si>
-  <si>
-    <t>F2-1: Sex: Male; Negative family history suggestive of LD; Comorbidities: osteoarthritis; No dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination showed difficulty walking attributed to osteoarthritis; No neurodegeneration suggestive of LD; No MRI evidence of LD; Father of F2-2, grandfather of F2-3. | F2-2: Sex: Female; Negative family history suggestive of LD; Comorbidities: depression, anxiety; Presence of dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination showed nystagmus, hyperreflexia and spasticity; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daugther of F2-1, mother of F2-3 | F2-3: Sex: Female; Negative family history suggestive of LD; Comorbidities: speech delay, learning difficulties, behavioral difficulties; Dysautonomic symptoms present; No documented orthostatic hypotension; Neurological examination showed lower limbs hyperreflexia with left plantar unresponsiveness; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daughter of F2-2, granddaughter of F2-1</t>
-  </si>
-  <si>
-    <t>Late urinary urgency, dysarthria, speech apraxia and dysphafia, MRI showing leukodystrophy, asymmetrical spastic weakness of upper and lower extremities, decreased dexterity upper limb spasticity, dyspnea likely from neuromuscular weakness, neurological defects reported to be worsened by environmental heat. | DEL3-1: Sex: Female; Age at symptom onset: 37; Ethnicity: Northern European/Native American; Affect: Depressed mood; Oral motor control and atriculation: Muffled voice, unilateral facial weakness, and drooling; Eye and extraocular movement examination: Normal dilated examination, Saccadic intrusion; Motor examination: Asymmetrical spastic weakness of upper and lower extremities; DTRs/plantar responses: Lower extremity clonus/extensor; Sensory examination: Normal; Autonomic nervous system: Normal by history and laboratory testing; EMG/NCV: Normal; Family history and inheritance patterns: Positive/autosomal dominant; Comorbidities: Neurologic deficity reported to be worsened by environmental heat | DEL3-2: Sex: Female; Age at symptom onset: 34; Ethnicity: Northern European/Native American; Affect: Normal; Oral motor control and atriculation: Speech apraxia and dysphagia; Eye and extraocular movement examination: Optic disk pallor, limited up-gaze and sacadic intrusion; Motor examination: Asymmetrical (left &gt; right) spastic weakness of upper and lower extremities; DTRs/plantar responses: Brisk; Sensory examination: Normal; Autonomic nervous system: Normal by history; EMG/NCV: L peroneal entrapment neuropathy; Family history and inhertance patterns: Positive/autosomal dominant; Comorbidities: Dyspnea likely from neuromusclar weakness; L leg pain likely from peroneal neuropathy | DEL3-3: Sex: Male; Age at symptom onset: 32; Ethnicity: Northern European/Native American; Affect: Pseudobulbar affect; Oral motor control and atriculation: Dysarthria; Eye and extraocular movement examination: Normal; Motor examination: Decreased dexterity upper limb spasticity and asymmetrical weakness of upper and lower limbs (right &gt; left); DTRs/plantar responses: Brisk/extensor; Sensory examination: Normal; Autonomic nervous system: Late urinary urgency; EMG/NCV: NA; Family history and inheritance patterns: Positive/autosomal dominant; Comorbidities: Neurological deficits resported to be worsened by environmental heat</t>
-  </si>
-  <si>
-    <t>F1-1: Sex: Male; Negative family history suggestive of LD; Comorbidities: gout, diabetes, Parkinson, axonal sensorimotor polyneuropathy; Dysautonomic symptoms present; Orthostatic hypotension present; Neurological examination consistent with Parkinson and polyneuropathy; No neurodegeneration suggestive of LD; No MRI evidence of LD; Sibling of F1-2, father of F1-3, grandfather of F1-5 | F1-2: Sex: Male; Negative family history suggestive of LD; Comorbidities: hypothyroidism, sensorineural hearing loss, Meniere, posterior vitreous detachment, hypertension, essential tremor, mild cognitive impairment, irritable bowel syndrome; Negative for dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination showed slightly unsteady gait and the inability to perform the tandem gait; No neurodegeneration suggestive of LD; No MRI evidence of LD; Sibling to F1-1, father of F1-4 | F1-3: Sex: Female; Negative for family history suggestive of LD; Comorbidities: asthma, irritable bowel syndrome, migraines, goiter, erythema nodosum, chronic pain, carpal tunnel syndrome; Dysautonomic symptoms present; No documented orthostatic hypotension; Neurological examination showed slightly slow tongue movements, mild weakness in shoulder abduction, slightly slow fine finger movements and an absent right ankle jerk; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daughter of F1-1, Mother of F1-5 | F1-4: Sex: Male; Negative family history suggestive of LD; Comorbidities: hypothyroidism, depression, back pain; Dysautonomic symptoms present; No documented orthostatic hypotension; Neurological examination showed brisk reflexes, 3-5 beats of clonus, down going plantar, decreased sensation on the left L5-S1 distribution, slow and hesitant gait; No neurodegeneration suggestive of LD; No MRI evidence of LD; Son of F1-2 | F1-5: Sex: Male; Negative family history suggestive of LD; Comorbidities: failure to thrive, microcephaly, global developmental delay, autistic spectrum disorder, learning difficulties, mild dysmorphic facial features; No dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination normal; No neurodegeneration suggestive of LD; No MRI evidence of LD; Son of F1-3, grandson of F1-1</t>
-  </si>
-  <si>
     <t>Sex: Male; Positive family history suggestive of LD (mother and maternal grandmother with neurological regression around 30 years and death a few years later); Comorbidities: neurological sequelae from MVA at age 31; Dysautonomic symptoms present; Documented orthostatic hypotension present; Neurological examination showed spastic gait, dysdiadokokinesia on the left side, brisk deep tendon reflexes, clonus, Babinski, dysautonomia at age 33; Neurodegeneration suggestive of LD present: bed ridden, no sphincter control, gastronomy at age 39; Presence of MRI evidence of LD</t>
   </si>
   <si>
-    <t>F3-1: Sex: Female; Negative family history suggestive of LD; No comorbidities; No dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination unremarkable; No neurodegeneration suggestive of LD; No MRI evidence of LD; Mother of F3-2 | F3-2: Sex: Female; Negative family history suggestive of LD; Comorbidities: chronic dysuria and UTIs, refractory depression, hypothyroidism, hyperlipidemia, panhypopituitarism, vitamin B12 deficiency, ankylosing spondylitis, fibromyalgia; Dysautonomic symptoms present; Documented orthostatic hypotension present; Neurological examination showed gait disturbance; Mild hyperreflexia; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daughter of F3-1</t>
-  </si>
-  <si>
-    <t>DEL1-1: Sex: Male; Age at symptom onset: 34; Ethnicity: East Asian; Affect: Normal; Oral motor control and atriculation: Soft "breathy" and halting voice and dysphagia; Eye and extraocular movement examination: normal; Motor examination: Head and hand tremor (asymmetrical), incoordination and spastic and ataxic gait, and weakness of lower extremeties; DTRs/plantar responses: Brisk with clonus/extensor; Sensory examination: Normal; Autonomic nervous system: Early orthostatic intolerance and urinary urgency; EMG/NCV: NA; Family history and inheritance patterns: Negative; Comorbidities: Migraines, gout, and dyslipidemia | Pedigree IV-Patient 5: Sex: Female; Postive family history; 43 yo age of onset; Negative autonomic disturbance; Postive for pyramidal signs; Positive for ataxia; Cognitive impairment +MMSE 9 | Pedigree IV-Patient 6: Sex: Male; Positive family history; 34 yo age of onset; Negative autonomic disturbance; Postive for pyramidal signs; Positive for ataxia; Cognitive impairment +MoCA 10</t>
-  </si>
-  <si>
-    <t>Urinary urgency, ejaculatory failure, orthostatic intolerance, selective noradreneric failure, isolated cardiovascular sympathetic impairment, pyramidal signs, ataxia, MRI showing leukodystrophy | Cardiovascular reflexes and pharmacological assessment indicated a selective sympathetic failure, sparing cardiovagal function. Microneurography revealed absent sympathetic activity. The evaluation of autonomic innervation of skin annexes showed severely depleted and morphologically abnormal noradrenergic dopamine-β-hydroxylase (DβH) immunoreactive fibres with preserved cholinergic vasoactive intestinal polypeptide (VIP) immunoreactive fibres. | IV11: Sex: Female; Sibling to IV11 and IV12; Age of onset 50; Clinical signs at first evaluation at age 53 - autonomic symptoms: bowel/bladder dysfunction, OH, cerebellar signs: ataxia; pyramidal signs: brisk tendon reflexes; psuedobulbar signs absent; detailed clinical progression listed in paper | IV10: Sex: Male; Sibling to IV10 and IV12; Age of onset 48; clinical signs at first evaluation at age 50 - autonomic symptoms: bowel/bladder dysfunction, impotence, OH; cerebellar signs: nystagmus, dysmetria, ataxia; pyramidal signs: brisk tendon reflexes, pseudobulbar signs absent; detailed clinical progression listed in paper | IV12: Sex: Male; Sibling to IV10 and IV11; age at onset: 42; clinical signs at first evaluation at 44 years old - autonomic symptoms: bladder dysfunction, impotence, OH; cerebellar signs: action tremor, ataxia; pyramidal signs: brisk tendon reflexes, pseudobulbar signs absent; detailed clinical progression listed in paper</t>
-  </si>
-  <si>
-    <t>Proband II-4: Sex: Female; Difficulty using her hands with involuntary movement, gait imbalance, urinary incontinence, constipation, speech slowly and mild inarticulate speech; Neurological - postural tremor of all extremities, increasing frequency and intensity of involuntary movement when keeping arms flat or when in a standing posture, slightly increased muscle tone and mild spasticity in the lower limbs, MMSE normal, MRI showed diffuse and symmetrical T2-hyperintense lesions in WM with less affected perventricular rims, mild withering of the cerebellum, brain stem, cerebrum, and difuse spinal cord atrophy; Family history - father and elder sister had similar gait impairment at least 10 years before heath and brother had several years' history of autonomic symptoms and gait disturbance and nephew has diffiulty walking</t>
-  </si>
-  <si>
-    <t>Pedigree I - Patient 1: Sex: Female; Negative family history; 44 yo age of onset; + autonomic disturbance; + pyramidal signs; + Ataxia; Cognitive impairment +MMSE23; MRI findings with MCP lesion</t>
+    <t>Sex: Male; Onset: 43 year; Autonomic symptoms: Bladder symptoms, constipation, postural hypotension, dry skin; Pyramidal signs: +; Ataxia: +; Cognition: Normal; Neurophysiological studies: VEP: normal, NCS: normal; SEP: pathological; MRI showing leukodystrophy: +; Other symptoms/signs: Increased symptoms with infection; Includes 3 affected family members ... Bladder symptoms, constipation, postural hypotention, dry skin, pyramidal signs, Ataxia, VEP: Normal, NCS: Normal, SEP: Pathological , MRI showing leukodystrophy, increased symptoms with infection</t>
+  </si>
+  <si>
+    <t>20 individuals in this family were misdiagnosed as having chronic progressive MS.  Early autonomic dysfunction. CT/MRI scans illustrate a widespread symmetrical demyelination of the white matter, normal immunoglobulin levels in cerebrospinal fluid, no pathological indication of brain inflammation has been found. Five generations of the ADLD pedigree involved. Disease onset mean age: 40.5 +- 4.9 years, n = 16. The earliest symptoms usually involve abnormalities of the autonomic nervous system, such as bowel/bladder dysfunction, impotence, orthostatic hypotension and decreased sweating. These symptoms precede others by several years and are followed by loss of fine motor skills. Nerve conduction velocities performed on three affected individuals were normal. Spastic paralysis and posterior column dysfunction occur in 88% of these patients, and 81% exhibit Babinski signs. Exhibit cerebellar signs. For instance, nystagmus is present in 69% of the individuals, and all patients experience ataxia. ... Bowel/bladder dysfunction, impotence, orthostatic hypotention, decreased sweating, pyramidal signs, ataxia, MRI showing leukodystrophy, spastic paralysis, posterior column dysfunction, Babinski signs. ... [PATIENT] Ireland: 47-year-old man with 6-year history of autonomic dysfunction; Progressive fatigue, gait ataxia, falls, dysarthria, urinary frequency, and urinary urgency; Examination showed gait ataxia and bilateral past-pointing; Neurological signs progressed over time; MRI demonstrated widespread diffuse white-matter disease with interval radiologic progression on repeat imaging; Slowly progressive multisystem neurological dysfunction consistent with ADLD caused by LMNB1 duplication; First genetically confirmed Irish case reported. ... [1/58/F] Constipation for many years before neurologic symptoms. Fine motor difficulty starting in her 40s. Progressive gait difficulty, hand numbness, urinary frequency, and incontinence. Ataxia, spastic paraparesis, dysarthria, dysmetria, head titubation, hyperreflexia, sensory loss, orthostatic hypotension, confusion, lethargy, and mild dementia. Eventually wheelchair-bound and bedridden. CT/MRI showed severe diffuse symmetric white-matter disease, greatest in frontoparietal regions, with cerebellar involvement and ventricular enlargement. ...[2/50/F] 15-year progressive neurologic illness. Ataxia, weakness, sensory symptoms, urinary dysfunction, constipation, decreased sweating, orthostatic light-headedness, visual complaints, and hearing impairment. MRI showed severe diffuse cerebral white-matter abnormalities with ventricular enlargement. CT showed diffuse frontoparietal white-matter lucencies. ... [3/60/F] 7-year history of progressive ataxia and weakness. Urinary dysfunction, constipation, decreased sweating, visual complaints, and hearing impairment. MRI showed moderate diffuse cerebral white-matter disease with mild ventricular enlargement. CT showed mild frontoparietal-predominant white-matter changes. ... [4/53/M] 20-year progressive illness. Ataxia, weakness, sensory symptoms, urinary dysfunction, constipation, decreased sweating, orthostatic symptoms, hearing impairment, and impotence. MRI showed moderate cerebral white-matter abnormalities with cerebellar and brainstem involvement. CT showed mild frontoparietal white-matter disease. ... [5/56/M] 18-year progressive illness. Ataxia, weakness, sensory symptoms, urinary dysfunction, constipation, decreased sweating, orthostatic symptoms, visual complaints, and impotence. MRI showed severe diffuse cerebral white-matter abnormalities with cerebellar involvement and ventricular enlargement. CT showed diffuse centrum semiovale white-matter lucencies.</t>
+  </si>
+  <si>
+    <t>[SHARED FAMILY SYMPTOMS] Symptoms in this family usually presented early in their 5th decade of life and consisted of bladder and/or bowel disturbances, lower limb weakness, orthostatic hypotension, and/or impotence. Disease progresses slowly and sometimes seems to remit. ... [II-2 and II-4] were said to be “crawling on the floor” in their 50s. ... [III:10] because bedridden (tetraplegic and anarthric) at 72 and survived until 78 years. Lower limbs show marked hyperreflexia in most individuals with occasional involvement of the upper limbs. Patients display a spastic gait and have frequent falls. Babinski sign is usually present of indifferent. Less overt cerebellar signs with slightly affected rapid alternating movements and finger-to-nose tests. Sensory system is intact. No hearing or visual loss. No dementia reported in the family. Nerve conduction studies normal. Electroencephalogram did not show any epileptic discharges, but did show a diffuse slowing of electrical activity. Impotence, bladder incontinence, constipation or fecal incontinence, decreased sweating, and orthostatic hypotension. ... [IV:13] had severe episodic temperature dysregulation leading to drops in temperature to as low as 32 degC. Average age of death: 62 years. ... [IV:4] Brain MRI of IV:4 is representative of those seen in other family members – fluid-attenuated inversion recovery images show severe and confluent abnormalities of the white matter, even more pronounced in the posterior areas, and no significant cortical atrophy or ventriculomegaly. Spinal cord has consistently shown severe atrophy throughout.  ... Bladder/bowel disturbances, lower limb weakness, orthostatic hypotension, impotence, decreased sweating, temperature dysregulation, ataxia, MRI showing leukodystrophy, lower limb hyperreflexia with occasional upper limb involvement</t>
+  </si>
+  <si>
+    <t>Bladder symptoms, constipation, erectile dysfunction, pyramidal signs, Ataxia, MMT: 23, distal sensory loss clinically, NCS: Normal, MRI showing leukodystrophy, postural tremor, perkinsonism, Levodopa responsive. ... [PATIENT 1] Sex: M; Onset: 54 year; Autonomic symptoms: Bladder symptoms, constipation, erectile dysfunction; Pyramidal signs: +, Ataxia: +; Cognition: Normal; Neurophysiological studies: Distal sensory loss clinically; MRI showing leukodystrophy: +; Other symptoms/signs: Postural tremor; 4 patients were affected in the IL family over three generations. Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD. ... [PATIENT 2] Sex: M; Onset: 50 year; Autonomic symptoms: Bladder symptoms, constipation, erectile dusfunction; Pyramidal signs: +; Ataxia: +; Cognition: MMT: 23; Neurophysiological studies: NCS: normal; MRI showing leukodystrophy: +; Other symptoms/signs: Parkinsonism, levodopa responsive, no tremor; 4 patients were affected in the IL family over three generations. ... [SHARED FAMILY SYMPTOMS]Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD.</t>
+  </si>
+  <si>
+    <t>Bladder symptoms, postural hypotension, heat intolerance, fecal incontinnence, pyramidal signs, ataxia, MMT: 24, 26, NCS: Normal, MRI showing leukodystrophy. ... [PATIENT] Sex: Female; Onset: 53 year; Autonomic symptoms: Bladder symptoms, postural hypotension, heat intolerance; Pyramidal signs: +; Ataxia: +; Cognition: MMT: 24; Neurophysiological studies: NCS: normal; MRI showing leukodystrophy: +; 4 patients were affected in the DE family over two generations. Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD. ... [PATIENT 2] Sex: Female; Onset: 58 year; Autonomic symptoms: Bladder symptoms, fecal incontinence; Pyramidal signs: +; Ataxia: unknown; Cognition: MMT: 26; Neurophysiological studies: NCS: normal; MRI showing leukodystrophy: +; 4 patients were affected in the DE family over two generations. ... [SHARED PATIENT SYMPTOMS] Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD.</t>
+  </si>
+  <si>
+    <t>[F2-1] Sex: Male; Negative family history suggestive of LD; Comorbidities: osteoarthritis; No dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination showed difficulty walking attributed to osteoarthritis; No neurodegeneration suggestive of LD; No MRI evidence of LD; Father of F2-2, grandfather of F2-3. ... [F2-2] Sex: Female; Negative family history suggestive of LD; Comorbidities: depression, anxiety; Presence of dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination showed nystagmus, hyperreflexia and spasticity; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daugther of F2-1, mother of F2-3. ... [F2-3] Sex: Female; Negative family history suggestive of LD; Comorbidities: speech delay, learning difficulties, behavioral difficulties; Dysautonomic symptoms present; No documented orthostatic hypotension; Neurological examination showed lower limbs hyperreflexia with left plantar unresponsiveness; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daughter of F2-2, granddaughter of F2-1</t>
+  </si>
+  <si>
+    <t>Late urinary urgency, dysarthria, speech apraxia and dysphafia, MRI showing leukodystrophy, asymmetrical spastic weakness of upper and lower extremities, decreased dexterity upper limb spasticity, dyspnea likely from neuromuscular weakness, neurological defects reported to be worsened by environmental heat. ... [DEL3-1] Sex: Female; Age at symptom onset: 37; Ethnicity: Northern European/Native American; Affect: Depressed mood; Oral motor control and atriculation: Muffled voice, unilateral facial weakness, and drooling; Eye and extraocular movement examination: Normal dilated examination, Saccadic intrusion; Motor examination: Asymmetrical spastic weakness of upper and lower extremities; DTRs/plantar responses: Lower extremity clonus/extensor; Sensory examination: Normal; Autonomic nervous system: Normal by history and laboratory testing; EMG/NCV: Normal; Family history and inheritance patterns: Positive/autosomal dominant; Comorbidities: Neurologic deficity reported to be worsened by environmental heat. ... [DEL3-2] Sex: Female; Age at symptom onset: 34; Ethnicity: Northern European/Native American; Affect: Normal; Oral motor control and atriculation: Speech apraxia and dysphagia; Eye and extraocular movement examination: Optic disk pallor, limited up-gaze and sacadic intrusion; Motor examination: Asymmetrical (left &gt; right) spastic weakness of upper and lower extremities; DTRs/plantar responses: Brisk; Sensory examination: Normal; Autonomic nervous system: Normal by history; EMG/NCV: L peroneal entrapment neuropathy; Family history and inhertance patterns: Positive/autosomal dominant; Comorbidities: Dyspnea likely from neuromusclar weakness; L leg pain likely from peroneal neuropathy. ... [DEL3-3] Sex: Male; Age at symptom onset: 32; Ethnicity: Northern European/Native American; Affect: Pseudobulbar affect; Oral motor control and atriculation: Dysarthria; Eye and extraocular movement examination: Normal; Motor examination: Decreased dexterity upper limb spasticity and asymmetrical weakness of upper and lower limbs (right &gt; left); DTRs/plantar responses: Brisk/extensor; Sensory examination: Normal; Autonomic nervous system: Late urinary urgency; EMG/NCV: NA; Family history and inheritance patterns: Positive/autosomal dominant; Comorbidities: Neurological deficits resported to be worsened by environmental heat</t>
+  </si>
+  <si>
+    <t>[F1-1] Sex: Male; Negative family history suggestive of LD; Comorbidities: gout, diabetes, Parkinson, axonal sensorimotor polyneuropathy; Dysautonomic symptoms present; Orthostatic hypotension present; Neurological examination consistent with Parkinson and polyneuropathy; No neurodegeneration suggestive of LD; No MRI evidence of LD; Sibling of F1-2, father of F1-3, grandfather of F1-5. ... [F1-2] Sex: Male; Negative family history suggestive of LD; Comorbidities: hypothyroidism, sensorineural hearing loss, Meniere, posterior vitreous detachment, hypertension, essential tremor, mild cognitive impairment, irritable bowel syndrome; Negative for dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination showed slightly unsteady gait and the inability to perform the tandem gait; No neurodegeneration suggestive of LD; No MRI evidence of LD; Sibling to F1-1, father of F1-4. ... [F1-3] Sex: Female; Negative for family history suggestive of LD; Comorbidities: asthma, irritable bowel syndrome, migraines, goiter, erythema nodosum, chronic pain, carpal tunnel syndrome; Dysautonomic symptoms present; No documented orthostatic hypotension; Neurological examination showed slightly slow tongue movements, mild weakness in shoulder abduction, slightly slow fine finger movements and an absent right ankle jerk; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daughter of F1-1, Mother of F1-5. ... [F1-4] Sex: Male; Negative family history suggestive of LD; Comorbidities: hypothyroidism, depression, back pain; Dysautonomic symptoms present; No documented orthostatic hypotension; Neurological examination showed brisk reflexes, 3-5 beats of clonus, down going plantar, decreased sensation on the left L5-S1 distribution, slow and hesitant gait; No neurodegeneration suggestive of LD; No MRI evidence of LD; Son of F1-2. ... [F1-5] Sex: Male; Negative family history suggestive of LD; Comorbidities: failure to thrive, microcephaly, global developmental delay, autistic spectrum disorder, learning difficulties, mild dysmorphic facial features; No dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination normal; No neurodegeneration suggestive of LD; No MRI evidence of LD; Son of F1-3, grandson of F1-1</t>
+  </si>
+  <si>
+    <t>Urinary urgency and incontinence, ataxia, MRI showing leukodystrophy, slowly progressive spasticity of lower, Sex: Male, Age at symptom onset: 52, Ethnicity: Northern European, Affect: Chronic anxiety, Oral motor control and atriculation: Speech was normal, Eye and extraocular movement examination: Fine end-point nystagmus on lateral gaze, interrupted saccades, in vertical and horizontal planes, Motor examination: Tremor of lower extremities, spasticity, and cerebellar deficits, DTRs/plantar responses: Spastic in all limbs with lower limb clonus; positive Hoffman response, Sensory examination: Normal, Autonomic nervous system: late urinary urgency and incontinence, EMG/NCV: Normal, Family history and inheritance patterns: Positive/autosomal dominant, Comorbidities: Hypertension, GERD, and degenerative joint diseaselimbs, fine motor difficulty, fine end point nystagmus on left and right lateral gaze, leg cramps, snout reflex</t>
+  </si>
+  <si>
+    <t>[F3-1] Sex: Female; Negative family history suggestive of LD; No comorbidities; No dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination unremarkable; No neurodegeneration suggestive of LD; No MRI evidence of LD; Mother of F3-2. ... [F3-2] Sex: Female; Negative family history suggestive of LD; Comorbidities: chronic dysuria and UTIs, refractory depression, hypothyroidism, hyperlipidemia, panhypopituitarism, vitamin B12 deficiency, ankylosing spondylitis, fibromyalgia; Dysautonomic symptoms present; Documented orthostatic hypotension present; Neurological examination showed gait disturbance; Mild hyperreflexia; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daughter of F3-1</t>
+  </si>
+  <si>
+    <t>[DEL1-1] Sex: Male; Age at symptom onset: 34; Ethnicity: East Asian; Affect: Normal; Oral motor control and atriculation: Soft "breathy" and halting voice and dysphagia; Eye and extraocular movement examination: normal; Motor examination: Head and hand tremor (asymmetrical), incoordination and spastic and ataxic gait, and weakness of lower extremeties; DTRs/plantar responses: Brisk with clonus/extensor; Sensory examination: Normal; Autonomic nervous system: Early orthostatic intolerance and urinary urgency; EMG/NCV: NA; Family history and inheritance patterns: Negative; Comorbidities: Migraines, gout, and dyslipidemia. ... [PEDIGREE] IV-Patient 5: Sex: Female; Postive family history; 43 yo age of onset; Negative autonomic disturbance; Postive for pyramidal signs; Positive for ataxia; Cognitive impairment +MMSE 9. ... [PEDIGREE IV-PATIENT 6] Sex: Male; Positive family history; 34 yo age of onset; Negative autonomic disturbance; Postive for pyramidal signs; Positive for ataxia; Cognitive impairment +MoCA 10</t>
+  </si>
+  <si>
+    <t>Urinary urgency, ejaculatory failure, orthostatic intolerance, selective noradreneric failure, isolated cardiovascular sympathetic impairment, pyramidal signs, ataxia, MRI showing leukodystrophy. ... Cardiovascular reflexes and pharmacological assessment indicated a selective sympathetic failure, sparing cardiovagal function. Microneurography revealed absent sympathetic activity. The evaluation of autonomic innervation of skin annexes showed severely depleted and morphologically abnormal noradrenergic dopamine-β-hydroxylase (DβH) immunoreactive fibres with preserved cholinergic vasoactive intestinal polypeptide (VIP) immunoreactive fibres. ... [IV11] Sex: Female; Sibling to IV11 and IV12; Age of onset 50; Clinical signs at first evaluation at age 53 - autonomic symptoms: bowel/bladder dysfunction, OH, cerebellar signs: ataxia; pyramidal signs: brisk tendon reflexes; psuedobulbar signs absent; detailed clinical progression listed in paper. ... [IV10] Sex: Male; Sibling to IV10 and IV12; Age of onset 48; clinical signs at first evaluation at age 50 - autonomic symptoms: bowel/bladder dysfunction, impotence, OH; cerebellar signs: nystagmus, dysmetria, ataxia; pyramidal signs: brisk tendon reflexes, pseudobulbar signs absent; detailed clinical progression listed in paper. ... [IV12] Sex: Male; Sibling to IV10 and IV11; age at onset: 42; clinical signs at first evaluation at 44 years old - autonomic symptoms: bladder dysfunction, impotence, OH; cerebellar signs: action tremor, ataxia; pyramidal signs: brisk tendon reflexes, pseudobulbar signs absent; detailed clinical progression listed in paper</t>
+  </si>
+  <si>
+    <t>[PROBAND II-4] Sex: Female; Difficulty using her hands with involuntary movement, gait imbalance, urinary incontinence, constipation, speech slowly and mild inarticulate speech; Neurological - postural tremor of all extremities, increasing frequency and intensity of involuntary movement when keeping arms flat or when in a standing posture, slightly increased muscle tone and mild spasticity in the lower limbs, MMSE normal, MRI showed diffuse and symmetrical T2-hyperintense lesions in WM with less affected perventricular rims, mild withering of the cerebellum, brain stem, cerebrum, and difuse spinal cord atrophy; Family history - father and elder sister had similar gait impairment at least 10 years before heath and brother had several years' history of autonomic symptoms and gait disturbance and nephew has diffiulty walking</t>
+  </si>
+  <si>
+    <t>[PEDIGREE I - PATIENT 1] Sex: Female; Negative family history; 44 yo age of onset; + autonomic disturbance; + pyramidal signs; + Ataxia; Cognitive impairment +MMSE23; MRI findings with MCP lesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[PEDIGREE II - PATIENT 2] Sex: Male; + family history; 55 yo age of onset, 57 age at examination; + autonomic disturbance, + pyramidal signs, + ataxia; Cognitive impairment +MoCA 21. ... [PEDIGREE II - PATIENT 3] Sex: Male; + family history; 52 yo age of onset; + autonomic disturbance; + pyramidal signs; + ataxia; Cognitive impairment +MMSE15 </t>
   </si>
 </sst>
 </file>
@@ -785,7 +776,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1888,7 +1879,7 @@
         <v>59651</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1950,7 +1941,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B42" s="2">
         <v>5</v>
@@ -1999,7 +1990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -2010,7 +2001,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2027,7 +2018,7 @@
         <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2044,7 +2035,7 @@
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2086,7 +2077,7 @@
         <v>42</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2114,7 +2105,7 @@
         <v>61</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2131,7 +2122,7 @@
         <v>63</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2185,7 +2176,7 @@
         <v>76</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2202,7 +2193,7 @@
         <v>179</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2224,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2254,7 +2245,7 @@
         <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2265,7 +2256,7 @@
         <v>96</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2273,10 +2264,10 @@
         <v>98</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2284,7 +2275,7 @@
         <v>105</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2293,7 +2284,7 @@
         <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2322,16 +2313,16 @@
         <v>110</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="E29" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2421,7 +2412,7 @@
         <v>133</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C38" s="2">
         <v>2</v>
@@ -2430,7 +2421,7 @@
         <v>58</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2455,10 +2446,10 @@
         <v>44</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>176</v>
       </c>
@@ -2469,15 +2460,15 @@
         <v>6</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>205</v>
+        <v>181</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>177</v>
@@ -2486,10 +2477,10 @@
         <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -2715,7 +2706,7 @@
         <v>83</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>84</v>
@@ -2751,7 +2742,7 @@
         <v>83</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>84</v>
@@ -2818,7 +2809,7 @@
         <v>83</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>84</v>
@@ -2879,13 +2870,13 @@
         <v>122</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2913,7 +2904,7 @@
         <v>125</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>126</v>
@@ -2996,10 +2987,10 @@
         <v>147</v>
       </c>
       <c r="C38" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>147</v>
@@ -3024,7 +3015,7 @@
         <v>153</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3038,12 +3029,12 @@
         <v>153</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>152</v>
@@ -3052,7 +3043,7 @@
         <v>153</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16B7447-1DC4-4810-A71F-79D9D70DB06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C72D020-47C9-4E62-9997-0FF7B23BA7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Molecular" sheetId="4" r:id="rId1"/>
-    <sheet name="Clinical" sheetId="1" r:id="rId2"/>
-    <sheet name="Publication" sheetId="5" r:id="rId3"/>
+    <sheet name="Evidence" sheetId="6" r:id="rId2"/>
+    <sheet name="Clinical" sheetId="1" r:id="rId3"/>
+    <sheet name="Publication" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="225">
   <si>
     <t>Item name</t>
   </si>
@@ -100,9 +101,6 @@
     <t>10.1002/humu.22348, 10.1007/s10048-010-0269-y</t>
   </si>
   <si>
-    <t>Giorgio 2013, Meijer 2001</t>
-  </si>
-  <si>
     <t>10.1001/archneur.65.11.1496</t>
   </si>
   <si>
@@ -265,9 +263,6 @@
     <t>ADLD_dup_14</t>
   </si>
   <si>
-    <t>LN_dup_1</t>
-  </si>
-  <si>
     <t>Portugal</t>
   </si>
   <si>
@@ -283,12 +278,6 @@
     <t>10.1212/NXG.0000000000000305</t>
   </si>
   <si>
-    <t>LN_dup_2</t>
-  </si>
-  <si>
-    <t>LN_dup_3</t>
-  </si>
-  <si>
     <t>Nmezi et al. 2025</t>
   </si>
   <si>
@@ -298,9 +287,6 @@
     <t>Britain, England</t>
   </si>
   <si>
-    <t>LN_dup_4</t>
-  </si>
-  <si>
     <t>ADLD_del_2</t>
   </si>
   <si>
@@ -334,9 +320,6 @@
     <t>BR1</t>
   </si>
   <si>
-    <t>LN_dup_5</t>
-  </si>
-  <si>
     <t>10.1212/NXG.0000000000200261</t>
   </si>
   <si>
@@ -358,9 +341,6 @@
     <t>ADLD_del_4</t>
   </si>
   <si>
-    <t>LN_dup_6</t>
-  </si>
-  <si>
     <t>Microhomology of "GC"</t>
   </si>
   <si>
@@ -695,6 +675,45 @@
   </si>
   <si>
     <t xml:space="preserve">[PEDIGREE II - PATIENT 2] Sex: Male; + family history; 55 yo age of onset, 57 age at examination; + autonomic disturbance, + pyramidal signs, + ataxia; Cognitive impairment +MoCA 21. ... [PEDIGREE II - PATIENT 3] Sex: Male; + family history; 52 yo age of onset; + autonomic disturbance; + pyramidal signs; + ataxia; Cognitive impairment +MMSE15 </t>
+  </si>
+  <si>
+    <t>Giorgio 2013, Schuster 2011, Meijer 2008</t>
+  </si>
+  <si>
+    <t>10.1002/humu.22348, 10.1007/s10048-010-0269-y, 10.1001/archneur.65.11.1496</t>
+  </si>
+  <si>
+    <t>NonADLD_dup_1</t>
+  </si>
+  <si>
+    <t>NonADLD_dup_2</t>
+  </si>
+  <si>
+    <t>NonADLD_dup_3</t>
+  </si>
+  <si>
+    <t>NonADLD_dup_4</t>
+  </si>
+  <si>
+    <t>NonADLD_dup_5</t>
+  </si>
+  <si>
+    <t>NonADLD_dup_6</t>
+  </si>
+  <si>
+    <t>Publications</t>
+  </si>
+  <si>
+    <t>Literature case labels</t>
+  </si>
+  <si>
+    <t>Multigenerational families</t>
+  </si>
+  <si>
+    <t>Estimated unique affected individuals</t>
+  </si>
+  <si>
+    <t>Deduplication status</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1081,7 @@
   <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -1119,7 +1138,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2">
         <v>5</v>
@@ -1137,12 +1156,12 @@
         <v>16</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2">
         <v>5</v>
@@ -1160,12 +1179,12 @@
         <v>16</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2">
         <v>5</v>
@@ -1183,12 +1202,12 @@
         <v>16</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -1206,12 +1225,12 @@
         <v>16</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2">
         <v>5</v>
@@ -1226,15 +1245,15 @@
         <v>169456</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
@@ -1249,15 +1268,15 @@
         <v>340785</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
@@ -1275,12 +1294,12 @@
         <v>16</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2">
         <v>5</v>
@@ -1298,12 +1317,12 @@
         <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2">
         <v>5</v>
@@ -1321,12 +1340,12 @@
         <v>16</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2">
         <v>5</v>
@@ -1343,7 +1362,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B13" s="2">
         <v>5</v>
@@ -1361,12 +1380,12 @@
         <v>16</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2">
         <v>5</v>
@@ -1384,12 +1403,12 @@
         <v>16</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2">
         <v>5</v>
@@ -1406,7 +1425,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>75</v>
+        <v>214</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
@@ -1424,12 +1443,12 @@
         <v>16</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B17" s="2">
         <v>5</v>
@@ -1444,15 +1463,15 @@
         <v>672515</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -1467,12 +1486,12 @@
         <v>4365976</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1487,12 +1506,12 @@
         <v>4366000</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>86</v>
+        <v>217</v>
       </c>
       <c r="B20" s="2">
         <v>5</v>
@@ -1509,7 +1528,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2">
         <v>5</v>
@@ -1526,7 +1545,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2">
         <v>5</v>
@@ -1541,15 +1560,15 @@
         <v>608833</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2">
         <v>5</v>
@@ -1564,15 +1583,15 @@
         <v>474998</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>98</v>
+        <v>218</v>
       </c>
       <c r="B24" s="2">
         <v>5</v>
@@ -1589,7 +1608,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B25" s="2">
         <v>5</v>
@@ -1604,15 +1623,15 @@
         <v>250000</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="B26" s="2">
         <v>5</v>
@@ -1627,12 +1646,12 @@
         <v>275347</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B27" s="2">
         <v>5</v>
@@ -1650,12 +1669,12 @@
         <v>16</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B28" s="2">
         <v>5</v>
@@ -1673,12 +1692,12 @@
         <v>16</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B29" s="2">
         <v>5</v>
@@ -1696,12 +1715,12 @@
         <v>16</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B30" s="2">
         <v>5</v>
@@ -1719,12 +1738,12 @@
         <v>16</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B31" s="2">
         <v>5</v>
@@ -1742,12 +1761,12 @@
         <v>16</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B32" s="2">
         <v>5</v>
@@ -1765,12 +1784,12 @@
         <v>16</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B33" s="2">
         <v>5</v>
@@ -1788,12 +1807,12 @@
         <v>16</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B34" s="2">
         <v>5</v>
@@ -1810,7 +1829,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B35" s="2">
         <v>5</v>
@@ -1827,7 +1846,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B36" s="2">
         <v>5</v>
@@ -1842,12 +1861,12 @@
         <v>156734</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B37" s="2">
         <v>5</v>
@@ -1864,7 +1883,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B38" s="2">
         <v>5</v>
@@ -1879,12 +1898,12 @@
         <v>59651</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B39" s="2">
         <v>5</v>
@@ -1902,12 +1921,12 @@
         <v>16</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B40" s="2">
         <v>5</v>
@@ -1919,12 +1938,12 @@
         <v>126903760</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B41" s="2">
         <v>5</v>
@@ -1936,12 +1955,12 @@
         <v>126896451</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B42" s="2">
         <v>5</v>
@@ -1962,11 +1981,915 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93210A17-976E-449D-A8F5-248F94CB6DA5}">
+  <dimension ref="A1:G42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="104.85546875" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>126965629</v>
+      </c>
+      <c r="D2" s="2">
+        <v>126966115</v>
+      </c>
+      <c r="E2" s="2">
+        <v>277929</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>126736375</v>
+      </c>
+      <c r="D3" s="2">
+        <v>126939807</v>
+      </c>
+      <c r="E3" s="2">
+        <v>203432</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>126742343</v>
+      </c>
+      <c r="D4" s="2">
+        <v>126932074</v>
+      </c>
+      <c r="E4" s="2">
+        <v>189731</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
+        <v>126763901</v>
+      </c>
+      <c r="D5" s="2">
+        <v>126914184</v>
+      </c>
+      <c r="E5" s="2">
+        <v>150283</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="2">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>126683194</v>
+      </c>
+      <c r="D6" s="2">
+        <v>126922135</v>
+      </c>
+      <c r="E6" s="2">
+        <v>238941</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>126761184</v>
+      </c>
+      <c r="D7" s="2">
+        <v>126930640</v>
+      </c>
+      <c r="E7" s="2">
+        <v>169456</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>126667591</v>
+      </c>
+      <c r="D8" s="2">
+        <v>127008376</v>
+      </c>
+      <c r="E8" s="2">
+        <v>340785</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>126705616</v>
+      </c>
+      <c r="D9" s="2">
+        <v>126909458</v>
+      </c>
+      <c r="E9" s="2">
+        <v>203842</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="2">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>126686881</v>
+      </c>
+      <c r="D10" s="2">
+        <v>126915553</v>
+      </c>
+      <c r="E10" s="2">
+        <v>228672</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="2">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>126766751</v>
+      </c>
+      <c r="D11" s="2">
+        <v>126995994</v>
+      </c>
+      <c r="E11" s="2">
+        <v>229243</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="2">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>126687731</v>
+      </c>
+      <c r="D12" s="2">
+        <v>126965660</v>
+      </c>
+      <c r="E12" s="2">
+        <v>277929</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="2">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2">
+        <v>126775269</v>
+      </c>
+      <c r="D13" s="2">
+        <v>126893623</v>
+      </c>
+      <c r="E13" s="2">
+        <v>118354</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="2">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
+        <v>126716573</v>
+      </c>
+      <c r="D14" s="2">
+        <v>126926882</v>
+      </c>
+      <c r="E14" s="2">
+        <v>210309</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="2">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2">
+        <v>126743135</v>
+      </c>
+      <c r="D15" s="2">
+        <v>126865131</v>
+      </c>
+      <c r="E15" s="2">
+        <v>121996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" s="2">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
+        <v>125918128</v>
+      </c>
+      <c r="D16" s="2">
+        <v>126949480</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1031351</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="2">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>126016772</v>
+      </c>
+      <c r="D17" s="2">
+        <v>126689287</v>
+      </c>
+      <c r="E17" s="2">
+        <v>672515</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2">
+        <v>122477418</v>
+      </c>
+      <c r="D18" s="2">
+        <v>126843396</v>
+      </c>
+      <c r="E18" s="2">
+        <v>4365976</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B19" s="2">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2">
+        <v>122477254</v>
+      </c>
+      <c r="D19" s="2">
+        <v>126843256</v>
+      </c>
+      <c r="E19" s="2">
+        <v>4366000</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B20" s="2">
+        <v>5</v>
+      </c>
+      <c r="C20" s="2">
+        <v>122476520</v>
+      </c>
+      <c r="D20" s="2">
+        <v>126842588</v>
+      </c>
+      <c r="E20" s="2">
+        <v>4366065</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="2">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2">
+        <v>126050112</v>
+      </c>
+      <c r="D21" s="2">
+        <v>126707361</v>
+      </c>
+      <c r="E21" s="2">
+        <v>660000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="2">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2">
+        <v>126156719</v>
+      </c>
+      <c r="D22" s="2">
+        <v>126765604</v>
+      </c>
+      <c r="E22" s="2">
+        <v>608833</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="2">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2">
+        <v>126363827</v>
+      </c>
+      <c r="D23" s="2">
+        <v>126838825</v>
+      </c>
+      <c r="E23" s="2">
+        <v>474998</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B24" s="2">
+        <v>5</v>
+      </c>
+      <c r="C24" s="2">
+        <v>126512007</v>
+      </c>
+      <c r="D24" s="2">
+        <v>126978629</v>
+      </c>
+      <c r="E24" s="2">
+        <v>466623</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" s="2">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2">
+        <v>126522203</v>
+      </c>
+      <c r="D25" s="2">
+        <v>126772687</v>
+      </c>
+      <c r="E25" s="2">
+        <v>250000</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="2">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2">
+        <v>126637847</v>
+      </c>
+      <c r="D26" s="2">
+        <v>126913193</v>
+      </c>
+      <c r="E26" s="2">
+        <v>275347</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="2">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2">
+        <v>126695490</v>
+      </c>
+      <c r="D27" s="2">
+        <v>127036275</v>
+      </c>
+      <c r="E27" s="2">
+        <v>340785</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="2">
+        <v>5</v>
+      </c>
+      <c r="C28" s="2">
+        <v>126698430</v>
+      </c>
+      <c r="D28" s="2">
+        <v>126889630</v>
+      </c>
+      <c r="E28" s="2">
+        <v>191200</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="2">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2">
+        <v>126705102</v>
+      </c>
+      <c r="D29" s="2">
+        <v>127029777</v>
+      </c>
+      <c r="E29" s="2">
+        <v>324675</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="2">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2">
+        <v>126713540</v>
+      </c>
+      <c r="D30" s="2">
+        <v>126947560</v>
+      </c>
+      <c r="E30" s="2">
+        <v>234020</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" s="2">
+        <v>5</v>
+      </c>
+      <c r="C31" s="2">
+        <v>126718880</v>
+      </c>
+      <c r="D31" s="2">
+        <v>126866965</v>
+      </c>
+      <c r="E31" s="2">
+        <v>148085</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" s="2">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2">
+        <v>126732318</v>
+      </c>
+      <c r="D32" s="2">
+        <v>126886087</v>
+      </c>
+      <c r="E32" s="2">
+        <v>153769</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" s="2">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2">
+        <v>126736453</v>
+      </c>
+      <c r="D33" s="2">
+        <v>126864061</v>
+      </c>
+      <c r="E33" s="2">
+        <v>127608</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="2">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2">
+        <v>126739243</v>
+      </c>
+      <c r="D34" s="2">
+        <v>127054568</v>
+      </c>
+      <c r="E34" s="2">
+        <v>315000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B35" s="2">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2">
+        <v>126763765</v>
+      </c>
+      <c r="D35" s="2">
+        <v>126913191</v>
+      </c>
+      <c r="E35" s="2">
+        <v>275540</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" s="2">
+        <v>5</v>
+      </c>
+      <c r="C36" s="2">
+        <v>126766199</v>
+      </c>
+      <c r="D36" s="2">
+        <v>126922932</v>
+      </c>
+      <c r="E36" s="2">
+        <v>156734</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" s="2">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2">
+        <v>126762001</v>
+      </c>
+      <c r="D37" s="2">
+        <v>126997121</v>
+      </c>
+      <c r="E37" s="2">
+        <v>235000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="2">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2">
+        <v>126805047</v>
+      </c>
+      <c r="D38" s="2">
+        <v>126864688</v>
+      </c>
+      <c r="E38" s="2">
+        <v>59651</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="2">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2">
+        <v>126729432</v>
+      </c>
+      <c r="D39" s="2">
+        <v>126915116</v>
+      </c>
+      <c r="E39" s="2">
+        <v>184808</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B40" s="2">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2">
+        <v>126750808</v>
+      </c>
+      <c r="D40" s="2">
+        <v>126903760</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" s="2">
+        <v>5</v>
+      </c>
+      <c r="C41" s="2">
+        <v>126676886</v>
+      </c>
+      <c r="D41" s="2">
+        <v>126896451</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B42" s="2">
+        <v>5</v>
+      </c>
+      <c r="C42" s="2">
+        <v>126676469</v>
+      </c>
+      <c r="D42" s="2">
+        <v>126897351</v>
+      </c>
+      <c r="E42" s="2">
+        <v>221000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="21.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" style="2" customWidth="1"/>
@@ -2001,15 +2924,15 @@
         <v>16</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2">
         <v>31</v>
@@ -2018,15 +2941,15 @@
         <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -2035,197 +2958,197 @@
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>75</v>
+        <v>214</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2">
         <v>5</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>86</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C21" s="2">
         <v>32</v>
@@ -2233,10 +3156,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2245,37 +3168,37 @@
         <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>98</v>
+        <v>218</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2284,64 +3207,64 @@
         <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" s="2">
         <v>12</v>
@@ -2350,69 +3273,69 @@
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C32" s="2">
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C38" s="2">
         <v>2</v>
@@ -2421,23 +3344,23 @@
         <v>58</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C40" s="2">
         <v>6</v>
@@ -2446,41 +3369,41 @@
         <v>44</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C41" s="2">
         <v>6</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C42" s="2">
         <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -2488,12 +3411,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A753260-5018-4B3D-A2D6-F970E150F2D9}">
   <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="57.28515625" style="5" customWidth="1"/>
     <col min="3" max="3" width="105.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32.140625" style="2" customWidth="1"/>
@@ -2522,528 +3445,528 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>19</v>
+        <v>213</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>75</v>
+        <v>214</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>81</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>86</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>98</v>
+        <v>218</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2388684B-CA99-4C5B-AD67-D7724DF1017F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03D514F-A297-44FB-B3EA-CD2554FF70A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -701,9 +701,6 @@
     <t>NonADLD_dup_6</t>
   </si>
   <si>
-    <t>Summarry</t>
-  </si>
-  <si>
     <t>Testing 1</t>
   </si>
   <si>
@@ -825,6 +822,9 @@
   </si>
   <si>
     <t>Testing 41</t>
+  </si>
+  <si>
+    <t>Summary</t>
   </si>
 </sst>
 </file>
@@ -2106,12 +2106,12 @@
     <col min="2" max="2" width="95.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>220</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2119,7 +2119,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2127,7 +2127,7 @@
         <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2135,7 +2135,7 @@
         <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2143,7 +2143,7 @@
         <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2151,7 +2151,7 @@
         <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2159,7 +2159,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2167,7 +2167,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2175,7 +2175,7 @@
         <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2183,7 +2183,7 @@
         <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2191,7 +2191,7 @@
         <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2199,7 +2199,7 @@
         <v>69</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2207,7 +2207,7 @@
         <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
         <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2223,7 +2223,7 @@
         <v>73</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2231,7 +2231,7 @@
         <v>214</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2239,7 +2239,7 @@
         <v>75</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2247,7 +2247,7 @@
         <v>215</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2255,7 +2255,7 @@
         <v>216</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2263,7 +2263,7 @@
         <v>217</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2271,7 +2271,7 @@
         <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2279,7 +2279,7 @@
         <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2287,7 +2287,7 @@
         <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2295,7 +2295,7 @@
         <v>218</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2303,7 +2303,7 @@
         <v>99</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2311,7 +2311,7 @@
         <v>219</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2319,7 +2319,7 @@
         <v>120</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2327,7 +2327,7 @@
         <v>101</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -2335,7 +2335,7 @@
         <v>103</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2343,7 +2343,7 @@
         <v>105</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2351,7 +2351,7 @@
         <v>107</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -2359,7 +2359,7 @@
         <v>109</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2367,7 +2367,7 @@
         <v>121</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2375,7 +2375,7 @@
         <v>122</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -2383,7 +2383,7 @@
         <v>124</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -2391,7 +2391,7 @@
         <v>142</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2399,7 +2399,7 @@
         <v>125</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2407,7 +2407,7 @@
         <v>126</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2415,7 +2415,7 @@
         <v>143</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2423,7 +2423,7 @@
         <v>168</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2431,7 +2431,7 @@
         <v>169</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -2439,7 +2439,7 @@
         <v>193</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03D514F-A297-44FB-B3EA-CD2554FF70A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10F53F7-6FDF-43AB-8BE8-BC025BE52818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -710,9 +710,6 @@
     <t>Testing 3</t>
   </si>
   <si>
-    <t>Testing 4</t>
-  </si>
-  <si>
     <t>Testing 5</t>
   </si>
   <si>
@@ -825,6 +822,10 @@
   </si>
   <si>
     <t>Summary</t>
+  </si>
+  <si>
+    <t>Testing 4
+Testing for line break 4</t>
   </si>
 </sst>
 </file>
@@ -894,7 +895,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -913,6 +914,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2111,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2138,12 +2142,12 @@
         <v>222</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>223</v>
+      <c r="B5" s="7" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2151,7 +2155,7 @@
         <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2159,7 +2163,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2167,7 +2171,7 @@
         <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2175,7 +2179,7 @@
         <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2183,7 +2187,7 @@
         <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2191,7 +2195,7 @@
         <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2199,7 +2203,7 @@
         <v>69</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2207,7 +2211,7 @@
         <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2215,7 +2219,7 @@
         <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2223,7 +2227,7 @@
         <v>73</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2231,7 +2235,7 @@
         <v>214</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2239,7 +2243,7 @@
         <v>75</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2247,7 +2251,7 @@
         <v>215</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2255,7 +2259,7 @@
         <v>216</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2263,7 +2267,7 @@
         <v>217</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2271,7 +2275,7 @@
         <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2279,7 +2283,7 @@
         <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2287,7 +2291,7 @@
         <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2295,7 +2299,7 @@
         <v>218</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2303,7 +2307,7 @@
         <v>99</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2311,7 +2315,7 @@
         <v>219</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2319,7 +2323,7 @@
         <v>120</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2327,7 +2331,7 @@
         <v>101</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -2335,7 +2339,7 @@
         <v>103</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2343,7 +2347,7 @@
         <v>105</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2351,7 +2355,7 @@
         <v>107</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -2359,7 +2363,7 @@
         <v>109</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2367,7 +2371,7 @@
         <v>121</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2375,7 +2379,7 @@
         <v>122</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -2383,7 +2387,7 @@
         <v>124</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -2391,7 +2395,7 @@
         <v>142</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2399,7 +2403,7 @@
         <v>125</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2407,7 +2411,7 @@
         <v>126</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2415,7 +2419,7 @@
         <v>143</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2423,7 +2427,7 @@
         <v>168</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2431,7 +2435,7 @@
         <v>169</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -2439,7 +2443,7 @@
         <v>193</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10F53F7-6FDF-43AB-8BE8-BC025BE52818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291A3522-770D-4749-80B3-7132C0919991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Molecular" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="222">
   <si>
     <t>Item name</t>
   </si>
@@ -701,131 +701,15 @@
     <t>NonADLD_dup_6</t>
   </si>
   <si>
-    <t>Testing 1</t>
-  </si>
-  <si>
-    <t>Testing 2</t>
-  </si>
-  <si>
-    <t>Testing 3</t>
-  </si>
-  <si>
-    <t>Testing 5</t>
-  </si>
-  <si>
-    <t>Testing 6</t>
-  </si>
-  <si>
-    <t>Testing 7</t>
-  </si>
-  <si>
-    <t>Testing 8</t>
-  </si>
-  <si>
-    <t>Testing 9</t>
-  </si>
-  <si>
-    <t>Testing 10</t>
-  </si>
-  <si>
-    <t>Testing 11</t>
-  </si>
-  <si>
-    <t>Testing 12</t>
-  </si>
-  <si>
-    <t>Testing 13</t>
-  </si>
-  <si>
-    <t>Testing 14</t>
-  </si>
-  <si>
-    <t>Testing 15</t>
-  </si>
-  <si>
-    <t>Testing 16</t>
-  </si>
-  <si>
-    <t>Testing 17</t>
-  </si>
-  <si>
-    <t>Testing 18</t>
-  </si>
-  <si>
-    <t>Testing 19</t>
-  </si>
-  <si>
-    <t>Testing 20</t>
-  </si>
-  <si>
-    <t>Testing 21</t>
-  </si>
-  <si>
-    <t>Testing 22</t>
-  </si>
-  <si>
-    <t>Testing 23</t>
-  </si>
-  <si>
-    <t>Testing 24</t>
-  </si>
-  <si>
-    <t>Testing 25</t>
-  </si>
-  <si>
-    <t>Testing 26</t>
-  </si>
-  <si>
-    <t>Testing 27</t>
-  </si>
-  <si>
-    <t>Testing 28</t>
-  </si>
-  <si>
-    <t>Testing 29</t>
-  </si>
-  <si>
-    <t>Testing 30</t>
-  </si>
-  <si>
-    <t>Testing 31</t>
-  </si>
-  <si>
-    <t>Testing 32</t>
-  </si>
-  <si>
-    <t>Testing 33</t>
-  </si>
-  <si>
-    <t>Testing 34</t>
-  </si>
-  <si>
-    <t>Testing 35</t>
-  </si>
-  <si>
-    <t>Testing 36</t>
-  </si>
-  <si>
-    <t>Testing 37</t>
-  </si>
-  <si>
-    <t>Testing 38</t>
-  </si>
-  <si>
-    <t>Testing 39</t>
-  </si>
-  <si>
-    <t>Testing 40</t>
-  </si>
-  <si>
-    <t>Testing 41</t>
-  </si>
-  <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>Testing 4
-Testing for line break 4</t>
+    <t xml:space="preserve">publications
+literature case labels
+multigenerational family
+estimated unique individuals
+high-confidence linked individuals
+Deduplication status: </t>
   </si>
 </sst>
 </file>
@@ -2115,335 +1999,335 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>259</v>
+      <c r="B42" s="7" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291A3522-770D-4749-80B3-7132C0919991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7966FA85-E433-45E4-B445-5CA735165BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Molecular" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="224">
   <si>
     <t>Item name</t>
   </si>
@@ -62,27 +62,12 @@
     <t>Microhomology</t>
   </si>
   <si>
-    <t>Origin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Number of Individuals Affected </t>
   </si>
   <si>
     <t>Age of Onset (years)</t>
   </si>
   <si>
-    <t>Reported Symptoms</t>
-  </si>
-  <si>
-    <t>Pubmed link</t>
-  </si>
-  <si>
-    <t>Authors</t>
-  </si>
-  <si>
-    <t>AKA</t>
-  </si>
-  <si>
     <t>Pedigree</t>
   </si>
   <si>
@@ -675,9 +660,6 @@
   </si>
   <si>
     <t xml:space="preserve">[PEDIGREE II - PATIENT 2] Sex: Male; + family history; 55 yo age of onset, 57 age at examination; + autonomic disturbance, + pyramidal signs, + ataxia; Cognitive impairment +MoCA 21. ... [PEDIGREE II - PATIENT 3] Sex: Male; + family history; 52 yo age of onset; + autonomic disturbance; + pyramidal signs; + ataxia; Cognitive impairment +MMSE15 </t>
-  </si>
-  <si>
-    <t>Giorgio 2013, Schuster 2011, Meijer 2008</t>
   </si>
   <si>
     <t>10.1002/humu.22348, 10.1007/s10048-010-0269-y, 10.1001/archneur.65.11.1496</t>
@@ -710,6 +692,30 @@
 estimated unique individuals
 high-confidence linked individuals
 Deduplication status: </t>
+  </si>
+  <si>
+    <t>Country of origin</t>
+  </si>
+  <si>
+    <t>Commonly reported symptoms</t>
+  </si>
+  <si>
+    <t>Commonly reported imaging results</t>
+  </si>
+  <si>
+    <t>PMID</t>
+  </si>
+  <si>
+    <t>Publication</t>
+  </si>
+  <si>
+    <t>Cases reported</t>
+  </si>
+  <si>
+    <t>Giorgio 2013, Schuster 2011, Meijer 2008 *pedigree TEST</t>
+  </si>
+  <si>
+    <t>Giorgio 2013, Schuster 2011, Meijer 2008 TEST</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1126,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2">
         <v>5</v>
@@ -1135,15 +1141,15 @@
         <v>277929</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2">
         <v>5</v>
@@ -1158,15 +1164,15 @@
         <v>203432</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2">
         <v>5</v>
@@ -1181,15 +1187,15 @@
         <v>189731</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2">
         <v>5</v>
@@ -1204,15 +1210,15 @@
         <v>150283</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -1227,15 +1233,15 @@
         <v>238941</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2">
         <v>5</v>
@@ -1250,15 +1256,15 @@
         <v>169456</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
@@ -1273,15 +1279,15 @@
         <v>340785</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
@@ -1296,15 +1302,15 @@
         <v>203842</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2">
         <v>5</v>
@@ -1319,15 +1325,15 @@
         <v>228672</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2">
         <v>5</v>
@@ -1342,15 +1348,15 @@
         <v>229243</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2">
         <v>5</v>
@@ -1367,7 +1373,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2">
         <v>5</v>
@@ -1382,15 +1388,15 @@
         <v>118354</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2">
         <v>5</v>
@@ -1405,15 +1411,15 @@
         <v>210309</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B15" s="2">
         <v>5</v>
@@ -1430,7 +1436,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
@@ -1445,15 +1451,15 @@
         <v>1031351</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2">
         <v>5</v>
@@ -1468,15 +1474,15 @@
         <v>672515</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -1491,12 +1497,12 @@
         <v>4365976</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1511,12 +1517,12 @@
         <v>4366000</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B20" s="2">
         <v>5</v>
@@ -1533,7 +1539,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B21" s="2">
         <v>5</v>
@@ -1550,7 +1556,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B22" s="2">
         <v>5</v>
@@ -1565,15 +1571,15 @@
         <v>608833</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B23" s="2">
         <v>5</v>
@@ -1588,15 +1594,15 @@
         <v>474998</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B24" s="2">
         <v>5</v>
@@ -1613,7 +1619,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2">
         <v>5</v>
@@ -1628,15 +1634,15 @@
         <v>250000</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B26" s="2">
         <v>5</v>
@@ -1651,12 +1657,12 @@
         <v>275347</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B27" s="2">
         <v>5</v>
@@ -1671,15 +1677,15 @@
         <v>340785</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B28" s="2">
         <v>5</v>
@@ -1694,15 +1700,15 @@
         <v>191200</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B29" s="2">
         <v>5</v>
@@ -1717,15 +1723,15 @@
         <v>324675</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B30" s="2">
         <v>5</v>
@@ -1740,15 +1746,15 @@
         <v>234020</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B31" s="2">
         <v>5</v>
@@ -1763,15 +1769,15 @@
         <v>148085</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B32" s="2">
         <v>5</v>
@@ -1786,15 +1792,15 @@
         <v>153769</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B33" s="2">
         <v>5</v>
@@ -1809,15 +1815,15 @@
         <v>127608</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B34" s="2">
         <v>5</v>
@@ -1834,7 +1840,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B35" s="2">
         <v>5</v>
@@ -1851,7 +1857,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B36" s="2">
         <v>5</v>
@@ -1866,12 +1872,12 @@
         <v>156734</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B37" s="2">
         <v>5</v>
@@ -1888,7 +1894,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B38" s="2">
         <v>5</v>
@@ -1903,12 +1909,12 @@
         <v>59651</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B39" s="2">
         <v>5</v>
@@ -1923,15 +1929,15 @@
         <v>184808</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B40" s="2">
         <v>5</v>
@@ -1943,12 +1949,12 @@
         <v>126903760</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B41" s="2">
         <v>5</v>
@@ -1960,12 +1966,12 @@
         <v>126896451</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B42" s="2">
         <v>5</v>
@@ -1999,335 +2005,335 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -2338,7 +2344,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" style="2" customWidth="1"/>
@@ -2348,43 +2354,46 @@
     <col min="5" max="5" width="30.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2">
         <v>16</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2">
         <v>31</v>
@@ -2393,15 +2402,15 @@
         <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -2410,197 +2419,197 @@
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="E7" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C10" s="2">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C19" s="2">
         <v>5</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C21" s="2">
         <v>32</v>
@@ -2608,10 +2617,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2620,37 +2629,37 @@
         <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2659,64 +2668,64 @@
         <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2">
         <v>12</v>
@@ -2725,69 +2734,69 @@
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C32" s="2">
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C38" s="2">
         <v>2</v>
@@ -2796,23 +2805,23 @@
         <v>58</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C40" s="2">
         <v>6</v>
@@ -2821,41 +2830,41 @@
         <v>44</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C41" s="2">
         <v>6</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C42" s="2">
         <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2865,12 +2874,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A753260-5018-4B3D-A2D6-F970E150F2D9}">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="57.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="105.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="105.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.28515625" style="5" customWidth="1"/>
     <col min="4" max="4" width="32.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="39.140625" style="5" bestFit="1" customWidth="1"/>
   </cols>
@@ -2880,545 +2889,573 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>11</v>
+        <v>220</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>12</v>
+        <v>219</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>13</v>
+        <v>221</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>25</v>
+        <v>223</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>26</v>
+        <v>207</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>42</v>
+        <v>223</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>43</v>
+        <v>207</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>22</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>52</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>70</v>
+        <v>53</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>215</v>
+        <v>208</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>216</v>
+        <v>70</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>166</v>
+        <v>74</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>85</v>
+        <v>173</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>167</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>87</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>49</v>
+        <v>161</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>94</v>
+        <v>75</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>101</v>
+        <v>213</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>185</v>
+        <v>109</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>186</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>136</v>
+        <v>186</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>137</v>
+        <v>128</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>94</v>
+        <v>127</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>142</v>
+        <v>117</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>132</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>194</v>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7966FA85-E433-45E4-B445-5CA735165BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4714D92F-4B78-40C2-AED9-46CFA1B8DF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Molecular" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="302">
   <si>
     <t>Item name</t>
   </si>
@@ -134,15 +134,9 @@
     <t>India</t>
   </si>
   <si>
-    <t>Ataxia</t>
-  </si>
-  <si>
     <t>USA</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>USA, Irish-American</t>
   </si>
   <si>
@@ -509,18 +503,6 @@
     <t>Microhomology of "AA"</t>
   </si>
   <si>
-    <t>Autonomic symptoms present, ataxia, MRI showing leukodystrophy, hyperflexia</t>
-  </si>
-  <si>
-    <t>Micturition problems with imperative strangury , pyramidal signs, ataxia, below average results regarding verbal fluency and flexibility, verbal recall, working memory, executive functiions, and general working velocity, MRI showing leukodystrophy, symmetrical appendicular ataxia, mild spastic paraparesis, brisk deep tendon reflexes, and bilaterally positive Babinski signs</t>
-  </si>
-  <si>
-    <t>Urinary retention, fecal incontinence, impotence, pyramidal signs, ataxia, deficit in frontal functions, dysphagia, dysarthria, MRI showing leukodystrophy, spastic crying and laughing, acute motor axonal neuropathy</t>
-  </si>
-  <si>
-    <t>Constipation, pyramidal signs, MRI showing leukodystrophy, hypertension, benign prostate hyperplasia, right shoulder and neck stiffness, intermittent facial paresthesia, insomnia, belching symptoms, muscle spasms, stiffness in movement, difficulty of relaxation of the anal sphincter, REM sleep disorder, brisk deep tendon reflexes and increased tone</t>
-  </si>
-  <si>
     <t>10.1212/NXG.0000000000000305, 10.1097/NEN.0000000000000008</t>
   </si>
   <si>
@@ -609,57 +591,6 @@
   </si>
   <si>
     <t>Pedigree III - Patient 4</t>
-  </si>
-  <si>
-    <t>Sex: Male; Onset: 45 year; Autonomic symptoms: Bladder symptoms, constipation, postural hypotension, erectile dysfunction; Pyramidal signs: +; Ataxia: +; Cognition: Normal; Neurophysiological studies: NCS: normal, SEP: normal; MRI showing leukodystrophy: +; Includes 31 affected family members; Bladder symptoms, constipation, postural hypotention, erectile dysfunction , pyramidal signs, Ataxia, NCS: Normal, SEP:Normal: , MRI showing leukodystrophy, normal cognition</t>
-  </si>
-  <si>
-    <t>Sex: Male; Positive family history suggestive of LD (mother and maternal grandmother with neurological regression around 30 years and death a few years later); Comorbidities: neurological sequelae from MVA at age 31; Dysautonomic symptoms present; Documented orthostatic hypotension present; Neurological examination showed spastic gait, dysdiadokokinesia on the left side, brisk deep tendon reflexes, clonus, Babinski, dysautonomia at age 33; Neurodegeneration suggestive of LD present: bed ridden, no sphincter control, gastronomy at age 39; Presence of MRI evidence of LD</t>
-  </si>
-  <si>
-    <t>Sex: Male; Onset: 43 year; Autonomic symptoms: Bladder symptoms, constipation, postural hypotension, dry skin; Pyramidal signs: +; Ataxia: +; Cognition: Normal; Neurophysiological studies: VEP: normal, NCS: normal; SEP: pathological; MRI showing leukodystrophy: +; Other symptoms/signs: Increased symptoms with infection; Includes 3 affected family members ... Bladder symptoms, constipation, postural hypotention, dry skin, pyramidal signs, Ataxia, VEP: Normal, NCS: Normal, SEP: Pathological , MRI showing leukodystrophy, increased symptoms with infection</t>
-  </si>
-  <si>
-    <t>20 individuals in this family were misdiagnosed as having chronic progressive MS.  Early autonomic dysfunction. CT/MRI scans illustrate a widespread symmetrical demyelination of the white matter, normal immunoglobulin levels in cerebrospinal fluid, no pathological indication of brain inflammation has been found. Five generations of the ADLD pedigree involved. Disease onset mean age: 40.5 +- 4.9 years, n = 16. The earliest symptoms usually involve abnormalities of the autonomic nervous system, such as bowel/bladder dysfunction, impotence, orthostatic hypotension and decreased sweating. These symptoms precede others by several years and are followed by loss of fine motor skills. Nerve conduction velocities performed on three affected individuals were normal. Spastic paralysis and posterior column dysfunction occur in 88% of these patients, and 81% exhibit Babinski signs. Exhibit cerebellar signs. For instance, nystagmus is present in 69% of the individuals, and all patients experience ataxia. ... Bowel/bladder dysfunction, impotence, orthostatic hypotention, decreased sweating, pyramidal signs, ataxia, MRI showing leukodystrophy, spastic paralysis, posterior column dysfunction, Babinski signs. ... [PATIENT] Ireland: 47-year-old man with 6-year history of autonomic dysfunction; Progressive fatigue, gait ataxia, falls, dysarthria, urinary frequency, and urinary urgency; Examination showed gait ataxia and bilateral past-pointing; Neurological signs progressed over time; MRI demonstrated widespread diffuse white-matter disease with interval radiologic progression on repeat imaging; Slowly progressive multisystem neurological dysfunction consistent with ADLD caused by LMNB1 duplication; First genetically confirmed Irish case reported. ... [1/58/F] Constipation for many years before neurologic symptoms. Fine motor difficulty starting in her 40s. Progressive gait difficulty, hand numbness, urinary frequency, and incontinence. Ataxia, spastic paraparesis, dysarthria, dysmetria, head titubation, hyperreflexia, sensory loss, orthostatic hypotension, confusion, lethargy, and mild dementia. Eventually wheelchair-bound and bedridden. CT/MRI showed severe diffuse symmetric white-matter disease, greatest in frontoparietal regions, with cerebellar involvement and ventricular enlargement. ...[2/50/F] 15-year progressive neurologic illness. Ataxia, weakness, sensory symptoms, urinary dysfunction, constipation, decreased sweating, orthostatic light-headedness, visual complaints, and hearing impairment. MRI showed severe diffuse cerebral white-matter abnormalities with ventricular enlargement. CT showed diffuse frontoparietal white-matter lucencies. ... [3/60/F] 7-year history of progressive ataxia and weakness. Urinary dysfunction, constipation, decreased sweating, visual complaints, and hearing impairment. MRI showed moderate diffuse cerebral white-matter disease with mild ventricular enlargement. CT showed mild frontoparietal-predominant white-matter changes. ... [4/53/M] 20-year progressive illness. Ataxia, weakness, sensory symptoms, urinary dysfunction, constipation, decreased sweating, orthostatic symptoms, hearing impairment, and impotence. MRI showed moderate cerebral white-matter abnormalities with cerebellar and brainstem involvement. CT showed mild frontoparietal white-matter disease. ... [5/56/M] 18-year progressive illness. Ataxia, weakness, sensory symptoms, urinary dysfunction, constipation, decreased sweating, orthostatic symptoms, visual complaints, and impotence. MRI showed severe diffuse cerebral white-matter abnormalities with cerebellar involvement and ventricular enlargement. CT showed diffuse centrum semiovale white-matter lucencies.</t>
-  </si>
-  <si>
-    <t>[SHARED FAMILY SYMPTOMS] Symptoms in this family usually presented early in their 5th decade of life and consisted of bladder and/or bowel disturbances, lower limb weakness, orthostatic hypotension, and/or impotence. Disease progresses slowly and sometimes seems to remit. ... [II-2 and II-4] were said to be “crawling on the floor” in their 50s. ... [III:10] because bedridden (tetraplegic and anarthric) at 72 and survived until 78 years. Lower limbs show marked hyperreflexia in most individuals with occasional involvement of the upper limbs. Patients display a spastic gait and have frequent falls. Babinski sign is usually present of indifferent. Less overt cerebellar signs with slightly affected rapid alternating movements and finger-to-nose tests. Sensory system is intact. No hearing or visual loss. No dementia reported in the family. Nerve conduction studies normal. Electroencephalogram did not show any epileptic discharges, but did show a diffuse slowing of electrical activity. Impotence, bladder incontinence, constipation or fecal incontinence, decreased sweating, and orthostatic hypotension. ... [IV:13] had severe episodic temperature dysregulation leading to drops in temperature to as low as 32 degC. Average age of death: 62 years. ... [IV:4] Brain MRI of IV:4 is representative of those seen in other family members – fluid-attenuated inversion recovery images show severe and confluent abnormalities of the white matter, even more pronounced in the posterior areas, and no significant cortical atrophy or ventriculomegaly. Spinal cord has consistently shown severe atrophy throughout.  ... Bladder/bowel disturbances, lower limb weakness, orthostatic hypotension, impotence, decreased sweating, temperature dysregulation, ataxia, MRI showing leukodystrophy, lower limb hyperreflexia with occasional upper limb involvement</t>
-  </si>
-  <si>
-    <t>Bladder symptoms, constipation, erectile dysfunction, pyramidal signs, Ataxia, MMT: 23, distal sensory loss clinically, NCS: Normal, MRI showing leukodystrophy, postural tremor, perkinsonism, Levodopa responsive. ... [PATIENT 1] Sex: M; Onset: 54 year; Autonomic symptoms: Bladder symptoms, constipation, erectile dysfunction; Pyramidal signs: +, Ataxia: +; Cognition: Normal; Neurophysiological studies: Distal sensory loss clinically; MRI showing leukodystrophy: +; Other symptoms/signs: Postural tremor; 4 patients were affected in the IL family over three generations. Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD. ... [PATIENT 2] Sex: M; Onset: 50 year; Autonomic symptoms: Bladder symptoms, constipation, erectile dusfunction; Pyramidal signs: +; Ataxia: +; Cognition: MMT: 23; Neurophysiological studies: NCS: normal; MRI showing leukodystrophy: +; Other symptoms/signs: Parkinsonism, levodopa responsive, no tremor; 4 patients were affected in the IL family over three generations. ... [SHARED FAMILY SYMPTOMS]Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD.</t>
-  </si>
-  <si>
-    <t>Bladder symptoms, postural hypotension, heat intolerance, fecal incontinnence, pyramidal signs, ataxia, MMT: 24, 26, NCS: Normal, MRI showing leukodystrophy. ... [PATIENT] Sex: Female; Onset: 53 year; Autonomic symptoms: Bladder symptoms, postural hypotension, heat intolerance; Pyramidal signs: +; Ataxia: +; Cognition: MMT: 24; Neurophysiological studies: NCS: normal; MRI showing leukodystrophy: +; 4 patients were affected in the DE family over two generations. Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD. ... [PATIENT 2] Sex: Female; Onset: 58 year; Autonomic symptoms: Bladder symptoms, fecal incontinence; Pyramidal signs: +; Ataxia: unknown; Cognition: MMT: 26; Neurophysiological studies: NCS: normal; MRI showing leukodystrophy: +; 4 patients were affected in the DE family over two generations. ... [SHARED PATIENT SYMPTOMS] Patients in the family had an onset in their 6th decade with autonomic symptoms, pyramidal signs, and had brain MRI signs characteristic of ADLD.</t>
-  </si>
-  <si>
-    <t>[F2-1] Sex: Male; Negative family history suggestive of LD; Comorbidities: osteoarthritis; No dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination showed difficulty walking attributed to osteoarthritis; No neurodegeneration suggestive of LD; No MRI evidence of LD; Father of F2-2, grandfather of F2-3. ... [F2-2] Sex: Female; Negative family history suggestive of LD; Comorbidities: depression, anxiety; Presence of dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination showed nystagmus, hyperreflexia and spasticity; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daugther of F2-1, mother of F2-3. ... [F2-3] Sex: Female; Negative family history suggestive of LD; Comorbidities: speech delay, learning difficulties, behavioral difficulties; Dysautonomic symptoms present; No documented orthostatic hypotension; Neurological examination showed lower limbs hyperreflexia with left plantar unresponsiveness; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daughter of F2-2, granddaughter of F2-1</t>
-  </si>
-  <si>
-    <t>Late urinary urgency, dysarthria, speech apraxia and dysphafia, MRI showing leukodystrophy, asymmetrical spastic weakness of upper and lower extremities, decreased dexterity upper limb spasticity, dyspnea likely from neuromuscular weakness, neurological defects reported to be worsened by environmental heat. ... [DEL3-1] Sex: Female; Age at symptom onset: 37; Ethnicity: Northern European/Native American; Affect: Depressed mood; Oral motor control and atriculation: Muffled voice, unilateral facial weakness, and drooling; Eye and extraocular movement examination: Normal dilated examination, Saccadic intrusion; Motor examination: Asymmetrical spastic weakness of upper and lower extremities; DTRs/plantar responses: Lower extremity clonus/extensor; Sensory examination: Normal; Autonomic nervous system: Normal by history and laboratory testing; EMG/NCV: Normal; Family history and inheritance patterns: Positive/autosomal dominant; Comorbidities: Neurologic deficity reported to be worsened by environmental heat. ... [DEL3-2] Sex: Female; Age at symptom onset: 34; Ethnicity: Northern European/Native American; Affect: Normal; Oral motor control and atriculation: Speech apraxia and dysphagia; Eye and extraocular movement examination: Optic disk pallor, limited up-gaze and sacadic intrusion; Motor examination: Asymmetrical (left &gt; right) spastic weakness of upper and lower extremities; DTRs/plantar responses: Brisk; Sensory examination: Normal; Autonomic nervous system: Normal by history; EMG/NCV: L peroneal entrapment neuropathy; Family history and inhertance patterns: Positive/autosomal dominant; Comorbidities: Dyspnea likely from neuromusclar weakness; L leg pain likely from peroneal neuropathy. ... [DEL3-3] Sex: Male; Age at symptom onset: 32; Ethnicity: Northern European/Native American; Affect: Pseudobulbar affect; Oral motor control and atriculation: Dysarthria; Eye and extraocular movement examination: Normal; Motor examination: Decreased dexterity upper limb spasticity and asymmetrical weakness of upper and lower limbs (right &gt; left); DTRs/plantar responses: Brisk/extensor; Sensory examination: Normal; Autonomic nervous system: Late urinary urgency; EMG/NCV: NA; Family history and inheritance patterns: Positive/autosomal dominant; Comorbidities: Neurological deficits resported to be worsened by environmental heat</t>
-  </si>
-  <si>
-    <t>[F1-1] Sex: Male; Negative family history suggestive of LD; Comorbidities: gout, diabetes, Parkinson, axonal sensorimotor polyneuropathy; Dysautonomic symptoms present; Orthostatic hypotension present; Neurological examination consistent with Parkinson and polyneuropathy; No neurodegeneration suggestive of LD; No MRI evidence of LD; Sibling of F1-2, father of F1-3, grandfather of F1-5. ... [F1-2] Sex: Male; Negative family history suggestive of LD; Comorbidities: hypothyroidism, sensorineural hearing loss, Meniere, posterior vitreous detachment, hypertension, essential tremor, mild cognitive impairment, irritable bowel syndrome; Negative for dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination showed slightly unsteady gait and the inability to perform the tandem gait; No neurodegeneration suggestive of LD; No MRI evidence of LD; Sibling to F1-1, father of F1-4. ... [F1-3] Sex: Female; Negative for family history suggestive of LD; Comorbidities: asthma, irritable bowel syndrome, migraines, goiter, erythema nodosum, chronic pain, carpal tunnel syndrome; Dysautonomic symptoms present; No documented orthostatic hypotension; Neurological examination showed slightly slow tongue movements, mild weakness in shoulder abduction, slightly slow fine finger movements and an absent right ankle jerk; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daughter of F1-1, Mother of F1-5. ... [F1-4] Sex: Male; Negative family history suggestive of LD; Comorbidities: hypothyroidism, depression, back pain; Dysautonomic symptoms present; No documented orthostatic hypotension; Neurological examination showed brisk reflexes, 3-5 beats of clonus, down going plantar, decreased sensation on the left L5-S1 distribution, slow and hesitant gait; No neurodegeneration suggestive of LD; No MRI evidence of LD; Son of F1-2. ... [F1-5] Sex: Male; Negative family history suggestive of LD; Comorbidities: failure to thrive, microcephaly, global developmental delay, autistic spectrum disorder, learning difficulties, mild dysmorphic facial features; No dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination normal; No neurodegeneration suggestive of LD; No MRI evidence of LD; Son of F1-3, grandson of F1-1</t>
-  </si>
-  <si>
-    <t>Urinary urgency and incontinence, ataxia, MRI showing leukodystrophy, slowly progressive spasticity of lower, Sex: Male, Age at symptom onset: 52, Ethnicity: Northern European, Affect: Chronic anxiety, Oral motor control and atriculation: Speech was normal, Eye and extraocular movement examination: Fine end-point nystagmus on lateral gaze, interrupted saccades, in vertical and horizontal planes, Motor examination: Tremor of lower extremities, spasticity, and cerebellar deficits, DTRs/plantar responses: Spastic in all limbs with lower limb clonus; positive Hoffman response, Sensory examination: Normal, Autonomic nervous system: late urinary urgency and incontinence, EMG/NCV: Normal, Family history and inheritance patterns: Positive/autosomal dominant, Comorbidities: Hypertension, GERD, and degenerative joint diseaselimbs, fine motor difficulty, fine end point nystagmus on left and right lateral gaze, leg cramps, snout reflex</t>
-  </si>
-  <si>
-    <t>[F3-1] Sex: Female; Negative family history suggestive of LD; No comorbidities; No dysautonomic symptoms; No documented orthostatic hypotension; Neurological examination unremarkable; No neurodegeneration suggestive of LD; No MRI evidence of LD; Mother of F3-2. ... [F3-2] Sex: Female; Negative family history suggestive of LD; Comorbidities: chronic dysuria and UTIs, refractory depression, hypothyroidism, hyperlipidemia, panhypopituitarism, vitamin B12 deficiency, ankylosing spondylitis, fibromyalgia; Dysautonomic symptoms present; Documented orthostatic hypotension present; Neurological examination showed gait disturbance; Mild hyperreflexia; No neurodegeneration suggestive of LD; No MRI evidence of LD; Daughter of F3-1</t>
-  </si>
-  <si>
-    <t>[DEL1-1] Sex: Male; Age at symptom onset: 34; Ethnicity: East Asian; Affect: Normal; Oral motor control and atriculation: Soft "breathy" and halting voice and dysphagia; Eye and extraocular movement examination: normal; Motor examination: Head and hand tremor (asymmetrical), incoordination and spastic and ataxic gait, and weakness of lower extremeties; DTRs/plantar responses: Brisk with clonus/extensor; Sensory examination: Normal; Autonomic nervous system: Early orthostatic intolerance and urinary urgency; EMG/NCV: NA; Family history and inheritance patterns: Negative; Comorbidities: Migraines, gout, and dyslipidemia. ... [PEDIGREE] IV-Patient 5: Sex: Female; Postive family history; 43 yo age of onset; Negative autonomic disturbance; Postive for pyramidal signs; Positive for ataxia; Cognitive impairment +MMSE 9. ... [PEDIGREE IV-PATIENT 6] Sex: Male; Positive family history; 34 yo age of onset; Negative autonomic disturbance; Postive for pyramidal signs; Positive for ataxia; Cognitive impairment +MoCA 10</t>
-  </si>
-  <si>
-    <t>Urinary urgency, ejaculatory failure, orthostatic intolerance, selective noradreneric failure, isolated cardiovascular sympathetic impairment, pyramidal signs, ataxia, MRI showing leukodystrophy. ... Cardiovascular reflexes and pharmacological assessment indicated a selective sympathetic failure, sparing cardiovagal function. Microneurography revealed absent sympathetic activity. The evaluation of autonomic innervation of skin annexes showed severely depleted and morphologically abnormal noradrenergic dopamine-β-hydroxylase (DβH) immunoreactive fibres with preserved cholinergic vasoactive intestinal polypeptide (VIP) immunoreactive fibres. ... [IV11] Sex: Female; Sibling to IV11 and IV12; Age of onset 50; Clinical signs at first evaluation at age 53 - autonomic symptoms: bowel/bladder dysfunction, OH, cerebellar signs: ataxia; pyramidal signs: brisk tendon reflexes; psuedobulbar signs absent; detailed clinical progression listed in paper. ... [IV10] Sex: Male; Sibling to IV10 and IV12; Age of onset 48; clinical signs at first evaluation at age 50 - autonomic symptoms: bowel/bladder dysfunction, impotence, OH; cerebellar signs: nystagmus, dysmetria, ataxia; pyramidal signs: brisk tendon reflexes, pseudobulbar signs absent; detailed clinical progression listed in paper. ... [IV12] Sex: Male; Sibling to IV10 and IV11; age at onset: 42; clinical signs at first evaluation at 44 years old - autonomic symptoms: bladder dysfunction, impotence, OH; cerebellar signs: action tremor, ataxia; pyramidal signs: brisk tendon reflexes, pseudobulbar signs absent; detailed clinical progression listed in paper</t>
-  </si>
-  <si>
-    <t>[PROBAND II-4] Sex: Female; Difficulty using her hands with involuntary movement, gait imbalance, urinary incontinence, constipation, speech slowly and mild inarticulate speech; Neurological - postural tremor of all extremities, increasing frequency and intensity of involuntary movement when keeping arms flat or when in a standing posture, slightly increased muscle tone and mild spasticity in the lower limbs, MMSE normal, MRI showed diffuse and symmetrical T2-hyperintense lesions in WM with less affected perventricular rims, mild withering of the cerebellum, brain stem, cerebrum, and difuse spinal cord atrophy; Family history - father and elder sister had similar gait impairment at least 10 years before heath and brother had several years' history of autonomic symptoms and gait disturbance and nephew has diffiulty walking</t>
-  </si>
-  <si>
-    <t>[PEDIGREE I - PATIENT 1] Sex: Female; Negative family history; 44 yo age of onset; + autonomic disturbance; + pyramidal signs; + Ataxia; Cognitive impairment +MMSE23; MRI findings with MCP lesion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[PEDIGREE II - PATIENT 2] Sex: Male; + family history; 55 yo age of onset, 57 age at examination; + autonomic disturbance, + pyramidal signs, + ataxia; Cognitive impairment +MoCA 21. ... [PEDIGREE II - PATIENT 3] Sex: Male; + family history; 52 yo age of onset; + autonomic disturbance; + pyramidal signs; + ataxia; Cognitive impairment +MMSE15 </t>
   </si>
   <si>
     <t>10.1002/humu.22348, 10.1007/s10048-010-0269-y, 10.1001/archneur.65.11.1496</t>
@@ -716,6 +647,311 @@
   </si>
   <si>
     <t>Giorgio 2013, Schuster 2011, Meijer 2008 TEST</t>
+  </si>
+  <si>
+    <t>[Symptomatic - specific symptoms not documented] [Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Sexual dysfunction] [Thermoregulatory dysfunction] [Pyramidal signs]</t>
+  </si>
+  <si>
+    <t>[Cerebral white matter abnormalities (MRI), possibly symmetric] [Cerebellar white matter lesions (MRI), possibly symmetric] [Spinal cord abnormalities (MRI)]</t>
+  </si>
+  <si>
+    <t>[Pyramidal signs] [Cerebellar signs] [Autonomic dysfunction] [Dysphagia] [Pyramidal signs] [Tremor] [Dysphagia] [Cognitive impairment] [Possible Thermoregulatory dysfunction] [Tremor] [Bladder/bowel dysfunction] [Sexual dysfunction]</t>
+  </si>
+  <si>
+    <t>[MRI finding - 16 / 23 +] [Cerebral white matter abnormalities (MRI)] [Cerebellar white matter lesions (MRI)] [Possible Cerebral white matter abnormalities (CT)] [Possible Cerebellar white matter lesions (CT)] [Spinal cord abnormalities (MRI)]</t>
+  </si>
+  <si>
+    <t>[Autonomic dysfunction] [Pyramidal signs] [Cerebellar signs]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+[MRI abnormality, Grade 5]</t>
+  </si>
+  <si>
+    <t>Giorgio2013_A4</t>
+  </si>
+  <si>
+    <t>[Symptomatic - specific symptoms not documented]</t>
+  </si>
+  <si>
+    <t>Giorgio2013_A5</t>
+  </si>
+  <si>
+    <t>[Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Thermoregulatory dysfunction] [Pyramidal signs] [Cerebellar signs] [Sexual dysfunction]</t>
+  </si>
+  <si>
+    <t>[Cerebral white matter abnormalities (MRI), symmetric] [Cerebellar white matter lesions (MRI), symmetric] [Cerebellar white matter lesions (MRI)]  [Spinal cord abnormalities (MRI)] [Cerebellar white matter lesions (CT), symmetric] [Cerebral white matter abnormalities (CT)] [Cerebellar white matter lesions (CT)] [Spinal cord abnormalities (CT)]</t>
+  </si>
+  <si>
+    <t>Giorgio2013_A8,AV1</t>
+  </si>
+  <si>
+    <t>Giorgio2013_A10</t>
+  </si>
+  <si>
+    <t>Giorgio2013_A11</t>
+  </si>
+  <si>
+    <t>Not reported / unknown.</t>
+  </si>
+  <si>
+    <t>Giorgio2013_A14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Pyramidal signs] [Cerebellar signs] [Dysarthria] [Autonomic dysfunction] [Bladder/bowel dysfunction] [Pseudobulbar affect]
+</t>
+  </si>
+  <si>
+    <t>[Abnormality reported on MRI, region not further specified]</t>
+  </si>
+  <si>
+    <t>[Pyramidal signs] [Dysarthria]</t>
+  </si>
+  <si>
+    <t>[No abnormality reported on MRI]</t>
+  </si>
+  <si>
+    <t>[Pyramidal signs] [Dysarthria] [Cognitive impairment] [Tremor] [Dysphagia] [Pseudobulbar affect]</t>
+  </si>
+  <si>
+    <t>[Possible Cerebral white matter abnormalities (MRI)] [Possible Cerebellar white matter lesions (MRI)] [Possible abnormality reported on CT, region not further specified]</t>
+  </si>
+  <si>
+    <t>[Autonomic dysfunction] [Bladder/bowel dysfunction] [Pyramidal signs] [Cerebellar signs] [Dysarthria]</t>
+  </si>
+  <si>
+    <t>[Pyramidal signs] [Cerebellar signs]</t>
+  </si>
+  <si>
+    <t>[Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Pyramidal signs] [Cerebellar signs] [Tremor] [Dysarthria] [Thermoregulatory dysfunction] [Cognitive impairment]</t>
+  </si>
+  <si>
+    <t>[Cerebral white matter abnormalities (MRI)] [Cerebellar white matter lesions (MRI)]</t>
+  </si>
+  <si>
+    <t>Wang2025_Proband</t>
+  </si>
+  <si>
+    <t>[Autonomic dysfunction] [Bladder/bowel dysfunction] [Pyramidal signs] [Dysphagia]</t>
+  </si>
+  <si>
+    <t>[Cerebral white matter abnormalities (MRI), possibly symmetric] [Cerebellar white matter lesions (MRI), possibly symmetric]</t>
+  </si>
+  <si>
+    <t>Padiath2006_K50069</t>
+  </si>
+  <si>
+    <t>[Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Sexual dysfunction] [Pyramidal signs] [Cerebellar signs] [Dysphagia] [Possible Pseudobulbar affect]</t>
+  </si>
+  <si>
+    <t>[Cerebellar white matter lesions (MRI)]</t>
+  </si>
+  <si>
+    <t>Giorgio2013_FR1,FR2</t>
+  </si>
+  <si>
+    <t>[Autonomic dysfunction] [Bladder/bowel dysfunction] [Pyramidal signs] [Cerebellar signs] [Pseudobulbar affect] [Cognitive impairment]</t>
+  </si>
+  <si>
+    <t>[Cerebral white matter abnormalities (MRI), symmetric] [Cerebellar white matter lesions (MRI)] [Spinal cord abnormalities (MRI)]</t>
+  </si>
+  <si>
+    <t>Giorgio2013_IT1</t>
+  </si>
+  <si>
+    <t>Giorgio2013_IT2</t>
+  </si>
+  <si>
+    <t>[Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Sexual dysfunction] [Thermoregulatory dysfunction] [Pyramidal signs] [Cerebellar signs]</t>
+  </si>
+  <si>
+    <t>[Cerebral white matter abnormalities (MRI)]</t>
+  </si>
+  <si>
+    <t>Columbaro2013_ADLD2</t>
+  </si>
+  <si>
+    <t>[Autonomic dysfunction] [Orthostatic hypotension] [Sexual dysfunction]</t>
+  </si>
+  <si>
+    <t>[Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Pyramidal signs] [Cerebellar signs] [Tremor] [Dysarthria]</t>
+  </si>
+  <si>
+    <t>[Cerebral white matter abnormalities (MRI), symmetric] [Cerebellar white matter lesions (MRI), symmetric] [Spinal cord abnormalities (MRI)]</t>
+  </si>
+  <si>
+    <t>Mezaki2018_PedigreeI_Patient1</t>
+  </si>
+  <si>
+    <t>[Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Thermoregulatory dysfunction] [Pyramidal signs] [Cerebellar signs] [Cognitive impairment]</t>
+  </si>
+  <si>
+    <t>Mezaki2018_PedigreeII_Patient2</t>
+  </si>
+  <si>
+    <t>[Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Pyramidal signs] [Cerebellar signs] [Cognitive impairment]</t>
+  </si>
+  <si>
+    <t>Mezaki2018_PedigreeIII_Patient4</t>
+  </si>
+  <si>
+    <t>[Pyramidal signs] [Cerebellar signs] [Cognitive impairment]</t>
+  </si>
+  <si>
+    <t>Marklund 2008</t>
+  </si>
+  <si>
+    <t>Nmezi 2025</t>
+  </si>
+  <si>
+    <t>Giorgio 2015</t>
+  </si>
+  <si>
+    <t>Padiath 2006</t>
+  </si>
+  <si>
+    <t>DosSantos 2012</t>
+  </si>
+  <si>
+    <t>Columbaro 2013</t>
+  </si>
+  <si>
+    <t>Zhang 2019</t>
+  </si>
+  <si>
+    <t>Mezaki 2018</t>
+  </si>
+  <si>
+    <t>Giorgio2013_A1</t>
+  </si>
+  <si>
+    <t>Meijer2008_IV1; _II3; _II4; _III10; _IV13; _IV4</t>
+  </si>
+  <si>
+    <t>Meijer_2008</t>
+  </si>
+  <si>
+    <t>Marklund2008_Cohort</t>
+  </si>
+  <si>
+    <t>Finnsson2015_Family1_23F; _22M; _20M; _19F; _18F; _17F; _16F; _15M; _14F; _13F; _12F; _11M; _10M; _8F; _7F; _5M; _4M; _3M; _2M; _1F</t>
+  </si>
+  <si>
+    <t>Giorgio2013_A2</t>
+  </si>
+  <si>
+    <t>Sundblom2009_1; Marklund2006</t>
+  </si>
+  <si>
+    <t>Alturkustani2013_Sundlom_7</t>
+  </si>
+  <si>
+    <t>Finnsson 2015</t>
+  </si>
+  <si>
+    <t>Sundblom 2009; Marklund 2006</t>
+  </si>
+  <si>
+    <t>Alturkustani 2013</t>
+  </si>
+  <si>
+    <t>Giorgio2013_A3</t>
+  </si>
+  <si>
+    <t>Finnsson2019_Family2_5; _6</t>
+  </si>
+  <si>
+    <t>Finnsson 2019</t>
+  </si>
+  <si>
+    <t>Giorgio2013_A6,A7,K2-3</t>
+  </si>
+  <si>
+    <t>Coffeen2000_K2685</t>
+  </si>
+  <si>
+    <t>Alturkustani2013_Eldridge_1</t>
+  </si>
+  <si>
+    <t>Padiath2006_K4233; Alturkustani2013_Coffeen_3</t>
+  </si>
+  <si>
+    <t>Schwankhaus1988_1/56/F_Son; _1/56/F; _2/50/F; _3/60/F; _4/53/M; _5/56/M</t>
+  </si>
+  <si>
+    <t>Coffeen 2000</t>
+  </si>
+  <si>
+    <t>Padiath 2006; Alturkustani 2013</t>
+  </si>
+  <si>
+    <t>Alturkustani 2013_Eldridge</t>
+  </si>
+  <si>
+    <t>Schwankhaus 1988</t>
+  </si>
+  <si>
+    <t>Nmezi2019_DEL3-1; Nmezi2019_DEL3-2; Nmezi2019_DEL3-3</t>
+  </si>
+  <si>
+    <t>Nmezi2025_F1-1; Nmezi2025_F1-2; Nmezi2025_F1-3; Nmezi2025_F1-4; Nmezi2025_F1-5</t>
+  </si>
+  <si>
+    <t>Giorgio2015_ADLD-1-TO</t>
+  </si>
+  <si>
+    <t>Bergui1997_Family1</t>
+  </si>
+  <si>
+    <t>Brussino2010_ADLD-1-TO</t>
+  </si>
+  <si>
+    <t>Nmezi2019_DEL2-1</t>
+  </si>
+  <si>
+    <t>Alturkustani2013</t>
+  </si>
+  <si>
+    <t>Bergui 1997</t>
+  </si>
+  <si>
+    <t>Brussino 2010</t>
+  </si>
+  <si>
+    <t>Nmezi2025_F3-1; Nmezi2025_F3-2</t>
+  </si>
+  <si>
+    <t>Giorgio2013_BR1</t>
+  </si>
+  <si>
+    <t>Nmezi2025_F4-1</t>
+  </si>
+  <si>
+    <t>Nmezi2019_DEL1-1</t>
+  </si>
+  <si>
+    <t>Mezaki2018_PedigreeIV_Patient5; Mezaki2018_PedigreeIV_Patient6</t>
+  </si>
+  <si>
+    <t>Giorgio2013_IT3</t>
+  </si>
+  <si>
+    <t>Terlizzi2016_IV11; Terlizzi2016_IV10; Terlizzi2016_IV12</t>
+  </si>
+  <si>
+    <t>Terlizzi 2016</t>
+  </si>
+  <si>
+    <t>DosSantos2012_Proband; _Sister</t>
+  </si>
+  <si>
+    <t>Giorgio2013_G1</t>
+  </si>
+  <si>
+    <t>Columbaro2013_ADLD1; Columbaro2013_ADLD3</t>
+  </si>
+  <si>
+    <t>Zhang2019_II4_Proband; Zhang2019_II5</t>
   </si>
 </sst>
 </file>
@@ -726,7 +962,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -763,6 +999,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -785,7 +1026,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -807,6 +1048,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1190,7 +1443,7 @@
         <v>11</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1213,7 +1466,7 @@
         <v>11</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1236,7 +1489,7 @@
         <v>11</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1264,7 +1517,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
@@ -1282,12 +1535,12 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
@@ -1305,12 +1558,12 @@
         <v>11</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2">
         <v>5</v>
@@ -1328,12 +1581,12 @@
         <v>11</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2">
         <v>5</v>
@@ -1351,12 +1604,12 @@
         <v>11</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B12" s="2">
         <v>5</v>
@@ -1373,7 +1626,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B13" s="2">
         <v>5</v>
@@ -1391,12 +1644,12 @@
         <v>11</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2">
         <v>5</v>
@@ -1414,12 +1667,12 @@
         <v>11</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2">
         <v>5</v>
@@ -1436,7 +1689,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
@@ -1454,12 +1707,12 @@
         <v>11</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B17" s="2">
         <v>5</v>
@@ -1474,15 +1727,15 @@
         <v>672515</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -1497,12 +1750,12 @@
         <v>4365976</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1517,12 +1770,12 @@
         <v>4366000</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="B20" s="2">
         <v>5</v>
@@ -1539,7 +1792,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B21" s="2">
         <v>5</v>
@@ -1556,7 +1809,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B22" s="2">
         <v>5</v>
@@ -1571,15 +1824,15 @@
         <v>608833</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B23" s="2">
         <v>5</v>
@@ -1594,15 +1847,15 @@
         <v>474998</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="B24" s="2">
         <v>5</v>
@@ -1619,7 +1872,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2">
         <v>5</v>
@@ -1634,15 +1887,15 @@
         <v>250000</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="B26" s="2">
         <v>5</v>
@@ -1657,12 +1910,12 @@
         <v>275347</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B27" s="2">
         <v>5</v>
@@ -1680,12 +1933,12 @@
         <v>11</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B28" s="2">
         <v>5</v>
@@ -1703,12 +1956,12 @@
         <v>11</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B29" s="2">
         <v>5</v>
@@ -1726,12 +1979,12 @@
         <v>11</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B30" s="2">
         <v>5</v>
@@ -1749,12 +2002,12 @@
         <v>11</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B31" s="2">
         <v>5</v>
@@ -1772,12 +2025,12 @@
         <v>11</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B32" s="2">
         <v>5</v>
@@ -1795,12 +2048,12 @@
         <v>11</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B33" s="2">
         <v>5</v>
@@ -1818,12 +2071,12 @@
         <v>11</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B34" s="2">
         <v>5</v>
@@ -1840,7 +2093,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B35" s="2">
         <v>5</v>
@@ -1857,7 +2110,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B36" s="2">
         <v>5</v>
@@ -1872,12 +2125,12 @@
         <v>156734</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B37" s="2">
         <v>5</v>
@@ -1894,7 +2147,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B38" s="2">
         <v>5</v>
@@ -1909,12 +2162,12 @@
         <v>59651</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B39" s="2">
         <v>5</v>
@@ -1932,12 +2185,12 @@
         <v>11</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B40" s="2">
         <v>5</v>
@@ -1949,12 +2202,12 @@
         <v>126903760</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B41" s="2">
         <v>5</v>
@@ -1966,12 +2219,12 @@
         <v>126896451</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B42" s="2">
         <v>5</v>
@@ -2005,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2013,7 +2266,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2021,7 +2274,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2029,7 +2282,7 @@
         <v>24</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2037,7 +2290,7 @@
         <v>25</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2045,7 +2298,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2053,287 +2306,287 @@
         <v>27</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2351,7 +2604,8 @@
     <col min="2" max="2" width="21.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="110.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="152.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
@@ -2359,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
@@ -2368,10 +2622,10 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2385,7 +2639,10 @@
         <v>16</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>194</v>
+        <v>201</v>
+      </c>
+      <c r="F2" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2402,7 +2659,10 @@
         <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>190</v>
+        <v>203</v>
+      </c>
+      <c r="F3" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2419,7 +2679,10 @@
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>192</v>
+        <v>205</v>
+      </c>
+      <c r="F4" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2433,7 +2696,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>31</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2441,10 +2704,10 @@
         <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>33</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2452,175 +2715,181 @@
         <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>193</v>
+        <v>210</v>
+      </c>
+      <c r="F7" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>33</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" s="2">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>196</v>
+        <v>208</v>
+      </c>
+      <c r="F10" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>33</v>
+        <v>208</v>
+      </c>
+      <c r="F11" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+      <c r="F17" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19" s="2">
         <v>5</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+      <c r="F19" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C21" s="2">
         <v>32</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E21" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F21" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2629,37 +2898,43 @@
         <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="F22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+      <c r="F24" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2668,64 +2943,73 @@
         <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+      <c r="F25" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F26" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="F29" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="B31" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C31" s="2">
         <v>12</v>
@@ -2734,69 +3018,75 @@
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+      <c r="F31" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C32" s="2">
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F34" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F37" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="B38" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C38" s="2">
         <v>2</v>
@@ -2805,23 +3095,26 @@
         <v>58</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+      <c r="F38" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C40" s="2">
         <v>6</v>
@@ -2830,41 +3123,50 @@
         <v>44</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+      <c r="F40" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C41" s="2">
         <v>6</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+      <c r="F41" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C42" s="2">
         <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>206</v>
+        <v>249</v>
+      </c>
+      <c r="F42" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -2874,13 +3176,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A753260-5018-4B3D-A2D6-F970E150F2D9}">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="105.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5703125" style="5" customWidth="1"/>
     <col min="3" max="3" width="57.28515625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="32.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="255.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.140625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2889,576 +3191,1459 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="2">
+        <v>23649844</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" s="2">
+        <v>19001169</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E3"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" s="2">
+        <v>16823806</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C5" s="2">
+        <v>26053668</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E5"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="2">
+        <v>23649844</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E6"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C7" s="2">
+        <v>18945794</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E7"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C8" s="2">
+        <v>24128683</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E8"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C9" s="2">
+        <v>26053668</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="2">
+        <v>23649844</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E10"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C11" s="2">
+        <v>30192380</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="E11"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2">
+        <v>23649844</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E12"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="8">
+        <v>23649844</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="E13"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="8">
+        <v>23649844</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="E14"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C15" s="8">
+        <v>19151023</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="E15"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="C16" s="8">
+        <v>24128683</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E16"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C17" s="8">
+        <v>8042923</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="E17"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C18" s="8">
+        <v>6472420</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="E18"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="2">
+        <v>23649844</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E19"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="8">
+        <v>23649844</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E20"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="10">
+        <v>23649844</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E21"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="10">
+        <v>23649844</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E22"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="6"/>
+      <c r="E23"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="6"/>
+      <c r="E24"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="6"/>
+      <c r="E25"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="6"/>
+      <c r="E26"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="6"/>
+      <c r="E27"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="2">
+        <v>30842973</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="E28"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="6"/>
+      <c r="E29"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>187</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C30" s="2">
+        <v>39910058</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="E30"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="6"/>
+      <c r="E31"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="C32" s="8">
+        <v>19961535</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="E32"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C33" s="8">
+        <v>9225322</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="E33"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C34" s="8">
+        <v>25701871</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="E34"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="8">
+        <v>24128683</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="E35"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="C36" s="8">
+        <v>30842973</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="E36"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="2">
+        <v>23649844</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E37"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C38" s="2">
+        <v>39910058</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="E38"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>189</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C39" s="2">
+        <v>39910058</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E39"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="8">
+        <v>30842973</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="E40"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C41" s="8">
+        <v>30697589</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E41"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>190</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="2">
+        <v>40343075</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="E42"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C43" s="8">
+        <v>16951681</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="E43"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="6"/>
+      <c r="E44"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" s="8">
+        <v>23649844</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E45"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C46" s="8">
+        <v>26896090</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="E46"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" s="10">
+        <v>23649844</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E47"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C48" s="8">
+        <v>21909802</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="E48"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49" s="8">
+        <v>23649844</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="E49"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="10">
+        <v>23649844</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E50"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" s="10">
+        <v>23649844</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="E51"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C52" s="8">
+        <v>23261988</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E52"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="6"/>
+      <c r="E53"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="6"/>
+      <c r="E54"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C55" s="2">
+        <v>23261988</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E55"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>119</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C56" s="8">
+        <v>31695592</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E56"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="6"/>
+      <c r="E57"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>157</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C58" s="8">
+        <v>30697589</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="E58"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>158</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C59" s="8">
+        <v>30697589</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E59"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>182</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C60" s="8">
+        <v>30697589</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E60"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E82" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B83" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B84" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B85" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C85" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E85" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B86" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C87" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="D87" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="5" t="s">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C93" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="D93" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="C105" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E109" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="2" t="s">
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="C111" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E34" s="5" t="s">
+      <c r="C117" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C36" s="5" t="s">
+      <c r="D119" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B39" s="5" t="s">
+      <c r="B120" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C120" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="D120" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B40" s="5" t="s">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="B124" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D124" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>189</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4714D92F-4B78-40C2-AED9-46CFA1B8DF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D46D060-F624-485D-94EE-A02F6AE57953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Molecular" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="227">
   <si>
     <t>Item name</t>
   </si>
@@ -83,15 +83,6 @@
     <t>Canada</t>
   </si>
   <si>
-    <t>10.1002/humu.22348, 10.1007/s10048-010-0269-y</t>
-  </si>
-  <si>
-    <t>10.1001/archneur.65.11.1496</t>
-  </si>
-  <si>
-    <t>A1, CA2</t>
-  </si>
-  <si>
     <t>ADLD_dup_2</t>
   </si>
   <si>
@@ -101,18 +92,6 @@
     <t>Sweden</t>
   </si>
   <si>
-    <t>10.1002/humu.22348, 10.1007/s10048-010-0269-y, PMC8133955, 10.3174/ajnr.A1354, 10.1002/ajmg.b.30342, 10.1002/ana.24452</t>
-  </si>
-  <si>
-    <t>Giorgio 2013, Schuster 2011, Melberg 2006, Sundbloom 2008, Marklund 2006, Finnsson 2015</t>
-  </si>
-  <si>
-    <t>SE1, A2</t>
-  </si>
-  <si>
-    <t>10.1007/s10048-010-0269-y</t>
-  </si>
-  <si>
     <t>ADLD_dup_3</t>
   </si>
   <si>
@@ -146,45 +125,9 @@
     <t>40.5 ± 4.9</t>
   </si>
   <si>
-    <t>10.1002/humu.22348, 10.1007/s10048-010-0269-y, PMC8133955, 10.3174/ajnr.A1354, 10.1002/ana.24452</t>
-  </si>
-  <si>
-    <t>Giorgio 2013, Schuster 2011, Melberg 2006, Sundbloom 2008, Finnsson 2015</t>
-  </si>
-  <si>
-    <t>SE2, A3</t>
-  </si>
-  <si>
-    <t>10.1002/humu.22348, 10.1002/mds.24064</t>
-  </si>
-  <si>
-    <t>Giorgio 2013, Fogel 2012</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>10.1002/humu.22348</t>
-  </si>
-  <si>
     <t>Giorgio 2013</t>
   </si>
   <si>
-    <t>A5</t>
-  </si>
-  <si>
-    <t>10.1002/humu.22348, 10.1038/ng1872, https://doi.org/10.1093/hmg/9.5.787</t>
-  </si>
-  <si>
-    <t>Giorgio 2013, Padiath 2006, Coffeen 2000</t>
-  </si>
-  <si>
-    <t>A6, A7, K2-3, K2685, K50069</t>
-  </si>
-  <si>
-    <t>10.1038/ng1872</t>
-  </si>
-  <si>
     <t>ADLD_dup_7</t>
   </si>
   <si>
@@ -209,21 +152,6 @@
     <t>53, 58</t>
   </si>
   <si>
-    <t>A8, AV1</t>
-  </si>
-  <si>
-    <t>Giorgio 2013, Schuster 2011</t>
-  </si>
-  <si>
-    <t>IL, A10</t>
-  </si>
-  <si>
-    <t>DE, A11</t>
-  </si>
-  <si>
-    <t>A14</t>
-  </si>
-  <si>
     <t>Microhomology of "GG"</t>
   </si>
   <si>
@@ -251,18 +179,6 @@
     <t>Nmezi 2019</t>
   </si>
   <si>
-    <t>DEL3-1, DEL3-2, DEL3-3</t>
-  </si>
-  <si>
-    <t>10.1212/NXG.0000000000000305</t>
-  </si>
-  <si>
-    <t>Nmezi et al. 2025</t>
-  </si>
-  <si>
-    <t>10.1038/s41467-025-56378-9</t>
-  </si>
-  <si>
     <t>Britain, England</t>
   </si>
   <si>
@@ -272,18 +188,6 @@
     <t>ADLD_del_3</t>
   </si>
   <si>
-    <t>Quattrocolo et al. 1997, Brussino et al. 2010, Giorgio et al. 2015, Giordana et al. 2005, Piccinini et al. 2009</t>
-  </si>
-  <si>
-    <t>ADLD-1-TO</t>
-  </si>
-  <si>
-    <t>Nmezi 2019, Alturkustani 2013</t>
-  </si>
-  <si>
-    <t>CA-Del; CA2; S4; 1_3; DEL2-1, AC-11-519(Deletion)</t>
-  </si>
-  <si>
     <t>ADLD_invdup_1</t>
   </si>
   <si>
@@ -296,27 +200,12 @@
     <t>Brazil</t>
   </si>
   <si>
-    <t>BR1</t>
-  </si>
-  <si>
-    <t>10.1212/NXG.0000000000200261</t>
-  </si>
-  <si>
     <t>Wang 2025</t>
   </si>
   <si>
     <t>Alujr centromeric repeat, AluSP telomeric repeat, no microhomology at junctions</t>
   </si>
   <si>
-    <t>10.1002/humu.22348, 10.1001/archneur.65.11.1496, https://doi.org/10.1212/NXG.0000000000000305, 10.1097/NEN.0000000000000008</t>
-  </si>
-  <si>
-    <t>Giorgio, et al. 2013, Meijer et al. 2008, Nmezi et al. 2019, Alturkustani et al. 2013</t>
-  </si>
-  <si>
-    <t>DEL1-1</t>
-  </si>
-  <si>
     <t>ADLD_del_4</t>
   </si>
   <si>
@@ -356,30 +245,6 @@
     <t>France</t>
   </si>
   <si>
-    <t>10.1038/ng1873, PMID: 8958750</t>
-  </si>
-  <si>
-    <t>Padiath 2006, Asahara 1996</t>
-  </si>
-  <si>
-    <t>K50069</t>
-  </si>
-  <si>
-    <t>10.1002/humu.22348, 10.1016/j.autneu.2010.07.011</t>
-  </si>
-  <si>
-    <t>FR1, FR2</t>
-  </si>
-  <si>
-    <t>10.1002/humu.22348, 10.1007/s00415-011-6225-4</t>
-  </si>
-  <si>
-    <t>Giorgio 2013, Dos Santos 2011</t>
-  </si>
-  <si>
-    <t>10.1007/s00415-011-6225-4</t>
-  </si>
-  <si>
     <t>ADLD_dup_15</t>
   </si>
   <si>
@@ -416,36 +281,6 @@
     <t>Uruguay</t>
   </si>
   <si>
-    <t>10.1002/humu.22348, 10.1111/j.1468-1331.2009.02536.x</t>
-  </si>
-  <si>
-    <t>Giorgio 2013, Brussino 2008</t>
-  </si>
-  <si>
-    <t>IT1</t>
-  </si>
-  <si>
-    <t>10.1111/j.1468-1331.2009.02536.x</t>
-  </si>
-  <si>
-    <t>IT2</t>
-  </si>
-  <si>
-    <t>10.1016/j.bbadis.2012.12.006 10.1093/hmg/ddv034</t>
-  </si>
-  <si>
-    <t>Columbaro et al. 2013, Barlotelli-Stella et al. 2015</t>
-  </si>
-  <si>
-    <t>ADLD2</t>
-  </si>
-  <si>
-    <t>10.3389/fnins.2019.01030</t>
-  </si>
-  <si>
-    <t>1_3</t>
-  </si>
-  <si>
     <t>ADLD_dup_24</t>
   </si>
   <si>
@@ -455,12 +290,6 @@
     <t>220 kb</t>
   </si>
   <si>
-    <t>10.1212/nxg.0000000000000292</t>
-  </si>
-  <si>
-    <t>Mezaki et al. 2018</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -503,15 +332,6 @@
     <t>Microhomology of "AA"</t>
   </si>
   <si>
-    <t>10.1212/NXG.0000000000000305, 10.1097/NEN.0000000000000008</t>
-  </si>
-  <si>
-    <t>10.1159/000117406, 10.1111/j.1468-1331.2009.02844.x, 10.1093/hmg/ddv065, 10.1111/j.1750-3639.2005.tb00506.x, 10.1111/j.1750-3639.2009.00313.x</t>
-  </si>
-  <si>
-    <t>10.1111/j.1468-1331.2009.02844.x, 10.1093/hmg/ddv065</t>
-  </si>
-  <si>
     <t>ADLD_dup_28</t>
   </si>
   <si>
@@ -533,24 +353,9 @@
     <t>55, 52, 50</t>
   </si>
   <si>
-    <t>Pedigree I - Patient I</t>
-  </si>
-  <si>
-    <t>Pedigree II - Patient 2, Pedigree II - Patient 3, Pedigree III - Patient 4</t>
-  </si>
-  <si>
-    <t>F2-1, F2-2, F2-3</t>
-  </si>
-  <si>
-    <t>F1, F1-1, F1-2, F1-3, F1-4, F1-5, GM B206</t>
-  </si>
-  <si>
     <t>Northern European</t>
   </si>
   <si>
-    <t>F3-1, F3-2</t>
-  </si>
-  <si>
     <t>Southern Italy</t>
   </si>
   <si>
@@ -560,40 +365,16 @@
     <t>48, 50, 48, 42</t>
   </si>
   <si>
-    <t>Giorgio 2013, Guaraldi 2011, Terlizzi et al. 2016</t>
-  </si>
-  <si>
-    <t>IT3, IV11, IV10, IV12</t>
-  </si>
-  <si>
-    <t>10.1038/ng1872, 10.1016/j.autneu/2016.02.005</t>
-  </si>
-  <si>
-    <t>Zhang et al. 2019</t>
-  </si>
-  <si>
-    <t>Proband II-4</t>
-  </si>
-  <si>
     <t>China</t>
   </si>
   <si>
     <t>Predicted junction</t>
   </si>
   <si>
-    <t>GR1</t>
-  </si>
-  <si>
     <t>Korea</t>
   </si>
   <si>
     <t>ADLD_dup_30</t>
-  </si>
-  <si>
-    <t>Pedigree III - Patient 4</t>
-  </si>
-  <si>
-    <t>10.1002/humu.22348, 10.1007/s10048-010-0269-y, 10.1001/archneur.65.11.1496</t>
   </si>
   <si>
     <t>NonADLD_dup_1</t>
@@ -643,12 +424,6 @@
     <t>Cases reported</t>
   </si>
   <si>
-    <t>Giorgio 2013, Schuster 2011, Meijer 2008 *pedigree TEST</t>
-  </si>
-  <si>
-    <t>Giorgio 2013, Schuster 2011, Meijer 2008 TEST</t>
-  </si>
-  <si>
     <t>[Symptomatic - specific symptoms not documented] [Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Sexual dysfunction] [Thermoregulatory dysfunction] [Pyramidal signs]</t>
   </si>
   <si>
@@ -828,9 +603,6 @@
     <t>Meijer2008_IV1; _II3; _II4; _III10; _IV13; _IV4</t>
   </si>
   <si>
-    <t>Meijer_2008</t>
-  </si>
-  <si>
     <t>Marklund2008_Cohort</t>
   </si>
   <si>
@@ -952,6 +724,9 @@
   </si>
   <si>
     <t>Zhang2019_II4_Proband; Zhang2019_II5</t>
+  </si>
+  <si>
+    <t>Meijer 2008</t>
   </si>
 </sst>
 </file>
@@ -1402,7 +1177,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2">
         <v>5</v>
@@ -1420,12 +1195,12 @@
         <v>11</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2">
         <v>5</v>
@@ -1443,12 +1218,12 @@
         <v>11</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2">
         <v>5</v>
@@ -1466,12 +1241,12 @@
         <v>11</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>145</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -1489,12 +1264,12 @@
         <v>11</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>144</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2">
         <v>5</v>
@@ -1509,15 +1284,15 @@
         <v>169456</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
@@ -1532,15 +1307,15 @@
         <v>340785</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
@@ -1558,12 +1333,12 @@
         <v>11</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2">
         <v>5</v>
@@ -1581,12 +1356,12 @@
         <v>11</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2">
         <v>5</v>
@@ -1604,12 +1379,12 @@
         <v>11</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2">
         <v>5</v>
@@ -1626,7 +1401,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2">
         <v>5</v>
@@ -1644,12 +1419,12 @@
         <v>11</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="B14" s="2">
         <v>5</v>
@@ -1667,12 +1442,12 @@
         <v>11</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2">
         <v>5</v>
@@ -1689,7 +1464,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
@@ -1707,12 +1482,12 @@
         <v>11</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B17" s="2">
         <v>5</v>
@@ -1727,15 +1502,15 @@
         <v>672515</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -1750,12 +1525,12 @@
         <v>4365976</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1770,12 +1545,12 @@
         <v>4366000</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
       <c r="B20" s="2">
         <v>5</v>
@@ -1792,7 +1567,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="B21" s="2">
         <v>5</v>
@@ -1809,7 +1584,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2">
         <v>5</v>
@@ -1824,15 +1599,15 @@
         <v>608833</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2">
         <v>5</v>
@@ -1847,15 +1622,15 @@
         <v>474998</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="B24" s="2">
         <v>5</v>
@@ -1872,7 +1647,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="B25" s="2">
         <v>5</v>
@@ -1887,15 +1662,15 @@
         <v>250000</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="B26" s="2">
         <v>5</v>
@@ -1910,12 +1685,12 @@
         <v>275347</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B27" s="2">
         <v>5</v>
@@ -1933,12 +1708,12 @@
         <v>11</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="B28" s="2">
         <v>5</v>
@@ -1956,12 +1731,12 @@
         <v>11</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="B29" s="2">
         <v>5</v>
@@ -1979,12 +1754,12 @@
         <v>11</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="B30" s="2">
         <v>5</v>
@@ -2002,12 +1777,12 @@
         <v>11</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="B31" s="2">
         <v>5</v>
@@ -2025,12 +1800,12 @@
         <v>11</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="B32" s="2">
         <v>5</v>
@@ -2048,12 +1823,12 @@
         <v>11</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="B33" s="2">
         <v>5</v>
@@ -2071,12 +1846,12 @@
         <v>11</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="B34" s="2">
         <v>5</v>
@@ -2093,7 +1868,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="B35" s="2">
         <v>5</v>
@@ -2110,7 +1885,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="B36" s="2">
         <v>5</v>
@@ -2125,12 +1900,12 @@
         <v>156734</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="B37" s="2">
         <v>5</v>
@@ -2147,7 +1922,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="B38" s="2">
         <v>5</v>
@@ -2162,12 +1937,12 @@
         <v>59651</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="B39" s="2">
         <v>5</v>
@@ -2185,12 +1960,12 @@
         <v>11</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="B40" s="2">
         <v>5</v>
@@ -2202,12 +1977,12 @@
         <v>126903760</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>137</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="B41" s="2">
         <v>5</v>
@@ -2219,12 +1994,12 @@
         <v>126896451</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>137</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="B42" s="2">
         <v>5</v>
@@ -2258,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2266,327 +2041,327 @@
         <v>10</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2613,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
@@ -2622,10 +2397,10 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2639,18 +2414,18 @@
         <v>16</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="F2" t="s">
-        <v>202</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2">
         <v>31</v>
@@ -2659,18 +2434,18 @@
         <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="F3" t="s">
-        <v>204</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -2679,217 +2454,217 @@
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>205</v>
+        <v>130</v>
       </c>
       <c r="F4" t="s">
-        <v>206</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="F7" t="s">
-        <v>211</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C10" s="2">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="F10" t="s">
-        <v>215</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="F11" t="s">
-        <v>215</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>217</v>
+        <v>142</v>
       </c>
       <c r="F17" t="s">
-        <v>218</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2">
         <v>5</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="F19" t="s">
-        <v>220</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C21" s="2">
         <v>32</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>221</v>
+        <v>146</v>
       </c>
       <c r="F21" t="s">
-        <v>222</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2898,43 +2673,43 @@
         <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>223</v>
+        <v>148</v>
       </c>
       <c r="F22" t="s">
-        <v>218</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>205</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>168</v>
+        <v>104</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>224</v>
+        <v>149</v>
       </c>
       <c r="F24" t="s">
-        <v>220</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2943,73 +2718,73 @@
         <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="F25" t="s">
-        <v>226</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="F26" t="s">
-        <v>229</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>172</v>
+        <v>107</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="F29" t="s">
-        <v>232</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C31" s="2">
         <v>12</v>
@@ -3018,75 +2793,75 @@
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>234</v>
+        <v>159</v>
       </c>
       <c r="F31" t="s">
-        <v>235</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2">
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>238</v>
+        <v>163</v>
       </c>
       <c r="F34" t="s">
-        <v>239</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>241</v>
+        <v>166</v>
       </c>
       <c r="F37" t="s">
-        <v>239</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="C38" s="2">
         <v>2</v>
@@ -3095,26 +2870,26 @@
         <v>58</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>242</v>
+        <v>167</v>
       </c>
       <c r="F38" t="s">
-        <v>243</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="C40" s="2">
         <v>6</v>
@@ -3123,50 +2898,50 @@
         <v>44</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>245</v>
+        <v>170</v>
       </c>
       <c r="F40" t="s">
-        <v>226</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="C41" s="2">
         <v>6</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>247</v>
+        <v>172</v>
       </c>
       <c r="F41" t="s">
-        <v>226</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="C42" s="2">
         <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>249</v>
+        <v>174</v>
       </c>
       <c r="F42" t="s">
-        <v>226</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3176,7 +2951,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A753260-5018-4B3D-A2D6-F970E150F2D9}">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -3191,13 +2966,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>198</v>
+        <v>125</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>9</v>
@@ -3208,13 +2983,13 @@
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2">
         <v>23649844</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>258</v>
+        <v>183</v>
       </c>
       <c r="E2"/>
     </row>
@@ -3223,97 +2998,97 @@
         <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="C3" s="2">
         <v>19001169</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>259</v>
+        <v>184</v>
       </c>
       <c r="E3"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="C4" s="2">
         <v>16823806</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>261</v>
+        <v>185</v>
       </c>
       <c r="E4"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>266</v>
+        <v>190</v>
       </c>
       <c r="C5" s="2">
         <v>26053668</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>262</v>
+        <v>186</v>
       </c>
       <c r="E5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2">
         <v>23649844</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>263</v>
+        <v>187</v>
       </c>
       <c r="E6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>267</v>
+        <v>191</v>
       </c>
       <c r="C7" s="2">
         <v>18945794</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="E7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>268</v>
+        <v>192</v>
       </c>
       <c r="C8" s="2">
         <v>24128683</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="E8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>266</v>
+        <v>190</v>
       </c>
       <c r="C9" s="2">
         <v>26053668</v>
@@ -3323,202 +3098,202 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2">
         <v>23649844</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>269</v>
+        <v>193</v>
       </c>
       <c r="E10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>271</v>
+        <v>195</v>
       </c>
       <c r="C11" s="2">
         <v>30192380</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>270</v>
+        <v>194</v>
       </c>
       <c r="E11"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2">
         <v>23649844</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>207</v>
+        <v>132</v>
       </c>
       <c r="E12"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C13" s="8">
         <v>23649844</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>209</v>
+        <v>134</v>
       </c>
       <c r="E13"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C14" s="8">
         <v>23649844</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>272</v>
+        <v>196</v>
       </c>
       <c r="E14"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>277</v>
+        <v>201</v>
       </c>
       <c r="C15" s="8">
         <v>19151023</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>273</v>
+        <v>197</v>
       </c>
       <c r="E15"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>278</v>
+        <v>202</v>
       </c>
       <c r="C16" s="8">
         <v>24128683</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="E16"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>279</v>
+        <v>203</v>
       </c>
       <c r="C17" s="8">
         <v>8042923</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>274</v>
+        <v>198</v>
       </c>
       <c r="E17"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>280</v>
+        <v>204</v>
       </c>
       <c r="C18" s="8">
         <v>6472420</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>276</v>
+        <v>200</v>
       </c>
       <c r="E18"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C19" s="2">
         <v>23649844</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="E19"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C20" s="8">
         <v>23649844</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>213</v>
+        <v>138</v>
       </c>
       <c r="E20"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C21" s="10">
         <v>23649844</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>214</v>
+        <v>139</v>
       </c>
       <c r="E21"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C22" s="10">
         <v>23649844</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>216</v>
+        <v>141</v>
       </c>
       <c r="E22"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="6"/>
@@ -3526,7 +3301,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="6"/>
@@ -3534,7 +3309,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="6"/>
@@ -3542,7 +3317,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="6"/>
@@ -3550,7 +3325,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="6"/>
@@ -3558,22 +3333,22 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="C28" s="2">
         <v>30842973</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>281</v>
+        <v>205</v>
       </c>
       <c r="E28"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="6"/>
@@ -3581,22 +3356,22 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>251</v>
+        <v>176</v>
       </c>
       <c r="C30" s="2">
         <v>39910058</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>282</v>
+        <v>206</v>
       </c>
       <c r="E30"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="6"/>
@@ -3604,187 +3379,187 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>252</v>
+        <v>177</v>
       </c>
       <c r="C32" s="8">
         <v>19961535</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="E32"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>288</v>
+        <v>212</v>
       </c>
       <c r="C33" s="8">
         <v>9225322</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>284</v>
+        <v>208</v>
       </c>
       <c r="E33"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>289</v>
+        <v>213</v>
       </c>
       <c r="C34" s="8">
         <v>25701871</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>285</v>
+        <v>209</v>
       </c>
       <c r="E34"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="C35" s="8">
         <v>24128683</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>286</v>
+        <v>210</v>
       </c>
       <c r="E35"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>268</v>
+        <v>192</v>
       </c>
       <c r="C36" s="8">
         <v>30842973</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>287</v>
+        <v>211</v>
       </c>
       <c r="E36"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C37" s="2">
         <v>23649844</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>291</v>
+        <v>215</v>
       </c>
       <c r="E37"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>251</v>
+        <v>176</v>
       </c>
       <c r="C38" s="2">
         <v>39910058</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>292</v>
+        <v>216</v>
       </c>
       <c r="E38"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>251</v>
+        <v>176</v>
       </c>
       <c r="C39" s="2">
         <v>39910058</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="E39"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="C40" s="8">
         <v>30842973</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>293</v>
+        <v>217</v>
       </c>
       <c r="E40"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>257</v>
+        <v>182</v>
       </c>
       <c r="C41" s="8">
         <v>30697589</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>294</v>
+        <v>218</v>
       </c>
       <c r="E41"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="C42" s="2">
         <v>40343075</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>227</v>
+        <v>152</v>
       </c>
       <c r="E42"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>253</v>
+        <v>178</v>
       </c>
       <c r="C43" s="8">
         <v>16951681</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>230</v>
+        <v>155</v>
       </c>
       <c r="E43"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="6"/>
@@ -3792,127 +3567,127 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C45" s="8">
         <v>23649844</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>295</v>
+        <v>219</v>
       </c>
       <c r="E45"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>297</v>
+        <v>221</v>
       </c>
       <c r="C46" s="8">
         <v>26896090</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>296</v>
+        <v>220</v>
       </c>
       <c r="E46"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C47" s="10">
         <v>23649844</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>233</v>
+        <v>158</v>
       </c>
       <c r="E47"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>254</v>
+        <v>179</v>
       </c>
       <c r="C48" s="8">
         <v>21909802</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>298</v>
+        <v>222</v>
       </c>
       <c r="E48"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C49" s="8">
         <v>23649844</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>299</v>
+        <v>223</v>
       </c>
       <c r="E49"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C50" s="10">
         <v>23649844</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>236</v>
+        <v>161</v>
       </c>
       <c r="E50"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C51" s="10">
         <v>23649844</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>237</v>
+        <v>162</v>
       </c>
       <c r="E51"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="C52" s="8">
         <v>23261988</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="E52"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="6"/>
@@ -3920,7 +3695,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="6"/>
@@ -3928,37 +3703,37 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="C55" s="2">
         <v>23261988</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="E55"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>256</v>
+        <v>181</v>
       </c>
       <c r="C56" s="8">
         <v>31695592</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>301</v>
+        <v>225</v>
       </c>
       <c r="E56"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="6"/>
@@ -3966,46 +3741,46 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>257</v>
+        <v>182</v>
       </c>
       <c r="C58" s="8">
         <v>30697589</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>244</v>
+        <v>169</v>
       </c>
       <c r="E58"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>257</v>
+        <v>182</v>
       </c>
       <c r="C59" s="8">
         <v>30697589</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="E59"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>111</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>257</v>
       </c>
       <c r="C60" s="8">
         <v>30697589</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>248</v>
+        <v>173</v>
       </c>
       <c r="E60"/>
     </row>
@@ -4085,563 +3860,6 @@
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D46D060-F624-485D-94EE-A02F6AE57953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446CB353-0879-4FB6-92C7-1AA6D3759734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="226">
   <si>
     <t>Item name</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>Age of Onset (years)</t>
-  </si>
-  <si>
-    <t>Pedigree</t>
   </si>
   <si>
     <t>ADLD_dup_1</t>
@@ -1154,7 +1151,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
         <v>5</v>
@@ -1169,15 +1166,15 @@
         <v>277929</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2">
         <v>5</v>
@@ -1192,15 +1189,15 @@
         <v>203432</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2">
         <v>5</v>
@@ -1215,15 +1212,15 @@
         <v>189731</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2">
         <v>5</v>
@@ -1238,15 +1235,15 @@
         <v>150283</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -1261,15 +1258,15 @@
         <v>238941</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2">
         <v>5</v>
@@ -1284,15 +1281,15 @@
         <v>169456</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
@@ -1307,15 +1304,15 @@
         <v>340785</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
@@ -1330,15 +1327,15 @@
         <v>203842</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2">
         <v>5</v>
@@ -1353,15 +1350,15 @@
         <v>228672</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="2">
         <v>5</v>
@@ -1376,15 +1373,15 @@
         <v>229243</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2">
         <v>5</v>
@@ -1401,7 +1398,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="2">
         <v>5</v>
@@ -1416,15 +1413,15 @@
         <v>118354</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="2">
         <v>5</v>
@@ -1439,15 +1436,15 @@
         <v>210309</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="2">
         <v>5</v>
@@ -1464,7 +1461,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
@@ -1479,15 +1476,15 @@
         <v>1031351</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2">
         <v>5</v>
@@ -1502,15 +1499,15 @@
         <v>672515</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -1525,12 +1522,12 @@
         <v>4365976</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1545,12 +1542,12 @@
         <v>4366000</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B20" s="2">
         <v>5</v>
@@ -1567,7 +1564,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B21" s="2">
         <v>5</v>
@@ -1584,7 +1581,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="2">
         <v>5</v>
@@ -1599,15 +1596,15 @@
         <v>608833</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="2">
         <v>5</v>
@@ -1622,15 +1619,15 @@
         <v>474998</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B24" s="2">
         <v>5</v>
@@ -1647,7 +1644,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B25" s="2">
         <v>5</v>
@@ -1662,15 +1659,15 @@
         <v>250000</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B26" s="2">
         <v>5</v>
@@ -1685,12 +1682,12 @@
         <v>275347</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B27" s="2">
         <v>5</v>
@@ -1705,15 +1702,15 @@
         <v>340785</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B28" s="2">
         <v>5</v>
@@ -1728,15 +1725,15 @@
         <v>191200</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B29" s="2">
         <v>5</v>
@@ -1751,15 +1748,15 @@
         <v>324675</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="2">
         <v>5</v>
@@ -1774,15 +1771,15 @@
         <v>234020</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B31" s="2">
         <v>5</v>
@@ -1797,15 +1794,15 @@
         <v>148085</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B32" s="2">
         <v>5</v>
@@ -1820,15 +1817,15 @@
         <v>153769</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B33" s="2">
         <v>5</v>
@@ -1843,15 +1840,15 @@
         <v>127608</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" s="2">
         <v>5</v>
@@ -1868,7 +1865,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B35" s="2">
         <v>5</v>
@@ -1885,7 +1882,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B36" s="2">
         <v>5</v>
@@ -1900,12 +1897,12 @@
         <v>156734</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37" s="2">
         <v>5</v>
@@ -1922,7 +1919,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="2">
         <v>5</v>
@@ -1937,12 +1934,12 @@
         <v>59651</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B39" s="2">
         <v>5</v>
@@ -1957,15 +1954,15 @@
         <v>184808</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B40" s="2">
         <v>5</v>
@@ -1977,12 +1974,12 @@
         <v>126903760</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B41" s="2">
         <v>5</v>
@@ -1994,12 +1991,12 @@
         <v>126896451</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B42" s="2">
         <v>5</v>
@@ -2033,335 +2030,335 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2388,7 +2385,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
@@ -2397,35 +2394,35 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2">
         <v>16</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" t="s">
         <v>126</v>
-      </c>
-      <c r="F2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2">
         <v>31</v>
@@ -2434,18 +2431,18 @@
         <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" t="s">
         <v>128</v>
-      </c>
-      <c r="F3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -2454,217 +2451,217 @@
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" t="s">
         <v>130</v>
-      </c>
-      <c r="F4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="E7" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" t="s">
         <v>135</v>
-      </c>
-      <c r="F7" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2">
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" t="s">
         <v>142</v>
-      </c>
-      <c r="F17" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="2">
         <v>5</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F19" t="s">
         <v>144</v>
-      </c>
-      <c r="F19" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C21" s="2">
         <v>32</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F21" t="s">
         <v>146</v>
-      </c>
-      <c r="F21" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2673,43 +2670,43 @@
         <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2718,73 +2715,73 @@
         <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F25" t="s">
         <v>150</v>
-      </c>
-      <c r="F25" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F26" t="s">
         <v>153</v>
-      </c>
-      <c r="F26" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="E29" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F29" t="s">
         <v>156</v>
-      </c>
-      <c r="F29" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="2">
         <v>12</v>
@@ -2793,75 +2790,75 @@
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F31" t="s">
         <v>159</v>
-      </c>
-      <c r="F31" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C32" s="2">
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F34" t="s">
         <v>163</v>
-      </c>
-      <c r="F34" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C38" s="2">
         <v>2</v>
@@ -2870,26 +2867,26 @@
         <v>58</v>
       </c>
       <c r="E38" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F38" t="s">
         <v>167</v>
-      </c>
-      <c r="F38" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C40" s="2">
         <v>6</v>
@@ -2898,50 +2895,50 @@
         <v>44</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="C41" s="2">
         <v>6</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C42" s="2">
         <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2951,914 +2948,844 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A753260-5018-4B3D-A2D6-F970E150F2D9}">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="32.5703125" style="5" customWidth="1"/>
     <col min="3" max="3" width="57.28515625" style="5" customWidth="1"/>
     <col min="4" max="4" width="255.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.140625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
       <c r="B2" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="2">
         <v>23649844</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C3" s="2">
         <v>19001169</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="E3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C4" s="2">
         <v>16823806</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E4"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C5" s="2">
         <v>26053668</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E5"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2">
         <v>23649844</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="E6"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C7" s="2">
         <v>18945794</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="E7"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C8" s="2">
         <v>24128683</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="E8"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="C9" s="2">
         <v>26053668</v>
       </c>
       <c r="D9" s="6"/>
-      <c r="E9"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2">
         <v>23649844</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E10"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C11" s="2">
         <v>30192380</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="E11"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2">
         <v>23649844</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="8">
         <v>23649844</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="8">
         <v>23649844</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="E14"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C15" s="8">
         <v>19151023</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="E15"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C16" s="8">
         <v>24128683</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="E16"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" s="8">
         <v>8042923</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="E17"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C18" s="8">
         <v>6472420</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="E18"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="2">
         <v>23649844</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E19"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="8">
         <v>23649844</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E20"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="10">
         <v>23649844</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="10">
         <v>23649844</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="6"/>
-      <c r="E23"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="6"/>
-      <c r="E24"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="6"/>
-      <c r="E25"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="6"/>
-      <c r="E26"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="6"/>
-      <c r="E27"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="C28" s="2">
         <v>30842973</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="E28"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="6"/>
-      <c r="E29"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C30" s="2">
         <v>39910058</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="E30"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="6"/>
-      <c r="E31"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C32" s="8">
         <v>19961535</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="E32"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C33" s="8">
         <v>9225322</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="E33"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C34" s="8">
         <v>25701871</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E34"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" s="8">
         <v>24128683</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="E35"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C36" s="8">
         <v>30842973</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="E36"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C37" s="2">
         <v>23649844</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="E37"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C38" s="2">
         <v>39910058</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E38"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C39" s="2">
         <v>39910058</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="E39"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C40" s="8">
         <v>30842973</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E40"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C41" s="8">
         <v>30697589</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="E41"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="2">
         <v>40343075</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E42"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C43" s="8">
         <v>16951681</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="E43"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="6"/>
-      <c r="E44"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C45" s="8">
         <v>23649844</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="E45"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C46" s="8">
         <v>26896090</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="E46"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C47" s="10">
         <v>23649844</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="E47"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C48" s="8">
         <v>21909802</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="E48"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C49" s="8">
         <v>23649844</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="E49"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C50" s="10">
         <v>23649844</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="E50"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C51" s="10">
         <v>23649844</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="E51"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C52" s="8">
         <v>23261988</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="E52"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="6"/>
-      <c r="E53"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="6"/>
-      <c r="E54"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C55" s="2">
         <v>23261988</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E55"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C56" s="8">
         <v>31695592</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="E56"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="6"/>
-      <c r="E57"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C58" s="8">
         <v>30697589</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E58"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C59" s="8">
         <v>30697589</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E59"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C60" s="8">
         <v>30697589</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E60"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446CB353-0879-4FB6-92C7-1AA6D3759734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8854FAA-04C0-4DD7-BA95-C2C208B22596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -173,9 +173,6 @@
     <t>ADLD_del_1</t>
   </si>
   <si>
-    <t>Nmezi 2019</t>
-  </si>
-  <si>
     <t>Britain, England</t>
   </si>
   <si>
@@ -570,27 +567,9 @@
     <t>[Pyramidal signs] [Cerebellar signs] [Cognitive impairment]</t>
   </si>
   <si>
-    <t>Marklund 2008</t>
-  </si>
-  <si>
-    <t>Nmezi 2025</t>
-  </si>
-  <si>
-    <t>Giorgio 2015</t>
-  </si>
-  <si>
-    <t>Padiath 2006</t>
-  </si>
-  <si>
-    <t>DosSantos 2012</t>
-  </si>
-  <si>
     <t>Columbaro 2013</t>
   </si>
   <si>
-    <t>Zhang 2019</t>
-  </si>
-  <si>
     <t>Mezaki 2018</t>
   </si>
   <si>
@@ -618,9 +597,6 @@
     <t>Finnsson 2015</t>
   </si>
   <si>
-    <t>Sundblom 2009; Marklund 2006</t>
-  </si>
-  <si>
     <t>Alturkustani 2013</t>
   </si>
   <si>
@@ -648,18 +624,6 @@
     <t>Schwankhaus1988_1/56/F_Son; _1/56/F; _2/50/F; _3/60/F; _4/53/M; _5/56/M</t>
   </si>
   <si>
-    <t>Coffeen 2000</t>
-  </si>
-  <si>
-    <t>Padiath 2006; Alturkustani 2013</t>
-  </si>
-  <si>
-    <t>Alturkustani 2013_Eldridge</t>
-  </si>
-  <si>
-    <t>Schwankhaus 1988</t>
-  </si>
-  <si>
     <t>Nmezi2019_DEL3-1; Nmezi2019_DEL3-2; Nmezi2019_DEL3-3</t>
   </si>
   <si>
@@ -684,9 +648,6 @@
     <t>Bergui 1997</t>
   </si>
   <si>
-    <t>Brussino 2010</t>
-  </si>
-  <si>
     <t>Nmezi2025_F3-1; Nmezi2025_F3-2</t>
   </si>
   <si>
@@ -708,9 +669,6 @@
     <t>Terlizzi2016_IV11; Terlizzi2016_IV10; Terlizzi2016_IV12</t>
   </si>
   <si>
-    <t>Terlizzi 2016</t>
-  </si>
-  <si>
     <t>DosSantos2012_Proband; _Sister</t>
   </si>
   <si>
@@ -723,7 +681,49 @@
     <t>Zhang2019_II4_Proband; Zhang2019_II5</t>
   </si>
   <si>
-    <t>Meijer 2008</t>
+    <t>Coffeen 2000 *pedigree available</t>
+  </si>
+  <si>
+    <t>Brussino 2010 *pedigree available</t>
+  </si>
+  <si>
+    <t>DosSantos 2012 *pedigree available</t>
+  </si>
+  <si>
+    <t>Giorgio 2015 *pedigree available</t>
+  </si>
+  <si>
+    <t>Marklund 2008 *pedigree available</t>
+  </si>
+  <si>
+    <t>Meijer 2008 *pedigree available</t>
+  </si>
+  <si>
+    <t>Nmezi 2019 *pedigree available</t>
+  </si>
+  <si>
+    <t>Nmezi 2025 *pedigree available</t>
+  </si>
+  <si>
+    <t>Padiath 2006 *pedigree avialable; Alturkustani 2013</t>
+  </si>
+  <si>
+    <t>Padiath 2006 *pedigree available</t>
+  </si>
+  <si>
+    <t>Sundblom 2009 *pedigree available; Marklund 2006 *pedigree available</t>
+  </si>
+  <si>
+    <t>Terlizzi 2016 *pedigree available</t>
+  </si>
+  <si>
+    <t>Zhang 2019 *pedigree available</t>
+  </si>
+  <si>
+    <t>Alturkustani 2013; Eldridge 1984 *pedigree available</t>
+  </si>
+  <si>
+    <t>Schwankhaus 1988 *pedigree available</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1215,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1238,7 +1238,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1307,7 +1307,7 @@
         <v>20</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1330,7 +1330,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1376,7 +1376,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1416,7 +1416,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1461,7 +1461,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B16" s="2">
         <v>5</v>
@@ -1479,7 +1479,7 @@
         <v>10</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1499,15 +1499,15 @@
         <v>672515</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -1522,12 +1522,12 @@
         <v>4365976</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1542,12 +1542,12 @@
         <v>4366000</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B20" s="2">
         <v>5</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2">
         <v>5</v>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B22" s="2">
         <v>5</v>
@@ -1596,15 +1596,15 @@
         <v>608833</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2">
         <v>5</v>
@@ -1619,15 +1619,15 @@
         <v>474998</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B24" s="2">
         <v>5</v>
@@ -1644,7 +1644,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2">
         <v>5</v>
@@ -1659,15 +1659,15 @@
         <v>250000</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B26" s="2">
         <v>5</v>
@@ -1682,12 +1682,12 @@
         <v>275347</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B27" s="2">
         <v>5</v>
@@ -1705,12 +1705,12 @@
         <v>10</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" s="2">
         <v>5</v>
@@ -1728,12 +1728,12 @@
         <v>10</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2">
         <v>5</v>
@@ -1751,12 +1751,12 @@
         <v>10</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B30" s="2">
         <v>5</v>
@@ -1774,12 +1774,12 @@
         <v>10</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31" s="2">
         <v>5</v>
@@ -1797,12 +1797,12 @@
         <v>10</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B32" s="2">
         <v>5</v>
@@ -1820,12 +1820,12 @@
         <v>10</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B33" s="2">
         <v>5</v>
@@ -1843,12 +1843,12 @@
         <v>10</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B34" s="2">
         <v>5</v>
@@ -1865,7 +1865,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" s="2">
         <v>5</v>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B36" s="2">
         <v>5</v>
@@ -1897,12 +1897,12 @@
         <v>156734</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B37" s="2">
         <v>5</v>
@@ -1919,7 +1919,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B38" s="2">
         <v>5</v>
@@ -1934,12 +1934,12 @@
         <v>59651</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B39" s="2">
         <v>5</v>
@@ -1957,12 +1957,12 @@
         <v>10</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B40" s="2">
         <v>5</v>
@@ -1974,12 +1974,12 @@
         <v>126903760</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B41" s="2">
         <v>5</v>
@@ -1991,12 +1991,12 @@
         <v>126896451</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B42" s="2">
         <v>5</v>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2038,7 +2038,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2046,7 +2046,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2054,7 +2054,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2062,7 +2062,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2070,7 +2070,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2078,7 +2078,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2086,7 +2086,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2094,7 +2094,7 @@
         <v>29</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2102,7 +2102,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2110,7 +2110,7 @@
         <v>31</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2118,7 +2118,7 @@
         <v>37</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2126,7 +2126,7 @@
         <v>38</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2134,7 +2134,7 @@
         <v>39</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2142,15 +2142,15 @@
         <v>41</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -2158,207 +2158,207 @@
         <v>43</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2385,7 +2385,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
@@ -2394,10 +2394,10 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2411,10 +2411,10 @@
         <v>16</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" t="s">
         <v>125</v>
-      </c>
-      <c r="F2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2431,10 +2431,10 @@
         <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" t="s">
         <v>127</v>
-      </c>
-      <c r="F3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2451,10 +2451,10 @@
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" t="s">
         <v>129</v>
-      </c>
-      <c r="F4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2468,7 +2468,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2479,7 +2479,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2496,10 +2496,10 @@
         <v>26</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7" t="s">
         <v>134</v>
-      </c>
-      <c r="F7" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2510,7 +2510,7 @@
         <v>23</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2527,7 +2527,7 @@
         <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2544,10 +2544,10 @@
         <v>35</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2558,10 +2558,10 @@
         <v>23</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2586,7 +2586,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>42</v>
@@ -2597,24 +2597,24 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F17" t="s">
         <v>141</v>
-      </c>
-      <c r="F17" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>23</v>
@@ -2622,46 +2622,46 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="2">
         <v>5</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" t="s">
         <v>143</v>
-      </c>
-      <c r="F19" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" s="2">
         <v>32</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" t="s">
         <v>145</v>
-      </c>
-      <c r="F21" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -2670,43 +2670,43 @@
         <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -2715,70 +2715,70 @@
         <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F25" t="s">
         <v>149</v>
-      </c>
-      <c r="F25" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F26" t="s">
         <v>152</v>
-      </c>
-      <c r="F26" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="E29" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F29" t="s">
         <v>155</v>
-      </c>
-      <c r="F29" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>34</v>
@@ -2790,75 +2790,75 @@
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F31" t="s">
         <v>158</v>
-      </c>
-      <c r="F31" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C32" s="2">
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F34" t="s">
         <v>162</v>
-      </c>
-      <c r="F34" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F37" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C38" s="2">
         <v>2</v>
@@ -2867,26 +2867,26 @@
         <v>58</v>
       </c>
       <c r="E38" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F38" t="s">
         <v>166</v>
-      </c>
-      <c r="F38" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C40" s="2">
         <v>6</v>
@@ -2895,50 +2895,50 @@
         <v>44</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="C41" s="2">
         <v>6</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C42" s="2">
         <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2952,9 +2952,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="57.28515625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="255.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="139.85546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2962,13 +2962,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2982,7 +2982,7 @@
         <v>23649844</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2990,13 +2990,13 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C3" s="2">
         <v>19001169</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -3004,13 +3004,13 @@
         <v>13</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="C4" s="2">
         <v>16823806</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3018,13 +3018,13 @@
         <v>13</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C5" s="2">
         <v>26053668</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -3038,7 +3038,7 @@
         <v>23649844</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3046,13 +3046,13 @@
         <v>13</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="C7" s="2">
         <v>18945794</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3060,13 +3060,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C8" s="2">
         <v>24128683</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3074,7 +3074,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C9" s="2">
         <v>26053668</v>
@@ -3092,7 +3092,7 @@
         <v>23649844</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3100,13 +3100,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C11" s="2">
         <v>30192380</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -3120,7 +3120,7 @@
         <v>23649844</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3134,7 +3134,7 @@
         <v>23649844</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -3148,7 +3148,7 @@
         <v>23649844</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3156,13 +3156,13 @@
         <v>19</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="C15" s="8">
         <v>19151023</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3170,13 +3170,13 @@
         <v>19</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="C16" s="8">
         <v>24128683</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -3184,13 +3184,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="C17" s="8">
         <v>8042923</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -3198,13 +3198,13 @@
         <v>19</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="C18" s="8">
         <v>6472420</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3218,7 +3218,7 @@
         <v>23649844</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3232,7 +3232,7 @@
         <v>23649844</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3246,7 +3246,7 @@
         <v>23649844</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3260,7 +3260,7 @@
         <v>23649844</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3293,7 +3293,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="6"/>
@@ -3303,74 +3303,74 @@
         <v>43</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>44</v>
+        <v>217</v>
       </c>
       <c r="C28" s="2">
         <v>30842973</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="6"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="C30" s="2">
         <v>39910058</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="6"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="C32" s="8">
         <v>19961535</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="C33" s="8">
         <v>9225322</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>212</v>
@@ -3379,40 +3379,40 @@
         <v>25701871</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>44</v>
+        <v>217</v>
       </c>
       <c r="C35" s="8">
         <v>24128683</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C36" s="8">
         <v>30842973</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>27</v>
@@ -3421,103 +3421,103 @@
         <v>23649844</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="C38" s="2">
         <v>39910058</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="C39" s="2">
         <v>39910058</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="C40" s="8">
         <v>30842973</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C41" s="8">
         <v>30697589</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="2">
         <v>40343075</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="C43" s="8">
         <v>16951681</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="6"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>27</v>
@@ -3526,26 +3526,26 @@
         <v>23649844</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C46" s="8">
         <v>26896090</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>27</v>
@@ -3554,26 +3554,26 @@
         <v>23649844</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="C48" s="8">
         <v>21909802</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>27</v>
@@ -3582,12 +3582,12 @@
         <v>23649844</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>27</v>
@@ -3596,12 +3596,12 @@
         <v>23649844</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>27</v>
@@ -3610,112 +3610,112 @@
         <v>23649844</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C52" s="8">
         <v>23261988</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="6"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="6"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C55" s="2">
         <v>23261988</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>180</v>
+        <v>223</v>
       </c>
       <c r="C56" s="8">
         <v>31695592</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="6"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C58" s="8">
         <v>30697589</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C59" s="8">
         <v>30697589</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C60" s="8">
         <v>30697589</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8854FAA-04C0-4DD7-BA95-C2C208B22596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DFE790-6F95-4BAD-973B-3F7D4C7056BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="223">
   <si>
     <t>Item name</t>
   </si>
@@ -437,34 +437,16 @@
 [MRI abnormality, Grade 5]</t>
   </si>
   <si>
-    <t>Giorgio2013_A4</t>
-  </si>
-  <si>
     <t>[Symptomatic - specific symptoms not documented]</t>
   </si>
   <si>
-    <t>Giorgio2013_A5</t>
-  </si>
-  <si>
     <t>[Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Thermoregulatory dysfunction] [Pyramidal signs] [Cerebellar signs] [Sexual dysfunction]</t>
   </si>
   <si>
     <t>[Cerebral white matter abnormalities (MRI), symmetric] [Cerebellar white matter lesions (MRI), symmetric] [Cerebellar white matter lesions (MRI)]  [Spinal cord abnormalities (MRI)] [Cerebellar white matter lesions (CT), symmetric] [Cerebral white matter abnormalities (CT)] [Cerebellar white matter lesions (CT)] [Spinal cord abnormalities (CT)]</t>
   </si>
   <si>
-    <t>Giorgio2013_A8,AV1</t>
-  </si>
-  <si>
-    <t>Giorgio2013_A10</t>
-  </si>
-  <si>
-    <t>Giorgio2013_A11</t>
-  </si>
-  <si>
     <t>Not reported / unknown.</t>
-  </si>
-  <si>
-    <t>Giorgio2013_A14</t>
   </si>
   <si>
     <t xml:space="preserve">[Pyramidal signs] [Cerebellar signs] [Dysarthria] [Autonomic dysfunction] [Bladder/bowel dysfunction] [Pseudobulbar affect]
@@ -498,48 +480,30 @@
     <t>[Cerebral white matter abnormalities (MRI)] [Cerebellar white matter lesions (MRI)]</t>
   </si>
   <si>
-    <t>Wang2025_Proband</t>
-  </si>
-  <si>
     <t>[Autonomic dysfunction] [Bladder/bowel dysfunction] [Pyramidal signs] [Dysphagia]</t>
   </si>
   <si>
     <t>[Cerebral white matter abnormalities (MRI), possibly symmetric] [Cerebellar white matter lesions (MRI), possibly symmetric]</t>
   </si>
   <si>
-    <t>Padiath2006_K50069</t>
-  </si>
-  <si>
     <t>[Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Sexual dysfunction] [Pyramidal signs] [Cerebellar signs] [Dysphagia] [Possible Pseudobulbar affect]</t>
   </si>
   <si>
     <t>[Cerebellar white matter lesions (MRI)]</t>
   </si>
   <si>
-    <t>Giorgio2013_FR1,FR2</t>
-  </si>
-  <si>
     <t>[Autonomic dysfunction] [Bladder/bowel dysfunction] [Pyramidal signs] [Cerebellar signs] [Pseudobulbar affect] [Cognitive impairment]</t>
   </si>
   <si>
     <t>[Cerebral white matter abnormalities (MRI), symmetric] [Cerebellar white matter lesions (MRI)] [Spinal cord abnormalities (MRI)]</t>
   </si>
   <si>
-    <t>Giorgio2013_IT1</t>
-  </si>
-  <si>
-    <t>Giorgio2013_IT2</t>
-  </si>
-  <si>
     <t>[Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Sexual dysfunction] [Thermoregulatory dysfunction] [Pyramidal signs] [Cerebellar signs]</t>
   </si>
   <si>
     <t>[Cerebral white matter abnormalities (MRI)]</t>
   </si>
   <si>
-    <t>Columbaro2013_ADLD2</t>
-  </si>
-  <si>
     <t>[Autonomic dysfunction] [Orthostatic hypotension] [Sexual dysfunction]</t>
   </si>
   <si>
@@ -549,21 +513,12 @@
     <t>[Cerebral white matter abnormalities (MRI), symmetric] [Cerebellar white matter lesions (MRI), symmetric] [Spinal cord abnormalities (MRI)]</t>
   </si>
   <si>
-    <t>Mezaki2018_PedigreeI_Patient1</t>
-  </si>
-  <si>
     <t>[Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Thermoregulatory dysfunction] [Pyramidal signs] [Cerebellar signs] [Cognitive impairment]</t>
   </si>
   <si>
-    <t>Mezaki2018_PedigreeII_Patient2</t>
-  </si>
-  <si>
     <t>[Autonomic dysfunction] [Orthostatic hypotension] [Bladder/bowel dysfunction] [Pyramidal signs] [Cerebellar signs] [Cognitive impairment]</t>
   </si>
   <si>
-    <t>Mezaki2018_PedigreeIII_Patient4</t>
-  </si>
-  <si>
     <t>[Pyramidal signs] [Cerebellar signs] [Cognitive impairment]</t>
   </si>
   <si>
@@ -573,114 +528,18 @@
     <t>Mezaki 2018</t>
   </si>
   <si>
-    <t>Giorgio2013_A1</t>
-  </si>
-  <si>
-    <t>Meijer2008_IV1; _II3; _II4; _III10; _IV13; _IV4</t>
-  </si>
-  <si>
-    <t>Marklund2008_Cohort</t>
-  </si>
-  <si>
-    <t>Finnsson2015_Family1_23F; _22M; _20M; _19F; _18F; _17F; _16F; _15M; _14F; _13F; _12F; _11M; _10M; _8F; _7F; _5M; _4M; _3M; _2M; _1F</t>
-  </si>
-  <si>
-    <t>Giorgio2013_A2</t>
-  </si>
-  <si>
-    <t>Sundblom2009_1; Marklund2006</t>
-  </si>
-  <si>
-    <t>Alturkustani2013_Sundlom_7</t>
-  </si>
-  <si>
     <t>Finnsson 2015</t>
   </si>
   <si>
     <t>Alturkustani 2013</t>
   </si>
   <si>
-    <t>Giorgio2013_A3</t>
-  </si>
-  <si>
-    <t>Finnsson2019_Family2_5; _6</t>
-  </si>
-  <si>
     <t>Finnsson 2019</t>
   </si>
   <si>
-    <t>Giorgio2013_A6,A7,K2-3</t>
-  </si>
-  <si>
-    <t>Coffeen2000_K2685</t>
-  </si>
-  <si>
-    <t>Alturkustani2013_Eldridge_1</t>
-  </si>
-  <si>
-    <t>Padiath2006_K4233; Alturkustani2013_Coffeen_3</t>
-  </si>
-  <si>
-    <t>Schwankhaus1988_1/56/F_Son; _1/56/F; _2/50/F; _3/60/F; _4/53/M; _5/56/M</t>
-  </si>
-  <si>
-    <t>Nmezi2019_DEL3-1; Nmezi2019_DEL3-2; Nmezi2019_DEL3-3</t>
-  </si>
-  <si>
-    <t>Nmezi2025_F1-1; Nmezi2025_F1-2; Nmezi2025_F1-3; Nmezi2025_F1-4; Nmezi2025_F1-5</t>
-  </si>
-  <si>
-    <t>Giorgio2015_ADLD-1-TO</t>
-  </si>
-  <si>
-    <t>Bergui1997_Family1</t>
-  </si>
-  <si>
-    <t>Brussino2010_ADLD-1-TO</t>
-  </si>
-  <si>
-    <t>Nmezi2019_DEL2-1</t>
-  </si>
-  <si>
-    <t>Alturkustani2013</t>
-  </si>
-  <si>
     <t>Bergui 1997</t>
   </si>
   <si>
-    <t>Nmezi2025_F3-1; Nmezi2025_F3-2</t>
-  </si>
-  <si>
-    <t>Giorgio2013_BR1</t>
-  </si>
-  <si>
-    <t>Nmezi2025_F4-1</t>
-  </si>
-  <si>
-    <t>Nmezi2019_DEL1-1</t>
-  </si>
-  <si>
-    <t>Mezaki2018_PedigreeIV_Patient5; Mezaki2018_PedigreeIV_Patient6</t>
-  </si>
-  <si>
-    <t>Giorgio2013_IT3</t>
-  </si>
-  <si>
-    <t>Terlizzi2016_IV11; Terlizzi2016_IV10; Terlizzi2016_IV12</t>
-  </si>
-  <si>
-    <t>DosSantos2012_Proband; _Sister</t>
-  </si>
-  <si>
-    <t>Giorgio2013_G1</t>
-  </si>
-  <si>
-    <t>Columbaro2013_ADLD1; Columbaro2013_ADLD3</t>
-  </si>
-  <si>
-    <t>Zhang2019_II4_Proband; Zhang2019_II5</t>
-  </si>
-  <si>
     <t>Coffeen 2000 *pedigree available</t>
   </si>
   <si>
@@ -724,6 +583,138 @@
   </si>
   <si>
     <t>Schwankhaus 1988 *pedigree available</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>A14</t>
+  </si>
+  <si>
+    <t>Cohort</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Patient 1</t>
+  </si>
+  <si>
+    <t>Patient 7</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6, A7, K2-3</t>
+  </si>
+  <si>
+    <t>Family2_5, _6</t>
+  </si>
+  <si>
+    <t>Family1_23F, _22M, _20M, _19F, _18F, _17F, _16F, _15M, _14F, _13F, _12F, _11M, _10M, _8F, _7F, _5M, _4M, _3M, _2M, _1F</t>
+  </si>
+  <si>
+    <t>IV1, II3, II4, III10, IV13, IV4</t>
+  </si>
+  <si>
+    <t>K2685</t>
+  </si>
+  <si>
+    <t>K4233, Alturkustani2013_Coffeen_3</t>
+  </si>
+  <si>
+    <t>1/56/F_Son, _1/56/F, _2/50/F, _3/60/F, _4/53/M, _5/56/M</t>
+  </si>
+  <si>
+    <t>A8, AV1</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>DEL3-1, DEL3-2, DEL3-3</t>
+  </si>
+  <si>
+    <t>F1-1, F1-2, F1-3, F1-4, F1-5</t>
+  </si>
+  <si>
+    <t>ADLD-1-TO</t>
+  </si>
+  <si>
+    <t>Family 1</t>
+  </si>
+  <si>
+    <t>DEL2-1</t>
+  </si>
+  <si>
+    <t>BR1</t>
+  </si>
+  <si>
+    <t>F4-1</t>
+  </si>
+  <si>
+    <t>F3-1, F3-2</t>
+  </si>
+  <si>
+    <t>DEL1-1</t>
+  </si>
+  <si>
+    <t>PedigreeIV_Patient5, PedigreeIV_Patient6</t>
+  </si>
+  <si>
+    <t>Proband</t>
+  </si>
+  <si>
+    <t>K50069</t>
+  </si>
+  <si>
+    <t>IT3</t>
+  </si>
+  <si>
+    <t>IV11, IV10, IV12</t>
+  </si>
+  <si>
+    <t>FR1, FR2</t>
+  </si>
+  <si>
+    <t>Proband, Sister</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>IT1</t>
+  </si>
+  <si>
+    <t>IT2</t>
+  </si>
+  <si>
+    <t>ADLD1, ADLD3</t>
+  </si>
+  <si>
+    <t>ADLD2</t>
+  </si>
+  <si>
+    <t>II4_Proband, II5</t>
+  </si>
+  <si>
+    <t>PedigreeI_Patient1</t>
+  </si>
+  <si>
+    <t>PedigreeII_Patient2</t>
+  </si>
+  <si>
+    <t>PedigreeIII_Patient4</t>
   </si>
 </sst>
 </file>
@@ -2468,7 +2459,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2479,7 +2470,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2496,10 +2487,10 @@
         <v>26</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2510,7 +2501,7 @@
         <v>23</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2527,7 +2518,7 @@
         <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2544,10 +2535,10 @@
         <v>35</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F10" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2558,10 +2549,10 @@
         <v>23</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F11" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2606,10 +2597,10 @@
         <v>99</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F17" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2631,10 +2622,10 @@
         <v>5</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F19" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2650,10 +2641,10 @@
         <v>32</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F21" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2670,10 +2661,10 @@
         <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F22" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2695,10 +2686,10 @@
         <v>102</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F24" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2715,10 +2706,10 @@
         <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F25" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2726,10 +2717,10 @@
         <v>115</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F26" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2737,7 +2728,7 @@
         <v>66</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2759,10 +2750,10 @@
         <v>105</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F29" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2773,7 +2764,7 @@
         <v>65</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2790,10 +2781,10 @@
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="F31" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2810,7 +2801,7 @@
         <v>76</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2818,7 +2809,7 @@
         <v>67</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2826,10 +2817,10 @@
         <v>68</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="F34" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2847,10 +2838,10 @@
         <v>71</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="F37" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2867,10 +2858,10 @@
         <v>58</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="F38" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2895,10 +2886,10 @@
         <v>44</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="F40" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2915,10 +2906,10 @@
         <v>101</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="F41" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2935,10 +2926,10 @@
         <v>101</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="F42" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2982,7 +2973,7 @@
         <v>23649844</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2990,13 +2981,13 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="C3" s="2">
         <v>19001169</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -3004,13 +2995,13 @@
         <v>13</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="C4" s="2">
         <v>16823806</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3018,13 +3009,13 @@
         <v>13</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="C5" s="2">
         <v>26053668</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -3038,7 +3029,7 @@
         <v>23649844</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3046,13 +3037,13 @@
         <v>13</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="C7" s="2">
         <v>18945794</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3060,13 +3051,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="C8" s="2">
         <v>24128683</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3074,7 +3065,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="C9" s="2">
         <v>26053668</v>
@@ -3092,7 +3083,7 @@
         <v>23649844</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3100,13 +3091,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="C11" s="2">
         <v>30192380</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -3120,7 +3111,7 @@
         <v>23649844</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3134,7 +3125,7 @@
         <v>23649844</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -3148,7 +3139,7 @@
         <v>23649844</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3156,13 +3147,13 @@
         <v>19</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="C15" s="8">
         <v>19151023</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3170,13 +3161,13 @@
         <v>19</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>219</v>
+        <v>172</v>
       </c>
       <c r="C16" s="8">
         <v>24128683</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -3184,13 +3175,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="C17" s="8">
         <v>8042923</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -3198,13 +3189,13 @@
         <v>19</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>225</v>
+        <v>178</v>
       </c>
       <c r="C18" s="8">
         <v>6472420</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3218,7 +3209,7 @@
         <v>23649844</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>135</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3232,7 +3223,7 @@
         <v>23649844</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>136</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3246,7 +3237,7 @@
         <v>23649844</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3260,7 +3251,7 @@
         <v>23649844</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3303,13 +3294,13 @@
         <v>43</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="C28" s="2">
         <v>30842973</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3324,13 +3315,13 @@
         <v>112</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="C30" s="2">
         <v>39910058</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3345,13 +3336,13 @@
         <v>45</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="C32" s="8">
         <v>19961535</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3359,13 +3350,13 @@
         <v>45</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="C33" s="8">
         <v>9225322</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3373,13 +3364,13 @@
         <v>45</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="C34" s="8">
         <v>25701871</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3387,13 +3378,13 @@
         <v>46</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="C35" s="8">
         <v>24128683</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -3401,13 +3392,13 @@
         <v>46</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="C36" s="8">
         <v>30842973</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -3421,7 +3412,7 @@
         <v>23649844</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -3429,13 +3420,13 @@
         <v>47</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="C38" s="2">
         <v>39910058</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -3443,13 +3434,13 @@
         <v>114</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="C39" s="2">
         <v>39910058</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -3457,13 +3448,13 @@
         <v>53</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="C40" s="8">
         <v>30842973</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3471,13 +3462,13 @@
         <v>53</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C41" s="8">
         <v>30697589</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -3491,7 +3482,7 @@
         <v>40343075</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>150</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -3499,13 +3490,13 @@
         <v>66</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>220</v>
+        <v>173</v>
       </c>
       <c r="C43" s="8">
         <v>16951681</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -3526,7 +3517,7 @@
         <v>23649844</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -3534,13 +3525,13 @@
         <v>57</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="C46" s="8">
         <v>26896090</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -3554,7 +3545,7 @@
         <v>23649844</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -3562,13 +3553,13 @@
         <v>61</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>213</v>
+        <v>166</v>
       </c>
       <c r="C48" s="8">
         <v>21909802</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -3582,7 +3573,7 @@
         <v>23649844</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -3596,7 +3587,7 @@
         <v>23649844</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -3610,7 +3601,7 @@
         <v>23649844</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -3618,13 +3609,13 @@
         <v>68</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="C52" s="8">
         <v>23261988</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3646,13 +3637,13 @@
         <v>71</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="C55" s="2">
         <v>23261988</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>163</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3660,13 +3651,13 @@
         <v>72</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>223</v>
+        <v>176</v>
       </c>
       <c r="C56" s="8">
         <v>31695592</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3681,13 +3672,13 @@
         <v>95</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C58" s="8">
         <v>30697589</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>167</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -3695,13 +3686,13 @@
         <v>96</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C59" s="8">
         <v>30697589</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -3709,13 +3700,13 @@
         <v>109</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C60" s="8">
         <v>30697589</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Krizchelle\ADLD Patient Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DFE790-6F95-4BAD-973B-3F7D4C7056BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2639C71F-E11E-4CEC-BBAE-B904DDA99923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Molecular" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="243">
   <si>
     <t>Item name</t>
   </si>
@@ -390,14 +390,6 @@
   </si>
   <si>
     <t>Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">publications
-literature case labels
-multigenerational family
-estimated unique individuals
-high-confidence linked individuals
-Deduplication status: </t>
   </si>
   <si>
     <t>Country of origin</t>
@@ -715,6 +707,135 @@
   </si>
   <si>
     <t>PedigreeIII_Patient4</t>
+  </si>
+  <si>
+    <t>2 publications
+7 literature case labels
+Multigenerational family - 4 generations
+16 estimated unique individuals
+Deduplication status: partially resolved</t>
+  </si>
+  <si>
+    <t>5 publications
+24 literature case labels
+Multigenerational family - 6 generations
+31 estimated unique individuals
+Deduplication status: partially resolved</t>
+  </si>
+  <si>
+    <t>8 publications
+24 literature case labels
+Multigenerational family - 6 generations
+31 estimated unique individuals
+Deduplication status: partially resolved</t>
+  </si>
+  <si>
+    <t>3 publications
+4 literature case labels
+4 estimated unique individuals
+Deduplication status: partially resolved</t>
+  </si>
+  <si>
+    <t>1 publication
+1 literature case labels
+1 estimated unique individuals
+Deduplication status: resolved</t>
+  </si>
+  <si>
+    <t>5 publications
+13 literature case labels
+Multigenerational family - 5 generations
+13 estimated unique individuals
+Deduplication status: partially resolved</t>
+  </si>
+  <si>
+    <t>1 publications
+2 literature case labels
+2 estimated unique individuals
+Deduplication status: resolved</t>
+  </si>
+  <si>
+    <t>1 publications
+1 literature case labels
+1 estimated unique individuals
+Deduplication status: resolved</t>
+  </si>
+  <si>
+    <t>? publications
+? literature case labels
+Multigenerational family?
+? estimated unique individuals
+Deduplication status: ?</t>
+  </si>
+  <si>
+    <t>1 publications
+3 literature case labels
+Deduplication status: partially resolved</t>
+  </si>
+  <si>
+    <t>1 publications
+3 literature case labels
+3 estimated unique individuals
+Deduplication status: resolved</t>
+  </si>
+  <si>
+    <t>1 publications
+5 literature case labels
+5 estimated unique individuals
+Deduplication status: resolved</t>
+  </si>
+  <si>
+    <t>3 publications
+3 literature case labels
+Multigenerational family - 7 generations
+2 estimated unique individuals
+Deduplication status: partially resolved</t>
+  </si>
+  <si>
+    <t>2 publications
+2 literature case labels
+1 estimated unique individuals
+Deduplication status: partially resolved</t>
+  </si>
+  <si>
+    <t>2 publications
+2 literature case labels
+Deduplication status: partially resolved</t>
+  </si>
+  <si>
+    <t>2 publications
+23 literature case labels
+Deduplication status: partially resolved</t>
+  </si>
+  <si>
+    <t>1 publications
+1 literature case labels
+Multigenerational family - 2 generations
+Deduplication status: resolved</t>
+  </si>
+  <si>
+    <t>2 publications
+4 literature case labels
+Multigenerational family - 5 generations
+3 estimated unique individuals
+Deduplication status: partially resolved</t>
+  </si>
+  <si>
+    <t>2 publications
+3 literature case labels
+Multigenerational family - 5 generations
+1 estimated unique individuals
+Deduplication status: partially resolved</t>
+  </si>
+  <si>
+    <t>1 publications
+1 literature case labels
+Deduplication status: resolved</t>
+  </si>
+  <si>
+    <t>1 publications
+2 literature case labels
+Deduplication status: resolved</t>
   </si>
 </sst>
 </file>
@@ -2009,6 +2130,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93210A17-976E-449D-A8F5-248F94CB6DA5}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2024,342 +2148,322 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B12" s="7"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B13" s="7"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B15" s="7"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B16" s="7"/>
+    </row>
+    <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B19" s="7"/>
+    </row>
+    <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>113</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B21" s="7"/>
+    </row>
+    <row r="22" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B29" s="7"/>
+    </row>
+    <row r="30" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B39" s="7"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B40" s="7"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B41" s="7"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>117</v>
-      </c>
+      <c r="B42" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="86" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2376,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
@@ -2385,10 +2489,10 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2402,10 +2506,10 @@
         <v>16</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" t="s">
         <v>124</v>
-      </c>
-      <c r="F2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2422,10 +2526,10 @@
         <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3" t="s">
         <v>126</v>
-      </c>
-      <c r="F3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2442,10 +2546,10 @@
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" t="s">
         <v>128</v>
-      </c>
-      <c r="F4" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2459,7 +2563,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2470,7 +2574,7 @@
         <v>23</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2487,10 +2591,10 @@
         <v>26</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" t="s">
         <v>131</v>
-      </c>
-      <c r="F7" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2501,7 +2605,7 @@
         <v>23</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2518,7 +2622,7 @@
         <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2535,10 +2639,10 @@
         <v>35</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2549,10 +2653,10 @@
         <v>23</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2597,10 +2701,10 @@
         <v>99</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F17" t="s">
         <v>134</v>
-      </c>
-      <c r="F17" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2622,10 +2726,10 @@
         <v>5</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F19" t="s">
         <v>136</v>
-      </c>
-      <c r="F19" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2641,10 +2745,10 @@
         <v>32</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" t="s">
         <v>138</v>
-      </c>
-      <c r="F21" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2661,10 +2765,10 @@
         <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2675,7 +2779,7 @@
         <v>50</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2686,10 +2790,10 @@
         <v>102</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2706,10 +2810,10 @@
         <v>34</v>
       </c>
       <c r="E25" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" t="s">
         <v>142</v>
-      </c>
-      <c r="F25" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2717,10 +2821,10 @@
         <v>115</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F26" t="s">
         <v>144</v>
-      </c>
-      <c r="F26" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2728,7 +2832,7 @@
         <v>66</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2750,10 +2854,10 @@
         <v>105</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F29" t="s">
         <v>146</v>
-      </c>
-      <c r="F29" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2764,7 +2868,7 @@
         <v>65</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2781,10 +2885,10 @@
         <v>45</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F31" t="s">
         <v>148</v>
-      </c>
-      <c r="F31" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2801,7 +2905,7 @@
         <v>76</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2809,7 +2913,7 @@
         <v>67</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2817,10 +2921,10 @@
         <v>68</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F34" t="s">
         <v>150</v>
-      </c>
-      <c r="F34" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2838,10 +2942,10 @@
         <v>71</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2858,10 +2962,10 @@
         <v>58</v>
       </c>
       <c r="E38" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F38" t="s">
         <v>153</v>
-      </c>
-      <c r="F38" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2886,10 +2990,10 @@
         <v>44</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F40" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2906,10 +3010,10 @@
         <v>101</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F41" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2926,19 +3030,23 @@
         <v>101</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F42" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="21" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A753260-5018-4B3D-A2D6-F970E150F2D9}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2953,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2973,7 +3081,7 @@
         <v>23649844</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2981,13 +3089,13 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C3" s="2">
         <v>19001169</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2995,13 +3103,13 @@
         <v>13</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C4" s="2">
         <v>16823806</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3009,13 +3117,13 @@
         <v>13</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C5" s="2">
         <v>26053668</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -3029,7 +3137,7 @@
         <v>23649844</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3037,13 +3145,13 @@
         <v>13</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C7" s="2">
         <v>18945794</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3051,13 +3159,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C8" s="2">
         <v>24128683</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3065,7 +3173,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C9" s="2">
         <v>26053668</v>
@@ -3083,7 +3191,7 @@
         <v>23649844</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3091,13 +3199,13 @@
         <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C11" s="2">
         <v>30192380</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -3111,7 +3219,7 @@
         <v>23649844</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3125,7 +3233,7 @@
         <v>23649844</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -3139,7 +3247,7 @@
         <v>23649844</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3147,13 +3255,13 @@
         <v>19</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C15" s="8">
         <v>19151023</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3161,13 +3269,13 @@
         <v>19</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C16" s="8">
         <v>24128683</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -3175,13 +3283,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C17" s="8">
         <v>8042923</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -3189,13 +3297,13 @@
         <v>19</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C18" s="8">
         <v>6472420</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3209,7 +3317,7 @@
         <v>23649844</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3223,7 +3331,7 @@
         <v>23649844</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3237,7 +3345,7 @@
         <v>23649844</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3251,7 +3359,7 @@
         <v>23649844</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3294,13 +3402,13 @@
         <v>43</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C28" s="2">
         <v>30842973</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3315,13 +3423,13 @@
         <v>112</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C30" s="2">
         <v>39910058</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3336,13 +3444,13 @@
         <v>45</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C32" s="8">
         <v>19961535</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3350,13 +3458,13 @@
         <v>45</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C33" s="8">
         <v>9225322</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3364,13 +3472,13 @@
         <v>45</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C34" s="8">
         <v>25701871</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3378,13 +3486,13 @@
         <v>46</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C35" s="8">
         <v>24128683</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -3392,13 +3500,13 @@
         <v>46</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C36" s="8">
         <v>30842973</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -3412,7 +3520,7 @@
         <v>23649844</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -3420,13 +3528,13 @@
         <v>47</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C38" s="2">
         <v>39910058</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -3434,13 +3542,13 @@
         <v>114</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C39" s="2">
         <v>39910058</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -3448,13 +3556,13 @@
         <v>53</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C40" s="8">
         <v>30842973</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3462,13 +3570,13 @@
         <v>53</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C41" s="8">
         <v>30697589</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -3482,7 +3590,7 @@
         <v>40343075</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -3490,13 +3598,13 @@
         <v>66</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C43" s="8">
         <v>16951681</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -3517,7 +3625,7 @@
         <v>23649844</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -3525,13 +3633,13 @@
         <v>57</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C46" s="8">
         <v>26896090</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -3545,7 +3653,7 @@
         <v>23649844</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -3553,13 +3661,13 @@
         <v>61</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C48" s="8">
         <v>21909802</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -3573,7 +3681,7 @@
         <v>23649844</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -3587,7 +3695,7 @@
         <v>23649844</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -3601,7 +3709,7 @@
         <v>23649844</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -3609,13 +3717,13 @@
         <v>68</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C52" s="8">
         <v>23261988</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3637,13 +3745,13 @@
         <v>71</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C55" s="2">
         <v>23261988</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3651,13 +3759,13 @@
         <v>72</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C56" s="8">
         <v>31695592</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3672,13 +3780,13 @@
         <v>95</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C58" s="8">
         <v>30697589</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -3686,13 +3794,13 @@
         <v>96</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="8">
         <v>30697589</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -3700,13 +3808,13 @@
         <v>109</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C60" s="8">
         <v>30697589</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -3781,5 +3889,6 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="40" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>